--- a/research/traditional_assets/database/data/hong_kong/hong_kong_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_auto_truck.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,31 +590,31 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.177</v>
+        <v>0.02335</v>
       </c>
       <c r="E2">
-        <v>0.114</v>
+        <v>0.05662</v>
       </c>
       <c r="F2">
-        <v>0.355</v>
+        <v>0.0905</v>
       </c>
       <c r="G2">
-        <v>0.05805198797864265</v>
+        <v>0.05555498213064627</v>
       </c>
       <c r="H2">
-        <v>0.02312354517106592</v>
+        <v>0.020437478150975</v>
       </c>
       <c r="I2">
-        <v>0.02400577400856382</v>
+        <v>0.02000819906575318</v>
       </c>
       <c r="J2">
-        <v>0.02359309205584921</v>
+        <v>0.01872258813537234</v>
       </c>
       <c r="K2">
-        <v>2211.8</v>
+        <v>2920</v>
       </c>
       <c r="L2">
-        <v>0.06938632100035763</v>
+        <v>0.08970003938200359</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -638,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5607.7</v>
+        <v>9510.68</v>
       </c>
       <c r="V2">
-        <v>0.2917228068897709</v>
+        <v>0.4346845220411801</v>
       </c>
       <c r="W2">
-        <v>0.2094924179997917</v>
+        <v>0.04752588251716602</v>
       </c>
       <c r="X2">
-        <v>0.1009582556040706</v>
+        <v>0.1001516037203544</v>
       </c>
       <c r="Y2">
-        <v>0.108534162395721</v>
+        <v>-0.0526257212031884</v>
       </c>
       <c r="Z2">
-        <v>4.616807737713895</v>
+        <v>2.727605110492139</v>
       </c>
       <c r="AA2">
-        <v>0.1089247699600408</v>
+        <v>-0.03032160153885653</v>
       </c>
       <c r="AB2">
-        <v>0.09795753879853701</v>
+        <v>0.09784505554165163</v>
       </c>
       <c r="AC2">
-        <v>0.01096723116150383</v>
+        <v>-0.1281666570805082</v>
       </c>
       <c r="AD2">
-        <v>1335.5</v>
+        <v>1425.8</v>
       </c>
       <c r="AE2">
-        <v>3.83772119307326</v>
+        <v>3.841481522404171</v>
       </c>
       <c r="AF2">
-        <v>1339.337721193073</v>
+        <v>1429.641481522404</v>
       </c>
       <c r="AG2">
-        <v>-4268.362278806926</v>
+        <v>-8081.038518477596</v>
       </c>
       <c r="AH2">
-        <v>0.06513642953843199</v>
+        <v>0.06133393984740742</v>
       </c>
       <c r="AI2">
-        <v>0.08689021373875509</v>
+        <v>0.07032577251496872</v>
       </c>
       <c r="AJ2">
-        <v>-0.2854263664754517</v>
+        <v>-0.5856477933644239</v>
       </c>
       <c r="AK2">
-        <v>-0.4352612437014108</v>
+        <v>-0.7469881580414695</v>
       </c>
       <c r="AL2">
-        <v>59.5</v>
+        <v>59.971</v>
       </c>
       <c r="AM2">
-        <v>-111.5</v>
+        <v>-215.692</v>
       </c>
       <c r="AN2">
-        <v>1.15160085885021</v>
+        <v>1.307133217942324</v>
       </c>
       <c r="AO2">
-        <v>12.80504201680672</v>
+        <v>10.80522252422004</v>
       </c>
       <c r="AP2">
-        <v>-3.680606264438709</v>
+        <v>-7.408468146285238</v>
       </c>
       <c r="AQ2">
-        <v>-6.833183856502242</v>
+        <v>-3.004283886282291</v>
       </c>
     </row>
     <row r="3">
@@ -781,10 +781,10 @@
         <v>0.2094924179997917</v>
       </c>
       <c r="X3">
-        <v>0.1009582556040706</v>
+        <v>0.1009324961549014</v>
       </c>
       <c r="Y3">
-        <v>0.108534162395721</v>
+        <v>0.1085599218448903</v>
       </c>
       <c r="Z3">
         <v>4.616807737713895</v>
@@ -793,10 +793,10 @@
         <v>0.1089247699600408</v>
       </c>
       <c r="AB3">
-        <v>0.09795753879853701</v>
+        <v>0.09793345722791352</v>
       </c>
       <c r="AC3">
-        <v>0.01096723116150383</v>
+        <v>0.01099131273212732</v>
       </c>
       <c r="AD3">
         <v>1335.5</v>
@@ -839,6 +839,396 @@
       </c>
       <c r="AQ3">
         <v>-6.833183856502242</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brilliance China Automotive Holdings Limited (SEHK:1114)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Auto &amp; Truck</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.223</v>
+      </c>
+      <c r="E4">
+        <v>-0.0007599999999999999</v>
+      </c>
+      <c r="F4">
+        <v>-0.174</v>
+      </c>
+      <c r="G4">
+        <v>-0.1355812459858703</v>
+      </c>
+      <c r="H4">
+        <v>-0.1734104046242775</v>
+      </c>
+      <c r="I4">
+        <v>-0.2099984076163532</v>
+      </c>
+      <c r="J4">
+        <v>-0.159635355617655</v>
+      </c>
+      <c r="K4">
+        <v>751.9</v>
+      </c>
+      <c r="L4">
+        <v>4.829158638407193</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>3763.1</v>
+      </c>
+      <c r="V4">
+        <v>1.516645171691117</v>
+      </c>
+      <c r="W4">
+        <v>0.1048718914319985</v>
+      </c>
+      <c r="X4">
+        <v>0.09937071128580748</v>
+      </c>
+      <c r="Y4">
+        <v>0.005501180146191068</v>
+      </c>
+      <c r="Z4">
+        <v>0.03978735348336383</v>
+      </c>
+      <c r="AA4">
+        <v>-0.006351468322402129</v>
+      </c>
+      <c r="AB4">
+        <v>0.09786287845942668</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1042143467818288</v>
+      </c>
+      <c r="AD4">
+        <v>83.8</v>
+      </c>
+      <c r="AE4">
+        <v>0.003760329330910851</v>
+      </c>
+      <c r="AF4">
+        <v>83.80376032933091</v>
+      </c>
+      <c r="AG4">
+        <v>-3679.296239670669</v>
+      </c>
+      <c r="AH4">
+        <v>0.03267198341984926</v>
+      </c>
+      <c r="AI4">
+        <v>0.02271964292576892</v>
+      </c>
+      <c r="AJ4">
+        <v>3.070952163811171</v>
+      </c>
+      <c r="AK4">
+        <v>49.38901957918974</v>
+      </c>
+      <c r="AL4">
+        <v>0.205</v>
+      </c>
+      <c r="AM4">
+        <v>-84.595</v>
+      </c>
+      <c r="AN4">
+        <v>-3.597184065934066</v>
+      </c>
+      <c r="AO4">
+        <v>-159.5121951219512</v>
+      </c>
+      <c r="AP4">
+        <v>157.9368234748742</v>
+      </c>
+      <c r="AQ4">
+        <v>0.3865476683019091</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Qingling Motors Co., Ltd. (SEHK:1122)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Auto &amp; Truck</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.0583</v>
+      </c>
+      <c r="G5">
+        <v>-0.02463907603464871</v>
+      </c>
+      <c r="H5">
+        <v>-0.07064485081809432</v>
+      </c>
+      <c r="I5">
+        <v>-0.09720885466794996</v>
+      </c>
+      <c r="J5">
+        <v>-0.09720885466794996</v>
+      </c>
+      <c r="K5">
+        <v>-10.1</v>
+      </c>
+      <c r="L5">
+        <v>-0.01944177093358999</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>139.2</v>
+      </c>
+      <c r="V5">
+        <v>0.8375451263537906</v>
+      </c>
+      <c r="W5">
+        <v>-0.009820126397666504</v>
+      </c>
+      <c r="X5">
+        <v>0.09891171745397978</v>
+      </c>
+      <c r="Y5">
+        <v>-0.1087318438516463</v>
+      </c>
+      <c r="Z5">
+        <v>0.558506063472951</v>
+      </c>
+      <c r="AA5">
+        <v>-0.05429173475531092</v>
+      </c>
+      <c r="AB5">
+        <v>0.09782723262387659</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1521189673791875</v>
+      </c>
+      <c r="AD5">
+        <v>3.86</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>3.86</v>
+      </c>
+      <c r="AG5">
+        <v>-135.34</v>
+      </c>
+      <c r="AH5">
+        <v>0.02269787133952722</v>
+      </c>
+      <c r="AI5">
+        <v>0.003616060554962248</v>
+      </c>
+      <c r="AJ5">
+        <v>-4.385612443292285</v>
+      </c>
+      <c r="AK5">
+        <v>-0.1457996681964105</v>
+      </c>
+      <c r="AL5">
+        <v>0.213</v>
+      </c>
+      <c r="AM5">
+        <v>-19.587</v>
+      </c>
+      <c r="AN5">
+        <v>-0.1026595744680851</v>
+      </c>
+      <c r="AO5">
+        <v>-237.0892018779343</v>
+      </c>
+      <c r="AP5">
+        <v>3.599468085106382</v>
+      </c>
+      <c r="AQ5">
+        <v>2.578240669832031</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ev Dynamics (Holdings) Limited (SEHK:476)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Auto &amp; Truck</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.105</v>
+      </c>
+      <c r="G6">
+        <v>-7.115789473684211</v>
+      </c>
+      <c r="H6">
+        <v>-7.105263157894737</v>
+      </c>
+      <c r="I6">
+        <v>-26.92982456140351</v>
+      </c>
+      <c r="J6">
+        <v>-26.92982456140351</v>
+      </c>
+      <c r="K6">
+        <v>-33.6</v>
+      </c>
+      <c r="L6">
+        <v>-29.47368421052632</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0.68</v>
+      </c>
+      <c r="V6">
+        <v>0.0723404255319149</v>
+      </c>
+      <c r="W6">
+        <v>-0.1817198485667929</v>
+      </c>
+      <c r="X6">
+        <v>0.1101196359396547</v>
+      </c>
+      <c r="Y6">
+        <v>-0.2918394845064475</v>
+      </c>
+      <c r="Z6">
+        <v>0.006106314143080581</v>
+      </c>
+      <c r="AA6">
+        <v>-0.1644419685899771</v>
+      </c>
+      <c r="AB6">
+        <v>0.09718559598036912</v>
+      </c>
+      <c r="AC6">
+        <v>-0.2616275645703462</v>
+      </c>
+      <c r="AD6">
+        <v>2.64</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>2.64</v>
+      </c>
+      <c r="AG6">
+        <v>1.96</v>
+      </c>
+      <c r="AH6">
+        <v>0.2192691029900332</v>
+      </c>
+      <c r="AI6">
+        <v>0.01664145234493192</v>
+      </c>
+      <c r="AJ6">
+        <v>0.1725352112676056</v>
+      </c>
+      <c r="AK6">
+        <v>0.01240820460876171</v>
+      </c>
+      <c r="AL6">
+        <v>0.053</v>
+      </c>
+      <c r="AM6">
+        <v>-0.01</v>
+      </c>
+      <c r="AN6">
+        <v>-0.3295880149812734</v>
+      </c>
+      <c r="AO6">
+        <v>-579.2452830188679</v>
+      </c>
+      <c r="AP6">
+        <v>-0.2446941323345818</v>
+      </c>
+      <c r="AQ6">
+        <v>3070</v>
       </c>
     </row>
   </sheetData>
@@ -1133,49 +1523,49 @@
         <v>12.873781512605</v>
       </c>
       <c r="F2">
-        <v>7.04702013273357</v>
+        <v>3.04169570787619</v>
       </c>
       <c r="G2">
         <v>1.15491012356153</v>
       </c>
       <c r="H2">
-        <v>1.5957569651436</v>
+        <v>3.54612658920799</v>
       </c>
       <c r="I2">
         <v>0.065136429538432</v>
       </c>
       <c r="J2">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="K2">
         <v>19222.7</v>
       </c>
       <c r="L2">
-        <v>18860.2583501362</v>
+        <v>16648.7260961958</v>
       </c>
       <c r="M2">
         <v>14954.3377211931</v>
       </c>
       <c r="N2">
-        <v>15103.1417450436</v>
+        <v>15153.4336404344</v>
       </c>
       <c r="O2">
         <v>1339.33772119307</v>
       </c>
       <c r="P2">
-        <v>1850.58339490738</v>
+        <v>4112.40754423862</v>
       </c>
       <c r="Q2">
-        <v>0.097957538798537</v>
+        <v>0.0979334572279135</v>
       </c>
       <c r="R2">
-        <v>0.09744365554309389</v>
+        <v>0.0972484930913152</v>
       </c>
       <c r="S2">
         <v>0.054890074913216</v>
       </c>
       <c r="T2">
-        <v>0.049045074913216</v>
+        <v>0.051132574913216</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1184,20 +1574,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.100958255604071</v>
+        <v>0.100932496154901</v>
       </c>
       <c r="X2">
-        <v>0.102230328352642</v>
+        <v>0.10877747263584</v>
       </c>
       <c r="Y2">
         <v>1.07463496812016</v>
       </c>
       <c r="Z2">
-        <v>1.0994184541575</v>
+        <v>1.2275481615807</v>
       </c>
       <c r="AA2">
         <v>1335.5</v>
@@ -1230,7 +1620,7 @@
         <v>19222.7</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1808,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09792566492504134</v>
+        <v>0.09790132172561736</v>
       </c>
       <c r="C2">
-        <v>20571.18202025232</v>
+        <v>20571.2613865102</v>
       </c>
       <c r="D2">
-        <v>14963.48202025232</v>
+        <v>14963.5613865102</v>
       </c>
       <c r="E2">
         <v>-1339.337721193073</v>
@@ -1469,19 +1859,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09792566492504134</v>
+        <v>0.09790132172561736</v>
       </c>
       <c r="T2">
         <v>1.015551736571413</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.165</v>
       </c>
       <c r="W2">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1890,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09786292332704719</v>
+        <v>0.09782693029390224</v>
       </c>
       <c r="C3">
-        <v>20383.59429878679</v>
+        <v>20387.03686619029</v>
       </c>
       <c r="D3">
-        <v>14981.51467599872</v>
+        <v>14984.95724340222</v>
       </c>
       <c r="E3">
         <v>-1133.717343981143</v>
@@ -1533,37 +1923,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M3">
-        <v>11.85126285936972</v>
+        <v>11.56339433127301</v>
       </c>
       <c r="N3">
-        <v>754.1387371406302</v>
+        <v>754.4266056687269</v>
       </c>
       <c r="O3">
-        <v>124.432891628204</v>
+        <v>124.4803899353399</v>
       </c>
       <c r="P3">
-        <v>629.7058455124262</v>
+        <v>629.9462157333869</v>
       </c>
       <c r="Q3">
-        <v>1023.405845512426</v>
+        <v>1023.646215733387</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09836531068476266</v>
+        <v>0.09834076216643443</v>
       </c>
       <c r="T3">
         <v>1.024117248693</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.165</v>
       </c>
       <c r="W3">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1961,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>64.63361829785096</v>
+        <v>66.24266007502594</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1972,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09780018172905301</v>
+        <v>0.09775253886218713</v>
       </c>
       <c r="C4">
-        <v>20196.05009246293</v>
+        <v>20202.8736198124</v>
       </c>
       <c r="D4">
-        <v>14999.59084688679</v>
+        <v>15006.41437423626</v>
       </c>
       <c r="E4">
         <v>-928.0969667692118</v>
@@ -1615,37 +2005,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M4">
-        <v>23.70252571873943</v>
+        <v>23.12678866254602</v>
       </c>
       <c r="N4">
-        <v>742.2874742812604</v>
+        <v>742.8632113374539</v>
       </c>
       <c r="O4">
-        <v>122.477433256408</v>
+        <v>122.5724298706799</v>
       </c>
       <c r="P4">
-        <v>619.8100410248525</v>
+        <v>620.290781466774</v>
       </c>
       <c r="Q4">
-        <v>1013.510041024852</v>
+        <v>1013.990781466774</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09881392880692724</v>
+        <v>0.09878917077951307</v>
       </c>
       <c r="T4">
         <v>1.032857567184416</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.165</v>
       </c>
       <c r="W4">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +2043,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>32.31680914892547</v>
+        <v>33.12133003751297</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +2054,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09773744013105887</v>
+        <v>0.09767814743047203</v>
       </c>
       <c r="C5">
-        <v>20008.54955898256</v>
+        <v>20018.77191097053</v>
       </c>
       <c r="D5">
-        <v>15017.71069061835</v>
+        <v>15027.93304260632</v>
       </c>
       <c r="E5">
         <v>-722.476589557281</v>
@@ -1697,37 +2087,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M5">
-        <v>35.55378857810914</v>
+        <v>34.69018299381904</v>
       </c>
       <c r="N5">
-        <v>730.4362114218908</v>
+        <v>731.2998170061809</v>
       </c>
       <c r="O5">
-        <v>120.521974884612</v>
+        <v>120.6644698060199</v>
       </c>
       <c r="P5">
-        <v>609.9142365372788</v>
+        <v>610.635347200161</v>
       </c>
       <c r="Q5">
-        <v>1003.614236537279</v>
+        <v>1004.335347200161</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09927179678728082</v>
+        <v>0.09924682493100573</v>
       </c>
       <c r="T5">
         <v>1.041778098428232</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.165</v>
       </c>
       <c r="W5">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +2125,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>21.54453943261699</v>
+        <v>22.08088669167531</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +2136,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09767469853306472</v>
+        <v>0.09760375599875691</v>
       </c>
       <c r="C6">
-        <v>19821.09285681045</v>
+        <v>19834.73200477281</v>
       </c>
       <c r="D6">
-        <v>15035.87436565817</v>
+        <v>15049.51351362054</v>
       </c>
       <c r="E6">
         <v>-516.8562123453503</v>
@@ -1779,37 +2169,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M6">
-        <v>47.40505143747886</v>
+        <v>46.25357732509205</v>
       </c>
       <c r="N6">
-        <v>718.584948562521</v>
+        <v>719.7364226749079</v>
       </c>
       <c r="O6">
-        <v>118.566516512816</v>
+        <v>118.7565097413598</v>
       </c>
       <c r="P6">
-        <v>600.0184320497051</v>
+        <v>600.9799129335481</v>
       </c>
       <c r="Q6">
-        <v>993.718432049705</v>
+        <v>994.6799129335481</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09973920368389175</v>
+        <v>0.09971401354398779</v>
       </c>
       <c r="T6">
         <v>1.05088447407296</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.165</v>
       </c>
       <c r="W6">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +2207,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.15840457446274</v>
+        <v>16.56066501875648</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +2218,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09761195693507056</v>
+        <v>0.09752936456704181</v>
       </c>
       <c r="C7">
-        <v>19633.68014517894</v>
+        <v>19650.75416785234</v>
       </c>
       <c r="D7">
-        <v>15054.08203123859</v>
+        <v>15071.156053912</v>
       </c>
       <c r="E7">
         <v>-311.2358351334194</v>
@@ -1861,37 +2251,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M7">
-        <v>59.25631429684858</v>
+        <v>57.81697165636507</v>
       </c>
       <c r="N7">
-        <v>706.7336857031513</v>
+        <v>708.1730283436348</v>
       </c>
       <c r="O7">
-        <v>116.61105814102</v>
+        <v>116.8485496766997</v>
       </c>
       <c r="P7">
-        <v>590.1226275621314</v>
+        <v>591.324478666935</v>
       </c>
       <c r="Q7">
-        <v>983.8226275621313</v>
+        <v>985.0244786669349</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1002164507256945</v>
+        <v>0.1001910377067169</v>
       </c>
       <c r="T7">
         <v>1.060182562889157</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.165</v>
       </c>
       <c r="W7">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2289,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>12.92672365957019</v>
+        <v>13.24853201500518</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2300,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09754921533707639</v>
+        <v>0.09745497313532669</v>
       </c>
       <c r="C8">
-        <v>19446.31158409258</v>
+        <v>19466.83866837823</v>
       </c>
       <c r="D8">
-        <v>15072.33384736417</v>
+        <v>15092.86093164981</v>
       </c>
       <c r="E8">
         <v>-105.6154579214888</v>
@@ -1943,37 +2333,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M8">
-        <v>71.10757715621828</v>
+        <v>69.38036598763807</v>
       </c>
       <c r="N8">
-        <v>694.8824228437816</v>
+        <v>696.6096340123618</v>
       </c>
       <c r="O8">
-        <v>114.655599769224</v>
+        <v>114.9405896120397</v>
       </c>
       <c r="P8">
-        <v>580.2268230745576</v>
+        <v>581.669044400322</v>
       </c>
       <c r="Q8">
-        <v>973.9268230745575</v>
+        <v>975.369044400322</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.100703851959876</v>
+        <v>0.1006782113197168</v>
       </c>
       <c r="T8">
         <v>1.069678483382294</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.165</v>
       </c>
       <c r="W8">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2371,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>10.77226971630849</v>
+        <v>11.04044334583765</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2382,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09748647373908223</v>
+        <v>0.09738058170361158</v>
       </c>
       <c r="C9">
-        <v>19258.98733433285</v>
+        <v>19282.98577606661</v>
       </c>
       <c r="D9">
-        <v>15090.62997481637</v>
+        <v>15114.62841655012</v>
       </c>
       <c r="E9">
         <v>100.0049192904421</v>
@@ -2025,37 +2415,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M9">
-        <v>82.95884001558801</v>
+        <v>80.94376031891109</v>
       </c>
       <c r="N9">
-        <v>683.0311599844119</v>
+        <v>685.0462396810888</v>
       </c>
       <c r="O9">
-        <v>112.700141397428</v>
+        <v>113.0326295473797</v>
       </c>
       <c r="P9">
-        <v>570.331018586984</v>
+        <v>572.0136101337091</v>
       </c>
       <c r="Q9">
-        <v>964.0310185869839</v>
+        <v>965.713610133709</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1012017349410292</v>
+        <v>0.1011758617846091</v>
       </c>
       <c r="T9">
         <v>1.079378617219369</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.165</v>
       </c>
       <c r="W9">
-        <v>0.04812657491321597</v>
+        <v>0.04695757491321597</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2453,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>9.233374042550137</v>
+        <v>9.463237153575131</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2464,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09749721214108809</v>
+        <v>0.09740639027189649</v>
       </c>
       <c r="C10">
-        <v>19050.23237317568</v>
+        <v>19069.80651094304</v>
       </c>
       <c r="D10">
-        <v>15087.49539087113</v>
+        <v>15107.06952863849</v>
       </c>
       <c r="E10">
         <v>305.6252965023727</v>
@@ -2107,37 +2497,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M10">
-        <v>96.61956219442271</v>
+        <v>94.97459917672725</v>
       </c>
       <c r="N10">
-        <v>669.3704378055772</v>
+        <v>671.0154008232727</v>
       </c>
       <c r="O10">
-        <v>110.4461222379202</v>
+        <v>110.71754113584</v>
       </c>
       <c r="P10">
-        <v>558.924315567657</v>
+        <v>560.2978596874327</v>
       </c>
       <c r="Q10">
-        <v>952.6243155676569</v>
+        <v>953.9978596874327</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1017104414652509</v>
+        <v>0.1016843307378687</v>
       </c>
       <c r="T10">
         <v>1.089289623531164</v>
       </c>
       <c r="U10">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V10">
         <v>0.165</v>
       </c>
       <c r="W10">
-        <v>0.04904507491321597</v>
+        <v>0.04821007491321597</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2535,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.927897649325264</v>
+        <v>8.065209083690448</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2546,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09744365554309392</v>
+        <v>0.09734452384018137</v>
       </c>
       <c r="C11">
-        <v>18860.25835013621</v>
+        <v>18882.31842821708</v>
       </c>
       <c r="D11">
-        <v>15103.14174504359</v>
+        <v>15125.20182312445</v>
       </c>
       <c r="E11">
         <v>511.2456737143034</v>
@@ -2189,37 +2579,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M11">
-        <v>108.6970074687255</v>
+        <v>106.8464240738182</v>
       </c>
       <c r="N11">
-        <v>657.2929925312744</v>
+        <v>659.1435759261817</v>
       </c>
       <c r="O11">
-        <v>108.4533437676603</v>
+        <v>108.75869002782</v>
       </c>
       <c r="P11">
-        <v>548.8396487636142</v>
+        <v>550.3848858983617</v>
       </c>
       <c r="Q11">
-        <v>942.5396487636141</v>
+        <v>944.0848858983617</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1022303283526423</v>
+        <v>0.1022039748329582</v>
       </c>
       <c r="T11">
         <v>1.099418454157503</v>
       </c>
       <c r="U11">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V11">
         <v>0.165</v>
       </c>
       <c r="W11">
-        <v>0.04904507491321597</v>
+        <v>0.04821007491321597</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2617,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.047020132733569</v>
+        <v>7.169074741058175</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2628,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09757379894509975</v>
+        <v>0.09742460740846627</v>
       </c>
       <c r="C12">
-        <v>18616.67332115591</v>
+        <v>18653.23481915059</v>
       </c>
       <c r="D12">
-        <v>15065.17709327522</v>
+        <v>15101.7385912699</v>
       </c>
       <c r="E12">
         <v>716.8660509262345</v>
@@ -2271,37 +2661,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M12">
-        <v>125.2981010416909</v>
+        <v>122.2137953835119</v>
       </c>
       <c r="N12">
-        <v>640.691898958309</v>
+        <v>643.776204616488</v>
       </c>
       <c r="O12">
-        <v>105.714163328121</v>
+        <v>106.2230737617205</v>
       </c>
       <c r="P12">
-        <v>534.977735630188</v>
+        <v>537.5531308547675</v>
       </c>
       <c r="Q12">
-        <v>928.677735630188</v>
+        <v>931.2531308547674</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1027617682819757</v>
+        <v>0.1027351665746052</v>
       </c>
       <c r="T12">
         <v>1.109772369908872</v>
       </c>
       <c r="U12">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V12">
         <v>0.165</v>
       </c>
       <c r="W12">
-        <v>0.05088207491321597</v>
+        <v>0.04962957491321596</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2699,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.113340853786199</v>
+        <v>6.267623042032954</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2710,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.0976763873471056</v>
+        <v>0.09737693597675115</v>
       </c>
       <c r="C13">
-        <v>18381.26072974076</v>
+        <v>18461.57264799335</v>
       </c>
       <c r="D13">
-        <v>15035.384879072</v>
+        <v>15115.69679732459</v>
       </c>
       <c r="E13">
         <v>922.4864281381651</v>
@@ -2353,45 +2743,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M13">
-        <v>141.2206473698568</v>
+        <v>134.4351749218631</v>
       </c>
       <c r="N13">
-        <v>624.7693526301431</v>
+        <v>631.5548250781368</v>
       </c>
       <c r="O13">
-        <v>103.0869431839736</v>
+        <v>104.2065461378926</v>
       </c>
       <c r="P13">
-        <v>521.6824094461695</v>
+        <v>527.3482789402442</v>
       </c>
       <c r="Q13">
-        <v>915.3824094461694</v>
+        <v>921.0482789402441</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1033051506816313</v>
+        <v>0.1032782952093229</v>
       </c>
       <c r="T13">
         <v>1.120358957924317</v>
       </c>
       <c r="U13">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V13">
         <v>0.165</v>
       </c>
       <c r="W13">
-        <v>0.05213457491321597</v>
+        <v>0.04962957491321596</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>5.424065207645398</v>
+        <v>5.697839129120868</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2792,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09765372574911144</v>
+        <v>0.09740942454503604</v>
       </c>
       <c r="C14">
-        <v>18182.21125641075</v>
+        <v>18246.4368120856</v>
       </c>
       <c r="D14">
-        <v>15041.95578295392</v>
+        <v>15106.18133862877</v>
       </c>
       <c r="E14">
         <v>1128.106805350096</v>
@@ -2435,37 +2825,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M14">
-        <v>154.0588880398438</v>
+        <v>148.6305100814488</v>
       </c>
       <c r="N14">
-        <v>611.9311119601562</v>
+        <v>617.359489918551</v>
       </c>
       <c r="O14">
-        <v>100.9686334734258</v>
+        <v>101.8643158365609</v>
       </c>
       <c r="P14">
-        <v>510.9624784867304</v>
+        <v>515.4951740819902</v>
       </c>
       <c r="Q14">
-        <v>904.6624784867304</v>
+        <v>909.1951740819901</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.103860882681279</v>
+        <v>0.1038337676766479</v>
       </c>
       <c r="T14">
         <v>1.13118615021284</v>
       </c>
       <c r="U14">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V14">
         <v>0.165</v>
       </c>
       <c r="W14">
-        <v>0.05213457491321597</v>
+        <v>0.05029757491321597</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2863,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.972059773674948</v>
+        <v>5.153652500958525</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2874,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.09763106415111729</v>
+        <v>0.09736843311332093</v>
       </c>
       <c r="C15">
-        <v>17983.16752894703</v>
+        <v>18052.82424592074</v>
       </c>
       <c r="D15">
-        <v>15048.53243270213</v>
+        <v>15118.18914967585</v>
       </c>
       <c r="E15">
         <v>1333.727182562026</v>
@@ -2517,37 +2907,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M15">
-        <v>166.8971287098308</v>
+        <v>161.0163859215695</v>
       </c>
       <c r="N15">
-        <v>599.0928712901691</v>
+        <v>604.9736140784304</v>
       </c>
       <c r="O15">
-        <v>98.85032376287791</v>
+        <v>99.82064632294102</v>
       </c>
       <c r="P15">
-        <v>500.2425475272912</v>
+        <v>505.1529677554894</v>
       </c>
       <c r="Q15">
-        <v>893.9425475272911</v>
+        <v>898.8529677554893</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1044293901291945</v>
+        <v>0.1044020096259803</v>
       </c>
       <c r="T15">
         <v>1.142262243473513</v>
       </c>
       <c r="U15">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V15">
         <v>0.165</v>
       </c>
       <c r="W15">
-        <v>0.05213457491321597</v>
+        <v>0.05029757491321597</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2945,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.589593637238414</v>
+        <v>4.757217693192485</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2956,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09760840255312311</v>
+        <v>0.09732744168160583</v>
       </c>
       <c r="C16">
-        <v>17784.12955488954</v>
+        <v>17859.23078481332</v>
       </c>
       <c r="D16">
-        <v>15055.11483585657</v>
+        <v>15130.21606578036</v>
       </c>
       <c r="E16">
         <v>1539.347559773958</v>
@@ -2599,37 +2989,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M16">
-        <v>179.7353693798178</v>
+        <v>173.4022617616903</v>
       </c>
       <c r="N16">
-        <v>586.2546306201821</v>
+        <v>592.5877382383096</v>
       </c>
       <c r="O16">
-        <v>96.73201405233004</v>
+        <v>97.77697680932108</v>
       </c>
       <c r="P16">
-        <v>489.522616567852</v>
+        <v>494.8107614289885</v>
       </c>
       <c r="Q16">
-        <v>883.2226165678519</v>
+        <v>888.5107614289884</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1050111186805499</v>
+        <v>0.104983466504367</v>
       </c>
       <c r="T16">
         <v>1.153595920298388</v>
       </c>
       <c r="U16">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V16">
         <v>0.165</v>
       </c>
       <c r="W16">
-        <v>0.05213457491321597</v>
+        <v>0.05029757491321597</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +3027,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.261765520292812</v>
+        <v>4.41741642939302</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +3038,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09776109095512897</v>
+        <v>0.09741170024989071</v>
       </c>
       <c r="C17">
-        <v>17534.26950941724</v>
+        <v>17628.90960647741</v>
       </c>
       <c r="D17">
-        <v>15010.87516759621</v>
+        <v>15105.51526465637</v>
       </c>
       <c r="E17">
         <v>1744.967936985888</v>
@@ -2681,37 +3071,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M17">
-        <v>196.8916379712552</v>
+        <v>188.87244325999</v>
       </c>
       <c r="N17">
-        <v>569.0983620287446</v>
+        <v>577.1175567400099</v>
       </c>
       <c r="O17">
-        <v>93.90122973474287</v>
+        <v>95.22439686210164</v>
       </c>
       <c r="P17">
-        <v>475.1971322940018</v>
+        <v>481.8931598779083</v>
       </c>
       <c r="Q17">
-        <v>868.8971322940017</v>
+        <v>875.5931598779082</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1056065349625254</v>
+        <v>0.1055786047210686</v>
       </c>
       <c r="T17">
         <v>1.165196271872083</v>
       </c>
       <c r="U17">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V17">
         <v>0.165</v>
       </c>
       <c r="W17">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +3109,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.890414076964654</v>
+        <v>4.055594277168248</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +3120,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09775011935713479</v>
+        <v>0.09737905881817562</v>
       </c>
       <c r="C18">
-        <v>17331.81935182978</v>
+        <v>17432.84864458499</v>
       </c>
       <c r="D18">
-        <v>15014.04538722068</v>
+        <v>15115.07467997588</v>
       </c>
       <c r="E18">
         <v>1950.588314197819</v>
@@ -2763,37 +3153,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M18">
-        <v>210.017747169339</v>
+        <v>201.4639394773226</v>
       </c>
       <c r="N18">
-        <v>555.9722528306609</v>
+        <v>564.5260605226772</v>
       </c>
       <c r="O18">
-        <v>91.73542171705904</v>
+        <v>93.14679998624175</v>
       </c>
       <c r="P18">
-        <v>464.2368311136019</v>
+        <v>471.3792605364355</v>
       </c>
       <c r="Q18">
-        <v>857.9368311136018</v>
+        <v>865.0792605364354</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1062161278226432</v>
+        <v>0.1061879128953108</v>
       </c>
       <c r="T18">
         <v>1.177072822292771</v>
       </c>
       <c r="U18">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V18">
         <v>0.165</v>
       </c>
       <c r="W18">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +3191,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.647263197154362</v>
+        <v>3.802119634845232</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +3202,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09773914775914065</v>
+        <v>0.09734641738646049</v>
       </c>
       <c r="C19">
-        <v>17129.37053359333</v>
+        <v>17236.79978956705</v>
       </c>
       <c r="D19">
-        <v>15017.21694619616</v>
+        <v>15124.64620216988</v>
       </c>
       <c r="E19">
         <v>2156.20869140975</v>
@@ -2845,37 +3235,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M19">
-        <v>223.1438563674227</v>
+        <v>214.0554356946553</v>
       </c>
       <c r="N19">
-        <v>542.8461436325772</v>
+        <v>551.9345643053446</v>
       </c>
       <c r="O19">
-        <v>89.56961369937524</v>
+        <v>91.06920311038186</v>
       </c>
       <c r="P19">
-        <v>453.276529933202</v>
+        <v>460.8653611949627</v>
       </c>
       <c r="Q19">
-        <v>846.9765299332018</v>
+        <v>854.5653611949626</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1068404096673421</v>
+        <v>0.1068119031942335</v>
       </c>
       <c r="T19">
         <v>1.189235554651307</v>
       </c>
       <c r="U19">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V19">
         <v>0.165</v>
       </c>
       <c r="W19">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +3273,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.432718303204106</v>
+        <v>3.578465538677865</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +3284,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.09772817616114648</v>
+        <v>0.0973137759547454</v>
       </c>
       <c r="C20">
-        <v>16926.92305555687</v>
+        <v>17040.76306443795</v>
       </c>
       <c r="D20">
-        <v>15020.38984537162</v>
+        <v>15134.2298542527</v>
       </c>
       <c r="E20">
         <v>2361.82906862168</v>
@@ -2927,37 +3317,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M20">
-        <v>236.2699655655063</v>
+        <v>226.646931911988</v>
       </c>
       <c r="N20">
-        <v>529.7200344344935</v>
+        <v>539.3430680880119</v>
       </c>
       <c r="O20">
-        <v>87.40380568169144</v>
+        <v>88.99160623452197</v>
       </c>
       <c r="P20">
-        <v>442.3162287528021</v>
+        <v>450.35146185349</v>
       </c>
       <c r="Q20">
-        <v>836.016228752802</v>
+        <v>844.0514618534899</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1074799178984971</v>
+        <v>0.1074511127687397</v>
       </c>
       <c r="T20">
         <v>1.201694939018588</v>
       </c>
       <c r="U20">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V20">
         <v>0.165</v>
       </c>
       <c r="W20">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3355,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.242011730803878</v>
+        <v>3.379661897640207</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3366,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09771720456315233</v>
+        <v>0.09728113452303028</v>
       </c>
       <c r="C21">
-        <v>16724.47691857004</v>
+        <v>16844.73849227044</v>
       </c>
       <c r="D21">
-        <v>15023.56408559672</v>
+        <v>15143.82565929712</v>
       </c>
       <c r="E21">
         <v>2567.449445833611</v>
@@ -3009,37 +3399,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M21">
-        <v>249.39607476359</v>
+        <v>239.2384281293207</v>
       </c>
       <c r="N21">
-        <v>516.5939252364099</v>
+        <v>526.7515718706793</v>
       </c>
       <c r="O21">
-        <v>85.23799766400764</v>
+        <v>86.91400935866208</v>
       </c>
       <c r="P21">
-        <v>431.3559275724022</v>
+        <v>439.8375625120172</v>
       </c>
       <c r="Q21">
-        <v>825.0559275724022</v>
+        <v>833.5375625120171</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1081352164563473</v>
+        <v>0.1081061052957028</v>
       </c>
       <c r="T21">
         <v>1.214461962506048</v>
       </c>
       <c r="U21">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V21">
         <v>0.165</v>
       </c>
       <c r="W21">
-        <v>0.05330357491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3437,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.071379534445779</v>
+        <v>3.201784955659143</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3448,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09814043296515818</v>
+        <v>0.09724849309131518</v>
       </c>
       <c r="C22">
-        <v>16397.37495131065</v>
+        <v>16648.72609619579</v>
       </c>
       <c r="D22">
-        <v>14902.08249554926</v>
+        <v>15153.43364043441</v>
       </c>
       <c r="E22">
         <v>2773.069823045542</v>
@@ -3091,45 +3481,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M22">
-        <v>273.2144435766941</v>
+        <v>251.8299243466533</v>
       </c>
       <c r="N22">
-        <v>492.7755564233058</v>
+        <v>514.1600756533466</v>
       </c>
       <c r="O22">
-        <v>81.30796680984545</v>
+        <v>84.83641248280219</v>
       </c>
       <c r="P22">
-        <v>411.4675896134603</v>
+        <v>429.3236631705444</v>
       </c>
       <c r="Q22">
-        <v>805.1675896134602</v>
+        <v>823.0236631705443</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1088068974781437</v>
+        <v>0.10877747263584</v>
       </c>
       <c r="T22">
         <v>1.227548161580696</v>
       </c>
       <c r="U22">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V22">
         <v>0.165</v>
       </c>
       <c r="W22">
-        <v>0.05547457491321596</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.803621909487295</v>
+        <v>3.041695707876185</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3530,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09815117136716403</v>
+        <v>0.09765422665960008</v>
       </c>
       <c r="C23">
-        <v>16188.69782200736</v>
+        <v>16324.53762726277</v>
       </c>
       <c r="D23">
-        <v>14899.02574345791</v>
+        <v>15034.86554871332</v>
       </c>
       <c r="E23">
         <v>2978.690200257472</v>
@@ -3173,37 +3563,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M23">
-        <v>286.8751657555287</v>
+        <v>275.2164903676123</v>
       </c>
       <c r="N23">
-        <v>479.1148342444712</v>
+        <v>490.7735096323876</v>
       </c>
       <c r="O23">
-        <v>79.05394765033775</v>
+        <v>80.97762908934396</v>
       </c>
       <c r="P23">
-        <v>400.0608865941334</v>
+        <v>409.7958805430437</v>
       </c>
       <c r="Q23">
-        <v>793.7608865941334</v>
+        <v>803.4958805430435</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1094955830827705</v>
+        <v>0.1094658366174996</v>
       </c>
       <c r="T23">
         <v>1.240965656834448</v>
       </c>
       <c r="U23">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V23">
         <v>0.165</v>
       </c>
       <c r="W23">
-        <v>0.05547457491321596</v>
+        <v>0.05322007491321597</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3601,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.670116104273615</v>
+        <v>2.783227120500125</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3612,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09816190976916986</v>
+        <v>0.09764246022788495</v>
       </c>
       <c r="C24">
-        <v>15980.02194646403</v>
+        <v>16122.32964055175</v>
       </c>
       <c r="D24">
-        <v>14895.97024512651</v>
+        <v>15038.27793921422</v>
       </c>
       <c r="E24">
         <v>3184.310577469404</v>
@@ -3255,37 +3645,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M24">
-        <v>300.5358879343635</v>
+        <v>288.3220375279748</v>
       </c>
       <c r="N24">
-        <v>465.4541120656364</v>
+        <v>477.6679624720251</v>
       </c>
       <c r="O24">
-        <v>76.79992849083001</v>
+        <v>78.81521380788413</v>
       </c>
       <c r="P24">
-        <v>388.6541835748064</v>
+        <v>398.8527486641409</v>
       </c>
       <c r="Q24">
-        <v>782.3541835748064</v>
+        <v>792.5527486641408</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.110201927292644</v>
+        <v>0.1101718509576634</v>
       </c>
       <c r="T24">
         <v>1.254727190428039</v>
       </c>
       <c r="U24">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V24">
         <v>0.165</v>
       </c>
       <c r="W24">
-        <v>0.05547457491321596</v>
+        <v>0.05322007491321597</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3683,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.548747190442996</v>
+        <v>2.656716796841028</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3694,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09869118317117571</v>
+        <v>0.09763069379616984</v>
       </c>
       <c r="C25">
-        <v>15625.3400362117</v>
+        <v>15920.12320317979</v>
       </c>
       <c r="D25">
-        <v>14746.90871208611</v>
+        <v>15041.6918790542</v>
       </c>
       <c r="E25">
         <v>3389.930954681334</v>
@@ -3337,45 +3727,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M25">
-        <v>326.9656355380591</v>
+        <v>301.4275846883373</v>
       </c>
       <c r="N25">
-        <v>439.0243644619408</v>
+        <v>464.5624153116626</v>
       </c>
       <c r="O25">
-        <v>72.43902013622024</v>
+        <v>76.65279852642432</v>
       </c>
       <c r="P25">
-        <v>366.5853443257205</v>
+        <v>387.9096167852383</v>
       </c>
       <c r="Q25">
-        <v>760.2853443257204</v>
+        <v>781.6096167852381</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1109266181053715</v>
+        <v>0.1108962033326366</v>
       </c>
       <c r="T25">
         <v>1.268846166452634</v>
       </c>
       <c r="U25">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V25">
         <v>0.165</v>
       </c>
       <c r="W25">
-        <v>0.05772907491321597</v>
+        <v>0.05322007491321597</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.34272326123654</v>
+        <v>2.541207370891418</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3776,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09966634657318153</v>
+        <v>0.09832032736445473</v>
       </c>
       <c r="C26">
-        <v>15152.75064061257</v>
+        <v>15516.99347741391</v>
       </c>
       <c r="D26">
-        <v>14479.93969369891</v>
+        <v>14844.18253050025</v>
       </c>
       <c r="E26">
         <v>3595.551331893265</v>
@@ -3419,45 +3809,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M26">
-        <v>364.3755112848719</v>
+        <v>331.805243534502</v>
       </c>
       <c r="N26">
-        <v>401.614488715128</v>
+        <v>434.1847564654979</v>
       </c>
       <c r="O26">
-        <v>66.26639063799612</v>
+        <v>71.64048481680716</v>
       </c>
       <c r="P26">
-        <v>335.3480980771319</v>
+        <v>362.5442716486908</v>
       </c>
       <c r="Q26">
-        <v>729.0480980771318</v>
+        <v>756.2442716486908</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1116703797289601</v>
+        <v>0.1116396176122143</v>
       </c>
       <c r="T26">
         <v>1.283336694477875</v>
       </c>
       <c r="U26">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V26">
         <v>0.165</v>
       </c>
       <c r="W26">
-        <v>0.06165357491321598</v>
+        <v>0.05614257491321597</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.102199451601297</v>
+        <v>2.308553029001033</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3858,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09973887497518738</v>
+        <v>0.09892228593273962</v>
       </c>
       <c r="C27">
-        <v>14927.65994838928</v>
+        <v>15143.16529990639</v>
       </c>
       <c r="D27">
-        <v>14460.46937868755</v>
+        <v>14675.97473020466</v>
       </c>
       <c r="E27">
         <v>3801.171709105196</v>
@@ -3501,37 +3891,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M27">
-        <v>379.5578242550749</v>
+        <v>360.0238884199414</v>
       </c>
       <c r="N27">
-        <v>386.432175744925</v>
+        <v>405.9661115800585</v>
       </c>
       <c r="O27">
-        <v>63.76130899791263</v>
+        <v>66.98440841070966</v>
       </c>
       <c r="P27">
-        <v>322.6708667470124</v>
+        <v>338.9817031693489</v>
       </c>
       <c r="Q27">
-        <v>716.3708667470123</v>
+        <v>732.6817031693488</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1124339749958445</v>
+        <v>0.1124028562725808</v>
       </c>
       <c r="T27">
         <v>1.29821363658379</v>
       </c>
       <c r="U27">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V27">
         <v>0.165</v>
       </c>
       <c r="W27">
-        <v>0.06165357491321598</v>
+        <v>0.05848057491321597</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3929,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.018111473537245</v>
+        <v>2.127608818852956</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3940,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1028508033771932</v>
+        <v>0.09896312450102451</v>
       </c>
       <c r="C28">
-        <v>13933.26986589635</v>
+        <v>14926.27120991343</v>
       </c>
       <c r="D28">
-        <v>13671.69967340654</v>
+        <v>14664.70101742362</v>
       </c>
       <c r="E28">
         <v>4006.792086317126</v>
@@ -3583,45 +3973,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M28">
-        <v>469.5859545304206</v>
+        <v>374.424843956739</v>
       </c>
       <c r="N28">
-        <v>296.4040454695793</v>
+        <v>391.5651560432609</v>
       </c>
       <c r="O28">
-        <v>48.90666750248059</v>
+        <v>64.60825074713804</v>
       </c>
       <c r="P28">
-        <v>247.4973779670987</v>
+        <v>326.9569052961228</v>
       </c>
       <c r="Q28">
-        <v>641.1973779670986</v>
+        <v>720.6569052961228</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1132182079726447</v>
+        <v>0.1131867230048491</v>
       </c>
       <c r="T28">
         <v>1.31349265820608</v>
       </c>
       <c r="U28">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V28">
         <v>0.165</v>
       </c>
       <c r="W28">
-        <v>0.07334357491321596</v>
+        <v>0.05848057491321597</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.631202962120065</v>
+        <v>2.045777710435535</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +4022,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1030402317791991</v>
+        <v>0.1007624730693094</v>
       </c>
       <c r="C29">
-        <v>13682.40494404617</v>
+        <v>14240.56128602566</v>
       </c>
       <c r="D29">
-        <v>13626.4551287683</v>
+        <v>14184.61147074779</v>
       </c>
       <c r="E29">
         <v>4212.412463529057</v>
@@ -3665,45 +4055,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M29">
-        <v>487.6469527815906</v>
+        <v>432.1294509343695</v>
       </c>
       <c r="N29">
-        <v>278.3430472184093</v>
+        <v>333.8605490656304</v>
       </c>
       <c r="O29">
-        <v>45.92660279103753</v>
+        <v>55.08699059582902</v>
       </c>
       <c r="P29">
-        <v>232.4164444273717</v>
+        <v>278.7735584698014</v>
       </c>
       <c r="Q29">
-        <v>626.1164444273717</v>
+        <v>672.4735584698013</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1140239267844257</v>
+        <v>0.1139920655380015</v>
       </c>
       <c r="T29">
         <v>1.329190283160488</v>
       </c>
       <c r="U29">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V29">
         <v>0.165</v>
       </c>
       <c r="W29">
-        <v>0.07334357491321596</v>
+        <v>0.06499357491321597</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.570788037597099</v>
+        <v>1.77259383349999</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +4104,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1032296601812049</v>
+        <v>0.1017802616375943</v>
       </c>
       <c r="C30">
-        <v>13431.83849520675</v>
+        <v>13777.04759109486</v>
       </c>
       <c r="D30">
-        <v>13581.50905714081</v>
+        <v>13926.71815302892</v>
       </c>
       <c r="E30">
         <v>4418.032840740989</v>
@@ -3747,37 +4137,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M30">
-        <v>505.7079510327607</v>
+        <v>470.5879906049629</v>
       </c>
       <c r="N30">
-        <v>260.2820489672392</v>
+        <v>295.402009395037</v>
       </c>
       <c r="O30">
-        <v>42.94653807959448</v>
+        <v>48.74133155018111</v>
       </c>
       <c r="P30">
-        <v>217.3355108876448</v>
+        <v>246.6606778448559</v>
       </c>
       <c r="Q30">
-        <v>611.0355108876447</v>
+        <v>640.3606778448558</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1148520266743117</v>
+        <v>0.1148197786970748</v>
       </c>
       <c r="T30">
         <v>1.345323953252519</v>
       </c>
       <c r="U30">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V30">
         <v>0.165</v>
       </c>
       <c r="W30">
-        <v>0.07334357491321596</v>
+        <v>0.06825007491321597</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +4175,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.514688464825774</v>
+        <v>1.62772959636153</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +4186,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1158381211799268</v>
+        <v>0.1019187952058792</v>
       </c>
       <c r="C31">
-        <v>10781.23637996632</v>
+        <v>13537.04803747404</v>
       </c>
       <c r="D31">
-        <v>11136.52731911231</v>
+        <v>13892.33897662003</v>
       </c>
       <c r="E31">
         <v>4623.653217952919</v>
@@ -3829,45 +4219,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M31">
-        <v>815.9555053020842</v>
+        <v>487.3947045551401</v>
       </c>
       <c r="N31">
-        <v>-49.96550530208435</v>
+        <v>278.5952954448598</v>
       </c>
       <c r="O31">
-        <v>-8.244308374843918</v>
+        <v>45.96822374840187</v>
       </c>
       <c r="P31">
-        <v>-41.72119692724043</v>
+        <v>232.6270716964579</v>
       </c>
       <c r="Q31">
-        <v>351.9788030727595</v>
+        <v>626.3270716964579</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1159185724394541</v>
+        <v>0.1156708077197839</v>
       </c>
       <c r="T31">
-        <v>1.366103206725465</v>
+        <v>1.361912092924607</v>
       </c>
       <c r="U31">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V31">
-        <v>0.1548961299712149</v>
+        <v>0.165</v>
       </c>
       <c r="W31">
-        <v>0.1156411543031529</v>
+        <v>0.06825007491321597</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>0.9387644240679692</v>
+        <v>1.571600989590443</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +4268,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1167484873465521</v>
+        <v>0.1020573287741641</v>
       </c>
       <c r="C32">
-        <v>10432.71911990054</v>
+        <v>13297.21780117015</v>
       </c>
       <c r="D32">
-        <v>10993.63043625846</v>
+        <v>13858.12911752807</v>
       </c>
       <c r="E32">
         <v>4829.273595164848</v>
@@ -3911,45 +4301,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M32">
-        <v>844.0919020366389</v>
+        <v>504.2014185053173</v>
       </c>
       <c r="N32">
-        <v>-78.10190203663899</v>
+        <v>261.7885814946826</v>
       </c>
       <c r="O32">
-        <v>-12.88681383604543</v>
+        <v>43.19511594662263</v>
       </c>
       <c r="P32">
-        <v>-65.21508820059356</v>
+        <v>218.59346554806</v>
       </c>
       <c r="Q32">
-        <v>328.4849117994064</v>
+        <v>612.2934655480599</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1169202663314463</v>
+        <v>0.1165461518574276</v>
       </c>
       <c r="T32">
-        <v>1.385618966821543</v>
+        <v>1.378974179444469</v>
       </c>
       <c r="U32">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V32">
-        <v>0.1497329256388411</v>
+        <v>0.165</v>
       </c>
       <c r="W32">
-        <v>0.1163476697151323</v>
+        <v>0.06825007491321597</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.9074722765990368</v>
+        <v>1.519214289937429</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4350,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1176588535131775</v>
+        <v>0.105871532342449</v>
       </c>
       <c r="C33">
-        <v>10087.82252677017</v>
+        <v>12211.68436916043</v>
       </c>
       <c r="D33">
-        <v>10854.35422034003</v>
+        <v>12978.21606273028</v>
       </c>
       <c r="E33">
         <v>5034.89397237678</v>
@@ -3993,45 +4383,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M33">
-        <v>872.2282987711936</v>
+        <v>611.5222225041865</v>
       </c>
       <c r="N33">
-        <v>-106.2382987711937</v>
+        <v>154.4677774958134</v>
       </c>
       <c r="O33">
-        <v>-17.52931929724697</v>
+        <v>25.48718328680921</v>
       </c>
       <c r="P33">
-        <v>-88.70897947394677</v>
+        <v>128.9805942090042</v>
       </c>
       <c r="Q33">
-        <v>304.9910205260531</v>
+        <v>522.6805942090041</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1179509948290035</v>
+        <v>0.117446868288916</v>
       </c>
       <c r="T33">
-        <v>1.405700401123305</v>
+        <v>1.39653081919679</v>
       </c>
       <c r="U33">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V33">
-        <v>0.1449028312633946</v>
+        <v>0.165</v>
       </c>
       <c r="W33">
-        <v>0.1170086034876291</v>
+        <v>0.08010707491321598</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>0.8781989773539065</v>
+        <v>1.252595526068157</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4432,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1185692196798028</v>
+        <v>0.1143788191986282</v>
       </c>
       <c r="C34">
-        <v>9746.410713477922</v>
+        <v>10396.10032944601</v>
       </c>
       <c r="D34">
-        <v>10718.56278425971</v>
+        <v>11368.25240022779</v>
       </c>
       <c r="E34">
         <v>5240.514349588711</v>
@@ -4075,37 +4465,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M34">
-        <v>900.3646955057483</v>
+        <v>819.4325150351323</v>
       </c>
       <c r="N34">
-        <v>-134.3746955057484</v>
+        <v>-53.44251503513237</v>
       </c>
       <c r="O34">
-        <v>-22.17182475844848</v>
+        <v>-8.818014980796843</v>
       </c>
       <c r="P34">
-        <v>-112.2028707472999</v>
+        <v>-44.62450005433553</v>
       </c>
       <c r="Q34">
-        <v>281.4971292527</v>
+        <v>349.0754999456644</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1190120388706065</v>
+        <v>0.118637920515938</v>
       </c>
       <c r="T34">
-        <v>1.426372465845706</v>
+        <v>1.419746644005794</v>
       </c>
       <c r="U34">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V34">
-        <v>0.1403746177864135</v>
+        <v>0.1542388759061888</v>
       </c>
       <c r="W34">
-        <v>0.1176282288993449</v>
+        <v>0.1053282288993449</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4503,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.850755259311597</v>
+        <v>0.9347810660981142</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4514,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1194795858464281</v>
+        <v>0.1151661853652536</v>
       </c>
       <c r="C35">
-        <v>9408.354508871715</v>
+        <v>10061.44046034816</v>
       </c>
       <c r="D35">
-        <v>10586.12695686543</v>
+        <v>11239.21290834187</v>
       </c>
       <c r="E35">
         <v>5446.134726800641</v>
@@ -4157,37 +4547,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M35">
-        <v>928.5010922403029</v>
+        <v>845.0397811299802</v>
       </c>
       <c r="N35">
-        <v>-162.511092240303</v>
+        <v>-79.04978112998026</v>
       </c>
       <c r="O35">
-        <v>-26.81433021965</v>
+        <v>-13.04321388644674</v>
       </c>
       <c r="P35">
-        <v>-135.696762020653</v>
+        <v>-66.00656724353351</v>
       </c>
       <c r="Q35">
-        <v>258.0032379793469</v>
+        <v>327.6934327564664</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1201047558686753</v>
+        <v>0.119725053657967</v>
       </c>
       <c r="T35">
-        <v>1.447661607126985</v>
+        <v>1.440936892423792</v>
       </c>
       <c r="U35">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V35">
-        <v>0.1361208414898555</v>
+        <v>0.1495649705756983</v>
       </c>
       <c r="W35">
-        <v>0.1182103012558052</v>
+        <v>0.1059103012558052</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4585,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8249747969082152</v>
+        <v>0.906454367125444</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4596,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1203899520130535</v>
+        <v>0.1159535515318789</v>
       </c>
       <c r="C36">
-        <v>9073.531047906028</v>
+        <v>9729.677132561497</v>
       </c>
       <c r="D36">
-        <v>10456.92387311167</v>
+        <v>11113.06995776714</v>
       </c>
       <c r="E36">
         <v>5651.755104012573</v>
@@ -4239,37 +4629,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M36">
-        <v>956.6374889748575</v>
+        <v>870.6470472248282</v>
       </c>
       <c r="N36">
-        <v>-190.6474889748577</v>
+        <v>-104.6570472248283</v>
       </c>
       <c r="O36">
-        <v>-31.45683568085152</v>
+        <v>-17.26841279209667</v>
       </c>
       <c r="P36">
-        <v>-159.1906532940061</v>
+        <v>-87.38863443273159</v>
       </c>
       <c r="Q36">
-        <v>234.5093467059938</v>
+        <v>306.3113655672684</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1212305855030492</v>
+        <v>0.1208451302285422</v>
       </c>
       <c r="T36">
-        <v>1.469595873901637</v>
+        <v>1.462769269581728</v>
       </c>
       <c r="U36">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V36">
-        <v>0.1321172873283892</v>
+        <v>0.1451660008528836</v>
       </c>
       <c r="W36">
-        <v>0.1187581340618854</v>
+        <v>0.1064581340618854</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4667,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8007108322932677</v>
+        <v>0.8797939445629308</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4678,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1519118391379683</v>
+        <v>0.1167409176985042</v>
       </c>
       <c r="C37">
-        <v>5761.546888105491</v>
+        <v>9400.713900817103</v>
       </c>
       <c r="D37">
-        <v>7350.560090523069</v>
+        <v>10989.72710323468</v>
       </c>
       <c r="E37">
         <v>5857.375481224504</v>
@@ -4321,45 +4711,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M37">
-        <v>1595.774836594665</v>
+        <v>896.2543133196759</v>
       </c>
       <c r="N37">
-        <v>-829.7848365946646</v>
+        <v>-130.264313319676</v>
       </c>
       <c r="O37">
-        <v>-136.9144980381197</v>
+        <v>-21.49361169774655</v>
       </c>
       <c r="P37">
-        <v>-692.870338556545</v>
+        <v>-108.7707016219295</v>
       </c>
       <c r="Q37">
-        <v>-299.1703385565451</v>
+        <v>284.9292983780704</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1237703190620029</v>
+        <v>0.1219996706935967</v>
       </c>
       <c r="T37">
-        <v>1.519076889250471</v>
+        <v>1.485273412190677</v>
       </c>
       <c r="U37">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V37">
-        <v>0.07920186927480879</v>
+        <v>0.1410184008285155</v>
       </c>
       <c r="W37">
-        <v>0.2041746621361897</v>
+        <v>0.1069746621361897</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.4800113289382351</v>
+        <v>0.8546569747182757</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4760,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1536712053045936</v>
+        <v>0.1175282838651296</v>
       </c>
       <c r="C38">
-        <v>5436.039774739125</v>
+        <v>9074.458554590685</v>
       </c>
       <c r="D38">
-        <v>7230.673354368632</v>
+        <v>10869.09213422019</v>
       </c>
       <c r="E38">
         <v>6062.995858436434</v>
@@ -4403,45 +4793,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M38">
-        <v>1641.368403354512</v>
+        <v>921.8615794145237</v>
       </c>
       <c r="N38">
-        <v>-875.378403354512</v>
+        <v>-155.8715794145238</v>
       </c>
       <c r="O38">
-        <v>-144.4374365534945</v>
+        <v>-25.71881060339643</v>
       </c>
       <c r="P38">
-        <v>-730.9409668010176</v>
+        <v>-130.1527688111274</v>
       </c>
       <c r="Q38">
-        <v>-337.2409668010176</v>
+        <v>263.5472311888726</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1249886052973467</v>
+        <v>0.1231902905481841</v>
       </c>
       <c r="T38">
-        <v>1.542812465645009</v>
+        <v>1.508480809256157</v>
       </c>
       <c r="U38">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V38">
-        <v>0.07700181735050857</v>
+        <v>0.1371012230277234</v>
       </c>
       <c r="W38">
-        <v>0.2046624942063659</v>
+        <v>0.1074624942063659</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.4666776809121731</v>
+        <v>0.8309165031983238</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4842,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.155430571471219</v>
+        <v>0.1183156500317549</v>
       </c>
       <c r="C39">
-        <v>5114.380578328523</v>
+        <v>8750.822888200884</v>
       </c>
       <c r="D39">
-        <v>7114.634535169962</v>
+        <v>10751.07684504232</v>
       </c>
       <c r="E39">
         <v>6268.616235648364</v>
@@ -4485,45 +4875,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M39">
-        <v>1686.961970114359</v>
+        <v>947.4688455093716</v>
       </c>
       <c r="N39">
-        <v>-920.9719701143596</v>
+        <v>-181.4788455093717</v>
       </c>
       <c r="O39">
-        <v>-151.9603750688693</v>
+        <v>-29.94400950904633</v>
       </c>
       <c r="P39">
-        <v>-769.0115950454903</v>
+        <v>-151.5348360003254</v>
       </c>
       <c r="Q39">
-        <v>-375.3115950454903</v>
+        <v>242.1651639996746</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1262455672861935</v>
+        <v>0.1244187078584728</v>
       </c>
       <c r="T39">
-        <v>1.56730155240128</v>
+        <v>1.532424949085619</v>
       </c>
       <c r="U39">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V39">
-        <v>0.07492068715184617</v>
+        <v>0.1333957845675147</v>
       </c>
       <c r="W39">
-        <v>0.2051239569754515</v>
+        <v>0.1079239569754515</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.4540647706172495</v>
+        <v>0.8084593004091799</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4924,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1571899376378443</v>
+        <v>0.1513614777443769</v>
       </c>
       <c r="C40">
-        <v>4796.38696925629</v>
+        <v>5179.59755037298</v>
       </c>
       <c r="D40">
-        <v>7002.26130330966</v>
+        <v>7385.471884426348</v>
       </c>
       <c r="E40">
         <v>6474.236612860295</v>
@@ -4567,37 +4957,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M40">
-        <v>1732.555536874207</v>
+        <v>1615.351921863406</v>
       </c>
       <c r="N40">
-        <v>-966.5655368742072</v>
+        <v>-849.3619218634066</v>
       </c>
       <c r="O40">
-        <v>-159.4833135842442</v>
+        <v>-140.1447171074621</v>
       </c>
       <c r="P40">
-        <v>-807.0822232899629</v>
+        <v>-709.2172047559445</v>
       </c>
       <c r="Q40">
-        <v>-413.382223289963</v>
+        <v>-315.5172047559446</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1275430764359708</v>
+        <v>0.1273358830594104</v>
       </c>
       <c r="T40">
-        <v>1.592580609698074</v>
+        <v>1.589286123487239</v>
       </c>
       <c r="U40">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V40">
-        <v>0.07294909012153443</v>
+        <v>0.07824199067049326</v>
       </c>
       <c r="W40">
-        <v>0.2055611322303748</v>
+        <v>0.1905611322303748</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4995,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4421156977062692</v>
+        <v>0.4741938828514742</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +5006,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1589493038044696</v>
+        <v>0.1529708439110022</v>
       </c>
       <c r="C41">
-        <v>4481.887958127161</v>
+        <v>4863.070809624069</v>
       </c>
       <c r="D41">
-        <v>6893.38266939246</v>
+        <v>7274.565520889369</v>
       </c>
       <c r="E41">
         <v>6679.856990072227</v>
@@ -4649,37 +5039,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M41">
-        <v>1778.149103634055</v>
+        <v>1657.861182965075</v>
       </c>
       <c r="N41">
-        <v>-1012.159103634055</v>
+        <v>-891.8711829650753</v>
       </c>
       <c r="O41">
-        <v>-167.006252099619</v>
+        <v>-147.1587451892374</v>
       </c>
       <c r="P41">
-        <v>-845.1528515344357</v>
+        <v>-744.7124377758378</v>
       </c>
       <c r="Q41">
-        <v>-451.4528515344358</v>
+        <v>-351.0124377758378</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1288831268693473</v>
+        <v>0.1286725368800564</v>
       </c>
       <c r="T41">
-        <v>1.618688488545584</v>
+        <v>1.615339994364079</v>
       </c>
       <c r="U41">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V41">
-        <v>0.07107860063123868</v>
+        <v>0.07623578578150624</v>
       </c>
       <c r="W41">
-        <v>0.2059758882414558</v>
+        <v>0.1909758882414558</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +5077,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4307793977650828</v>
+        <v>0.4620350653424621</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +5088,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.160708669971095</v>
+        <v>0.1545802100776275</v>
       </c>
       <c r="C42">
-        <v>4170.723027617538</v>
+        <v>4549.825712641292</v>
       </c>
       <c r="D42">
-        <v>6787.83811609477</v>
+        <v>7166.940801118523</v>
       </c>
       <c r="E42">
         <v>6885.477367284158</v>
@@ -4731,37 +5121,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M42">
-        <v>1823.742670393902</v>
+        <v>1700.370444066744</v>
       </c>
       <c r="N42">
-        <v>-1057.752670393902</v>
+        <v>-934.380444066744</v>
       </c>
       <c r="O42">
-        <v>-174.5291906149939</v>
+        <v>-154.1727732710128</v>
       </c>
       <c r="P42">
-        <v>-883.2234797789085</v>
+        <v>-780.2076707957312</v>
       </c>
       <c r="Q42">
-        <v>-489.5234797789086</v>
+        <v>-386.5076707957313</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1302678456505031</v>
+        <v>0.1300537458280574</v>
       </c>
       <c r="T42">
-        <v>1.645666630021344</v>
+        <v>1.64226232760348</v>
       </c>
       <c r="U42">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V42">
-        <v>0.06930163561545769</v>
+        <v>0.07432989113696857</v>
       </c>
       <c r="W42">
-        <v>0.2063699064519827</v>
+        <v>0.1913699064519827</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +5159,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4200099128209558</v>
+        <v>0.4504841887089005</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +5170,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1624680361377203</v>
+        <v>0.1561895762442529</v>
       </c>
       <c r="C43">
-        <v>3862.741342875846</v>
+        <v>4239.718730480306</v>
       </c>
       <c r="D43">
-        <v>6685.476808565007</v>
+        <v>7062.454196169467</v>
       </c>
       <c r="E43">
         <v>7091.097744496088</v>
@@ -4813,37 +5203,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M43">
-        <v>1869.33623715375</v>
+        <v>1742.879705168412</v>
       </c>
       <c r="N43">
-        <v>-1103.34623715375</v>
+        <v>-976.8897051684122</v>
       </c>
       <c r="O43">
-        <v>-182.0521291303687</v>
+        <v>-161.186801352788</v>
       </c>
       <c r="P43">
-        <v>-921.2941080233811</v>
+        <v>-815.7029038156242</v>
       </c>
       <c r="Q43">
-        <v>-527.5941080233812</v>
+        <v>-422.0029038156242</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1316995040513591</v>
+        <v>0.1314817754183635</v>
       </c>
       <c r="T43">
-        <v>1.673559284767468</v>
+        <v>1.670097282308624</v>
       </c>
       <c r="U43">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V43">
-        <v>0.06761135181995874</v>
+        <v>0.0725169669628962</v>
       </c>
       <c r="W43">
-        <v>0.2067447042619962</v>
+        <v>0.1917447042619962</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +5241,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4097657686058105</v>
+        <v>0.439496769472098</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +5252,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1642274023043457</v>
+        <v>0.1577989424108782</v>
       </c>
       <c r="C44">
-        <v>3557.801032304911</v>
+        <v>3932.614583939921</v>
       </c>
       <c r="D44">
-        <v>6586.156875206001</v>
+        <v>6960.970426841012</v>
       </c>
       <c r="E44">
         <v>7296.718121708018</v>
@@ -4895,37 +5285,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M44">
-        <v>1914.929803913597</v>
+        <v>1785.388966270081</v>
       </c>
       <c r="N44">
-        <v>-1148.939803913597</v>
+        <v>-1019.398966270081</v>
       </c>
       <c r="O44">
-        <v>-189.5750676457436</v>
+        <v>-168.2008294345633</v>
       </c>
       <c r="P44">
-        <v>-959.3647362678537</v>
+        <v>-851.1981368355173</v>
       </c>
       <c r="Q44">
-        <v>-565.6647362678538</v>
+        <v>-457.4981368355174</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1331805299832791</v>
+        <v>0.1329590474083352</v>
       </c>
       <c r="T44">
-        <v>1.702413755194493</v>
+        <v>1.698892063038083</v>
       </c>
       <c r="U44">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V44">
-        <v>0.06600155772900734</v>
+        <v>0.07079037251139866</v>
       </c>
       <c r="W44">
-        <v>0.2071016545572471</v>
+        <v>0.1921016545572471</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +5323,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4000094407818626</v>
+        <v>0.4290325606751434</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5334,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.165986768470971</v>
+        <v>0.1594083085775035</v>
       </c>
       <c r="C45">
-        <v>3255.768531514475</v>
+        <v>3628.385659236104</v>
       </c>
       <c r="D45">
-        <v>6489.744751627498</v>
+        <v>6862.361879349128</v>
       </c>
       <c r="E45">
         <v>7502.338498919949</v>
@@ -4977,37 +5367,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M45">
-        <v>1960.523370673445</v>
+        <v>1827.898227371749</v>
       </c>
       <c r="N45">
-        <v>-1194.533370673445</v>
+        <v>-1061.908227371749</v>
       </c>
       <c r="O45">
-        <v>-197.0980061611184</v>
+        <v>-175.2148575163387</v>
       </c>
       <c r="P45">
-        <v>-997.4353645123266</v>
+        <v>-886.6933698554108</v>
       </c>
       <c r="Q45">
-        <v>-603.7353645123267</v>
+        <v>-492.9933698554108</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1347135217373717</v>
+        <v>0.1344881535032183</v>
       </c>
       <c r="T45">
-        <v>1.732280663180362</v>
+        <v>1.728697186951032</v>
       </c>
       <c r="U45">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V45">
-        <v>0.06446663778182112</v>
+        <v>0.06914408477857543</v>
       </c>
       <c r="W45">
-        <v>0.207442002513184</v>
+        <v>0.192442002513184</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5405,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3907068956474007</v>
+        <v>0.4190550592640935</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5416,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1677461346375964</v>
+        <v>0.1610176747441289</v>
       </c>
       <c r="C46">
-        <v>2956.517984064021</v>
+        <v>3326.911472647354</v>
       </c>
       <c r="D46">
-        <v>6396.114581388975</v>
+        <v>6766.508069972309</v>
       </c>
       <c r="E46">
         <v>7707.958876131881</v>
@@ -5059,37 +5449,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M46">
-        <v>2006.116937433293</v>
+        <v>1870.407488473418</v>
       </c>
       <c r="N46">
-        <v>-1240.126937433293</v>
+        <v>-1104.417488473418</v>
       </c>
       <c r="O46">
-        <v>-204.6209446764933</v>
+        <v>-182.228885598114</v>
       </c>
       <c r="P46">
-        <v>-1035.5059927568</v>
+        <v>-922.188602875304</v>
       </c>
       <c r="Q46">
-        <v>-641.8059927567996</v>
+        <v>-528.4886028753041</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1363012631969676</v>
+        <v>0.1360718705300615</v>
       </c>
       <c r="T46">
-        <v>1.76321424645144</v>
+        <v>1.759566779575157</v>
       </c>
       <c r="U46">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V46">
-        <v>0.06300148692314336</v>
+        <v>0.06757262830633508</v>
       </c>
       <c r="W46">
-        <v>0.2077668801074874</v>
+        <v>0.1927668801074874</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5487,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3818271934735961</v>
+        <v>0.4095310806444551</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5498,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1695055008042217</v>
+        <v>0.1626270409107542</v>
       </c>
       <c r="C47">
-        <v>2659.930693342207</v>
+        <v>3028.078179409165</v>
       </c>
       <c r="D47">
-        <v>6305.14766787909</v>
+        <v>6673.295153946048</v>
       </c>
       <c r="E47">
         <v>7913.579253343811</v>
@@ -5141,37 +5531,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M47">
-        <v>2051.71050419314</v>
+        <v>1912.916749575086</v>
       </c>
       <c r="N47">
-        <v>-1285.72050419314</v>
+        <v>-1146.926749575086</v>
       </c>
       <c r="O47">
-        <v>-212.1438831918681</v>
+        <v>-189.2429136798893</v>
       </c>
       <c r="P47">
-        <v>-1073.576621001272</v>
+        <v>-957.6838358951971</v>
       </c>
       <c r="Q47">
-        <v>-679.8766210012722</v>
+        <v>-563.9838358951972</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1379467407096398</v>
+        <v>0.1377131772669717</v>
       </c>
       <c r="T47">
-        <v>1.795272687296011</v>
+        <v>1.79155890284016</v>
       </c>
       <c r="U47">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V47">
-        <v>0.06160145388040685</v>
+        <v>0.06607101434397208</v>
       </c>
       <c r="W47">
-        <v>0.2080773186975996</v>
+        <v>0.1930773186975995</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5569,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3733421447297384</v>
+        <v>0.4004303899634672</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5580,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.171264866970847</v>
+        <v>0.1642364070773796</v>
       </c>
       <c r="C48">
-        <v>2365.894620563318</v>
+        <v>2731.778122648622</v>
       </c>
       <c r="D48">
-        <v>6216.731972312134</v>
+        <v>6582.615474397438</v>
       </c>
       <c r="E48">
         <v>8119.199630555742</v>
@@ -5223,37 +5613,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M48">
-        <v>2097.304070952988</v>
+        <v>1955.426010676755</v>
       </c>
       <c r="N48">
-        <v>-1331.314070952988</v>
+        <v>-1189.436010676755</v>
       </c>
       <c r="O48">
-        <v>-219.666821707243</v>
+        <v>-196.2569417616646</v>
       </c>
       <c r="P48">
-        <v>-1111.647249245745</v>
+        <v>-993.1790689150907</v>
       </c>
       <c r="Q48">
-        <v>-717.947249245745</v>
+        <v>-599.4790689150908</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1396531618338924</v>
+        <v>0.139415273142286</v>
       </c>
       <c r="T48">
-        <v>1.828518477801493</v>
+        <v>1.824735919559422</v>
       </c>
       <c r="U48">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V48">
-        <v>0.06026229183952842</v>
+        <v>0.06463468794519008</v>
       </c>
       <c r="W48">
-        <v>0.2083742599577068</v>
+        <v>0.1933742599577068</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5651,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.365226011148657</v>
+        <v>0.3917253814860004</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5662,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1730242331374724</v>
+        <v>0.1658457732440049</v>
       </c>
       <c r="C49">
-        <v>2074.303924416587</v>
+        <v>2437.909418601672</v>
       </c>
       <c r="D49">
-        <v>6130.761653377333</v>
+        <v>6494.367147562418</v>
       </c>
       <c r="E49">
         <v>8324.820007767674</v>
@@ -5305,37 +5695,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M49">
-        <v>2142.897637712835</v>
+        <v>1997.935271778424</v>
       </c>
       <c r="N49">
-        <v>-1376.907637712835</v>
+        <v>-1231.945271778424</v>
       </c>
       <c r="O49">
-        <v>-227.1897602226178</v>
+        <v>-203.27096984344</v>
       </c>
       <c r="P49">
-        <v>-1149.717877490217</v>
+        <v>-1028.674301934984</v>
       </c>
       <c r="Q49">
-        <v>-756.0178774902175</v>
+        <v>-634.9743019349843</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1414239762081168</v>
+        <v>0.141181599050631</v>
       </c>
       <c r="T49">
-        <v>1.863018826439257</v>
+        <v>1.859164899173751</v>
       </c>
       <c r="U49">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V49">
-        <v>0.05898011541741081</v>
+        <v>0.06325948181869666</v>
       </c>
       <c r="W49">
-        <v>0.2086585654195117</v>
+        <v>0.1936585654195117</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5733,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3574552449540048</v>
+        <v>0.3833907989011918</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5744,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1747835993040977</v>
+        <v>0.1674551394106302</v>
       </c>
       <c r="C50">
-        <v>1785.058538391202</v>
+        <v>2146.375574753109</v>
       </c>
       <c r="D50">
-        <v>6047.13664456388</v>
+        <v>6408.453680925786</v>
       </c>
       <c r="E50">
         <v>8530.440384979604</v>
@@ -5387,37 +5777,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M50">
-        <v>2188.491204472683</v>
+        <v>2040.444532880092</v>
       </c>
       <c r="N50">
-        <v>-1422.501204472683</v>
+        <v>-1274.454532880092</v>
       </c>
       <c r="O50">
-        <v>-234.7126987379927</v>
+        <v>-210.2849979252152</v>
       </c>
       <c r="P50">
-        <v>-1187.78850573469</v>
+        <v>-1064.169534954877</v>
       </c>
       <c r="Q50">
-        <v>-794.0885057346901</v>
+        <v>-670.4695349548771</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1432628988275036</v>
+        <v>0.1430158605708354</v>
       </c>
       <c r="T50">
-        <v>1.898846111563089</v>
+        <v>1.894918070311708</v>
       </c>
       <c r="U50">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V50">
-        <v>0.05775136301288143</v>
+        <v>0.06194157594747383</v>
       </c>
       <c r="W50">
-        <v>0.208931024820408</v>
+        <v>0.1939310248204079</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5815,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3500082606841297</v>
+        <v>0.3754034905907505</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5826,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1765429654707231</v>
+        <v>0.1690645055772556</v>
       </c>
       <c r="C51">
-        <v>1498.063782228166</v>
+        <v>1857.085137890443</v>
       </c>
       <c r="D51">
-        <v>5965.762265612771</v>
+        <v>6324.783621275048</v>
       </c>
       <c r="E51">
         <v>8736.060762191533</v>
@@ -5469,37 +5859,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M51">
-        <v>2234.08477123253</v>
+        <v>2082.953793981761</v>
       </c>
       <c r="N51">
-        <v>-1468.09477123253</v>
+        <v>-1316.963793981761</v>
       </c>
       <c r="O51">
-        <v>-242.2356372533675</v>
+        <v>-217.2990260069905</v>
       </c>
       <c r="P51">
-        <v>-1225.859133979163</v>
+        <v>-1099.66476797477</v>
       </c>
       <c r="Q51">
-        <v>-832.1591339791627</v>
+        <v>-705.9647679747703</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1451739360594154</v>
+        <v>0.1449220539153616</v>
       </c>
       <c r="T51">
-        <v>1.936078388260404</v>
+        <v>1.93207332659233</v>
       </c>
       <c r="U51">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.05657276376772058</v>
+        <v>0.06067746215262743</v>
       </c>
       <c r="W51">
-        <v>0.209192363429431</v>
+        <v>0.1941923634294309</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5897,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3428652349558823</v>
+        <v>0.3677421948644086</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5908,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1783023316373484</v>
+        <v>0.1706738717438809</v>
       </c>
       <c r="C52">
-        <v>1213.230004326986</v>
+        <v>1569.951369372895</v>
       </c>
       <c r="D52">
-        <v>5886.548864923523</v>
+        <v>6243.270229969432</v>
       </c>
       <c r="E52">
         <v>8941.681139403465</v>
@@ -5551,37 +5941,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M52">
-        <v>2279.678337992378</v>
+        <v>2125.463055083429</v>
       </c>
       <c r="N52">
-        <v>-1513.688337992378</v>
+        <v>-1359.47305508343</v>
       </c>
       <c r="O52">
-        <v>-249.7585757687424</v>
+        <v>-224.3130540887659</v>
       </c>
       <c r="P52">
-        <v>-1263.929762223636</v>
+        <v>-1135.160000994664</v>
       </c>
       <c r="Q52">
-        <v>-870.2297622236357</v>
+        <v>-741.4600009946638</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1471614147806038</v>
+        <v>0.1469044949936689</v>
       </c>
       <c r="T52">
-        <v>1.974799956025612</v>
+        <v>1.970714793124176</v>
       </c>
       <c r="U52">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.05544130849236616</v>
+        <v>0.05946391290957487</v>
       </c>
       <c r="W52">
-        <v>0.209443248494093</v>
+        <v>0.194443248494093</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5979,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3360079302567646</v>
+        <v>0.3603873509671204</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5990,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1800616978039737</v>
+        <v>0.1722832379105063</v>
       </c>
       <c r="C53">
-        <v>930.4722522678039</v>
+        <v>1284.891945191584</v>
       </c>
       <c r="D53">
-        <v>5809.411490076272</v>
+        <v>6163.831183000053</v>
       </c>
       <c r="E53">
         <v>9147.301516615396</v>
@@ -5633,37 +6023,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M53">
-        <v>2325.271904752226</v>
+        <v>2167.972316185098</v>
       </c>
       <c r="N53">
-        <v>-1559.281904752226</v>
+        <v>-1401.982316185099</v>
       </c>
       <c r="O53">
-        <v>-257.2815142841172</v>
+        <v>-231.3270821705413</v>
       </c>
       <c r="P53">
-        <v>-1302.000390468108</v>
+        <v>-1170.655234014557</v>
       </c>
       <c r="Q53">
-        <v>-908.3003904681085</v>
+        <v>-776.9552340145575</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1492300150822487</v>
+        <v>0.148967852034356</v>
       </c>
       <c r="T53">
-        <v>2.015101995944502</v>
+        <v>2.010933462371608</v>
       </c>
       <c r="U53">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.05435422401212368</v>
+        <v>0.05829795383291653</v>
       </c>
       <c r="W53">
-        <v>0.2096842949287683</v>
+        <v>0.1946842949287683</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +6061,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3294195394674162</v>
+        <v>0.3533209323207062</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +6072,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1818210639705991</v>
+        <v>0.1738926040771316</v>
       </c>
       <c r="C54">
-        <v>649.7099689033548</v>
+        <v>1001.828678640491</v>
       </c>
       <c r="D54">
-        <v>5734.269583923753</v>
+        <v>6086.38829366089</v>
       </c>
       <c r="E54">
         <v>9352.921893827326</v>
@@ -5715,37 +6105,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M54">
-        <v>2370.865471512073</v>
+        <v>2210.481577286766</v>
       </c>
       <c r="N54">
-        <v>-1604.875471512073</v>
+        <v>-1444.491577286767</v>
       </c>
       <c r="O54">
-        <v>-264.8044527994921</v>
+        <v>-238.3411102523165</v>
       </c>
       <c r="P54">
-        <v>-1340.071018712581</v>
+        <v>-1206.15046703445</v>
       </c>
       <c r="Q54">
-        <v>-946.3710187125811</v>
+        <v>-812.4504670344503</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1513848070631289</v>
+        <v>0.1511171822850717</v>
       </c>
       <c r="T54">
-        <v>2.05708328752668</v>
+        <v>2.05282790950435</v>
       </c>
       <c r="U54">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.053308950473429</v>
+        <v>0.05717683933612969</v>
       </c>
       <c r="W54">
-        <v>0.2099160703467254</v>
+        <v>0.1949160703467253</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +6143,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3230845483238121</v>
+        <v>0.3465262990068465</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +6154,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1835804301372244</v>
+        <v>0.175501970243757</v>
       </c>
       <c r="C55">
-        <v>370.8667117351288</v>
+        <v>720.6872636343469</v>
       </c>
       <c r="D55">
-        <v>5661.04670396746</v>
+        <v>6010.867255866679</v>
       </c>
       <c r="E55">
         <v>9558.542271039258</v>
@@ -5797,37 +6187,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M55">
-        <v>2416.459038271921</v>
+        <v>2252.990838388435</v>
       </c>
       <c r="N55">
-        <v>-1650.469038271921</v>
+        <v>-1487.000838388436</v>
       </c>
       <c r="O55">
-        <v>-272.327391314867</v>
+        <v>-245.3551383340919</v>
       </c>
       <c r="P55">
-        <v>-1378.141646957054</v>
+        <v>-1241.645700054344</v>
       </c>
       <c r="Q55">
-        <v>-984.4416469570541</v>
+        <v>-847.9457000543438</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1536312923197912</v>
+        <v>0.1533579733975201</v>
       </c>
       <c r="T55">
-        <v>2.100851017048524</v>
+        <v>2.096505099068273</v>
       </c>
       <c r="U55">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.05230312121921336</v>
+        <v>0.05609803104676874</v>
       </c>
       <c r="W55">
-        <v>0.2101390995224953</v>
+        <v>0.1951390995224953</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +6225,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3169886134497778</v>
+        <v>0.3399880669501135</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +6236,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1853397963038498</v>
+        <v>0.1771113364103823</v>
       </c>
       <c r="C56">
-        <v>93.86989351880766</v>
+        <v>441.3970369020735</v>
       </c>
       <c r="D56">
-        <v>5589.67026296307</v>
+        <v>5937.197406346336</v>
       </c>
       <c r="E56">
         <v>9764.162648251189</v>
@@ -5879,37 +6269,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M56">
-        <v>2462.052605031768</v>
+        <v>2295.500099490104</v>
       </c>
       <c r="N56">
-        <v>-1696.062605031768</v>
+        <v>-1529.510099490104</v>
       </c>
       <c r="O56">
-        <v>-279.8503298302418</v>
+        <v>-252.3691664158673</v>
       </c>
       <c r="P56">
-        <v>-1416.212275201527</v>
+        <v>-1277.140933074237</v>
       </c>
       <c r="Q56">
-        <v>-1022.512275201527</v>
+        <v>-883.4409330742373</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1559754508484824</v>
+        <v>0.1556961902105096</v>
       </c>
       <c r="T56">
-        <v>2.146521691332187</v>
+        <v>2.142081296874105</v>
       </c>
       <c r="U56">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.05133454490033904</v>
+        <v>0.05505917861997672</v>
       </c>
       <c r="W56">
-        <v>0.210353868358422</v>
+        <v>0.195353868358422</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +6307,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3111184539414487</v>
+        <v>0.3336919916362225</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6318,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1870991624704751</v>
+        <v>0.1787207025770076</v>
       </c>
       <c r="C57">
-        <v>-181.3494577514703</v>
+        <v>163.8907574559616</v>
       </c>
       <c r="D57">
-        <v>5520.071288904723</v>
+        <v>5865.311504112154</v>
       </c>
       <c r="E57">
         <v>9969.783025463119</v>
@@ -5961,37 +6351,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M57">
-        <v>2507.646171791615</v>
+        <v>2338.009360591772</v>
       </c>
       <c r="N57">
-        <v>-1741.656171791616</v>
+        <v>-1572.019360591773</v>
       </c>
       <c r="O57">
-        <v>-287.3732683456166</v>
+        <v>-259.3831944976425</v>
       </c>
       <c r="P57">
-        <v>-1454.282903445999</v>
+        <v>-1312.63616609413</v>
       </c>
       <c r="Q57">
-        <v>-1060.582903445999</v>
+        <v>-918.93616609413</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1584237942006709</v>
+        <v>0.1581383277707432</v>
       </c>
       <c r="T57">
-        <v>2.194222173361792</v>
+        <v>2.189683103471307</v>
       </c>
       <c r="U57">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.0504011895385147</v>
+        <v>0.05405810264506807</v>
       </c>
       <c r="W57">
-        <v>0.2105608274184967</v>
+        <v>0.1955608274184967</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +6389,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3054617547788768</v>
+        <v>0.3276248645155639</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6400,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1888585286371005</v>
+        <v>0.180330068743633</v>
       </c>
       <c r="C58">
-        <v>-454.8569211482118</v>
+        <v>-111.8955981100353</v>
       </c>
       <c r="D58">
-        <v>5452.184202719912</v>
+        <v>5795.145525758088</v>
       </c>
       <c r="E58">
         <v>10175.40340267505</v>
@@ -6043,37 +6433,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M58">
-        <v>2553.239738551463</v>
+        <v>2380.518621693441</v>
       </c>
       <c r="N58">
-        <v>-1787.249738551463</v>
+        <v>-1614.528621693441</v>
       </c>
       <c r="O58">
-        <v>-294.8962068609915</v>
+        <v>-266.3972225794179</v>
       </c>
       <c r="P58">
-        <v>-1492.353531690472</v>
+        <v>-1348.131399114024</v>
       </c>
       <c r="Q58">
-        <v>-1098.653531690472</v>
+        <v>-954.4313991140237</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1609834258870498</v>
+        <v>0.1606914715837146</v>
       </c>
       <c r="T58">
-        <v>2.244090859120014</v>
+        <v>2.2394486285502</v>
       </c>
       <c r="U58">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.0495011682967555</v>
+        <v>0.05309277938354898</v>
       </c>
       <c r="W58">
-        <v>0.2107603950835688</v>
+        <v>0.1957603950835688</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6471,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3000070805863969</v>
+        <v>0.3217744205063574</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6482,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1906178948037258</v>
+        <v>0.1819394349102583</v>
       </c>
       <c r="C59">
-        <v>-726.7148889111941</v>
+        <v>-386.0230258027696</v>
       </c>
       <c r="D59">
-        <v>5385.94661216886</v>
+        <v>5726.638475277286</v>
       </c>
       <c r="E59">
         <v>10381.02377988698</v>
@@ -6125,37 +6515,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M59">
-        <v>2598.833305311311</v>
+        <v>2423.02788279511</v>
       </c>
       <c r="N59">
-        <v>-1832.843305311311</v>
+        <v>-1657.03788279511</v>
       </c>
       <c r="O59">
-        <v>-302.4191453763664</v>
+        <v>-273.4112506611932</v>
       </c>
       <c r="P59">
-        <v>-1530.424159934945</v>
+        <v>-1383.626632133917</v>
       </c>
       <c r="Q59">
-        <v>-1136.724159934945</v>
+        <v>-989.9266321339172</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1636621102100044</v>
+        <v>0.163363366271708</v>
       </c>
       <c r="T59">
-        <v>2.296279018634433</v>
+        <v>2.291528829214159</v>
       </c>
       <c r="U59">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.04863272674768961</v>
+        <v>0.05216132711366216</v>
       </c>
       <c r="W59">
-        <v>0.2109529603744279</v>
+        <v>0.1959529603744279</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6553,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2947437984708461</v>
+        <v>0.316129255234316</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6564,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1923772609703511</v>
+        <v>0.1835488010768836</v>
       </c>
       <c r="C60">
-        <v>-996.9827577051692</v>
+        <v>-658.5496710805965</v>
       </c>
       <c r="D60">
-        <v>5321.299120586813</v>
+        <v>5659.732207211386</v>
       </c>
       <c r="E60">
         <v>10586.64415709891</v>
@@ -6207,37 +6597,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M60">
-        <v>2644.426872071158</v>
+        <v>2465.537143896778</v>
       </c>
       <c r="N60">
-        <v>-1878.436872071158</v>
+        <v>-1699.547143896778</v>
       </c>
       <c r="O60">
-        <v>-309.9420838917411</v>
+        <v>-280.4252787429684</v>
       </c>
       <c r="P60">
-        <v>-1568.494788179417</v>
+        <v>-1419.12186515381</v>
       </c>
       <c r="Q60">
-        <v>-1174.794788179417</v>
+        <v>-1025.42186515381</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1664683509292902</v>
+        <v>0.166162494040082</v>
       </c>
       <c r="T60">
-        <v>2.350952328601919</v>
+        <v>2.346089039433543</v>
       </c>
       <c r="U60">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.04779423145893635</v>
+        <v>0.05126199388756454</v>
       </c>
       <c r="W60">
-        <v>0.2111388854828435</v>
+        <v>0.1961388854828435</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6635,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2896620088420384</v>
+        <v>0.3106787508337244</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6646,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1941366271369765</v>
+        <v>0.185158167243509</v>
       </c>
       <c r="C61">
-        <v>-1265.717106266931</v>
+        <v>-929.5309934499801</v>
       </c>
       <c r="D61">
-        <v>5258.185149236983</v>
+        <v>5594.371262053935</v>
       </c>
       <c r="E61">
         <v>10792.26453431084</v>
@@ -6289,37 +6679,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M61">
-        <v>2690.020438831006</v>
+        <v>2508.046404998447</v>
       </c>
       <c r="N61">
-        <v>-1924.030438831006</v>
+        <v>-1742.056404998447</v>
       </c>
       <c r="O61">
-        <v>-317.465022407116</v>
+        <v>-287.4393068247438</v>
       </c>
       <c r="P61">
-        <v>-1606.56541642389</v>
+        <v>-1454.617098173703</v>
       </c>
       <c r="Q61">
-        <v>-1212.86541642389</v>
+        <v>-1060.917098173703</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1694114814397607</v>
+        <v>0.1690981646264254</v>
       </c>
       <c r="T61">
-        <v>2.408292629299527</v>
+        <v>2.403310723322166</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.04698415973929335</v>
+        <v>0.05039314653353803</v>
       </c>
       <c r="W61">
-        <v>0.2113185080452112</v>
+        <v>0.1963185080452111</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6717,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2847524832684445</v>
+        <v>0.3054130092941698</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6728,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1958959933036018</v>
+        <v>0.1867675334101343</v>
       </c>
       <c r="C62">
-        <v>-1532.971860558515</v>
+        <v>-1199.019919787303</v>
       </c>
       <c r="D62">
-        <v>5196.550772157329</v>
+        <v>5530.502712928542</v>
       </c>
       <c r="E62">
         <v>10997.88491152277</v>
@@ -6371,37 +6761,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M62">
-        <v>2735.614005590853</v>
+        <v>2550.555666100115</v>
       </c>
       <c r="N62">
-        <v>-1969.624005590853</v>
+        <v>-1784.565666100115</v>
       </c>
       <c r="O62">
-        <v>-324.9879609224908</v>
+        <v>-294.453334906519</v>
       </c>
       <c r="P62">
-        <v>-1644.636044668363</v>
+        <v>-1490.112331193596</v>
       </c>
       <c r="Q62">
-        <v>-1250.936044668363</v>
+        <v>-1096.412331193596</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1725017684757547</v>
+        <v>0.1721806187420861</v>
       </c>
       <c r="T62">
-        <v>2.468499945032015</v>
+        <v>2.46339349140522</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.04620109041030514</v>
+        <v>0.04955326075797906</v>
       </c>
       <c r="W62">
-        <v>0.2114921431888332</v>
+        <v>0.1964921431888332</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6799,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2800066085473039</v>
+        <v>0.3003227924726003</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6810,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1976553594702271</v>
+        <v>0.1883768995767597</v>
       </c>
       <c r="C63">
-        <v>-1798.798447439831</v>
+        <v>-1467.066987276819</v>
       </c>
       <c r="D63">
-        <v>5136.344562487945</v>
+        <v>5468.076022650956</v>
       </c>
       <c r="E63">
         <v>11203.5052887347</v>
@@ -6453,37 +6843,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M63">
-        <v>2781.207572350701</v>
+        <v>2593.064927201784</v>
       </c>
       <c r="N63">
-        <v>-2015.217572350701</v>
+        <v>-1827.074927201784</v>
       </c>
       <c r="O63">
-        <v>-332.5108994378656</v>
+        <v>-301.4673629882944</v>
       </c>
       <c r="P63">
-        <v>-1682.706672912835</v>
+        <v>-1525.60756421349</v>
       </c>
       <c r="Q63">
-        <v>-1289.006672912835</v>
+        <v>-1131.90756421349</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1757505317700048</v>
+        <v>0.1754211474277806</v>
       </c>
       <c r="T63">
-        <v>2.531794815417451</v>
+        <v>2.526557427082277</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.04544369548554603</v>
+        <v>0.04874091222096301</v>
       </c>
       <c r="W63">
-        <v>0.2116600853769267</v>
+        <v>0.1966600853769266</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6881,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2754163362760366</v>
+        <v>0.2953994680058364</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6892,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1994147256368525</v>
+        <v>0.189986265743385</v>
       </c>
       <c r="C64">
-        <v>-2063.245937781101</v>
+        <v>-1733.720476775963</v>
       </c>
       <c r="D64">
-        <v>5077.517449358606</v>
+        <v>5407.042910363745</v>
       </c>
       <c r="E64">
         <v>11409.12566594663</v>
@@ -6535,37 +6925,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M64">
-        <v>2826.801139110548</v>
+        <v>2635.574188303453</v>
       </c>
       <c r="N64">
-        <v>-2060.811139110549</v>
+        <v>-1869.584188303453</v>
       </c>
       <c r="O64">
-        <v>-340.0338379532405</v>
+        <v>-308.4813910700697</v>
       </c>
       <c r="P64">
-        <v>-1720.777301157308</v>
+        <v>-1561.102797233383</v>
       </c>
       <c r="Q64">
-        <v>-1327.077301157308</v>
+        <v>-1167.402797233383</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1791702826060576</v>
+        <v>0.1788322302548274</v>
       </c>
       <c r="T64">
-        <v>2.598420994770542</v>
+        <v>2.593045780426547</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.044710732655134</v>
+        <v>0.04795476847546361</v>
       </c>
       <c r="W64">
-        <v>0.2118226100750816</v>
+        <v>0.1968226100750816</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6963,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2709741373038423</v>
+        <v>0.2906349604573552</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6974,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2011740918034778</v>
+        <v>0.1915956319100104</v>
       </c>
       <c r="C65">
-        <v>-2326.361179852165</v>
+        <v>-1999.026537347747</v>
       </c>
       <c r="D65">
-        <v>5020.022584499473</v>
+        <v>5347.35722700389</v>
       </c>
       <c r="E65">
         <v>11614.74604315856</v>
@@ -6617,37 +7007,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M65">
-        <v>2872.394705870396</v>
+        <v>2678.083449405121</v>
       </c>
       <c r="N65">
-        <v>-2106.404705870396</v>
+        <v>-1912.093449405121</v>
       </c>
       <c r="O65">
-        <v>-347.5567764686153</v>
+        <v>-315.495419151845</v>
       </c>
       <c r="P65">
-        <v>-1758.847929401781</v>
+        <v>-1596.598030253276</v>
       </c>
       <c r="Q65">
-        <v>-1365.147929401781</v>
+        <v>-1202.898030253276</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1827748848386537</v>
+        <v>0.1824276959373903</v>
       </c>
       <c r="T65">
-        <v>2.6686485892238</v>
+        <v>2.663128098816454</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.0440010384860049</v>
+        <v>0.04719358167426578</v>
       </c>
       <c r="W65">
-        <v>0.2119799752590094</v>
+        <v>0.1969799752590094</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +7045,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2666729605212418</v>
+        <v>0.2860217071167622</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +7056,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2029334579701032</v>
+        <v>0.1932049980766357</v>
       </c>
       <c r="C66">
-        <v>-2588.188923750724</v>
+        <v>-2263.029302635321</v>
       </c>
       <c r="D66">
-        <v>4963.815217812845</v>
+        <v>5288.974838928248</v>
       </c>
       <c r="E66">
         <v>11820.3664203705</v>
@@ -6699,37 +7089,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M66">
-        <v>2917.988272630244</v>
+        <v>2720.59271050679</v>
       </c>
       <c r="N66">
-        <v>-2151.998272630244</v>
+        <v>-1954.60271050679</v>
       </c>
       <c r="O66">
-        <v>-355.0797149839902</v>
+        <v>-322.5094472336204</v>
       </c>
       <c r="P66">
-        <v>-1796.918557646253</v>
+        <v>-1632.09326327317</v>
       </c>
       <c r="Q66">
-        <v>-1403.218557646253</v>
+        <v>-1238.39326327317</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1865797427508386</v>
+        <v>0.186222909713429</v>
       </c>
       <c r="T66">
-        <v>2.74277771670224</v>
+        <v>2.737103879339133</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.04331352225966106</v>
+        <v>0.04645618196060537</v>
       </c>
       <c r="W66">
-        <v>0.2121324227809395</v>
+        <v>0.1971324227809395</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +7127,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2625061955130973</v>
+        <v>0.2815526179430627</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +7138,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2046928241367285</v>
+        <v>0.194814364243261</v>
       </c>
       <c r="C67">
-        <v>-2848.771937564072</v>
+        <v>-2525.770999695376</v>
       </c>
       <c r="D67">
-        <v>4908.852581211428</v>
+        <v>5231.853519080125</v>
       </c>
       <c r="E67">
         <v>12025.98679758243</v>
@@ -6781,37 +7171,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M67">
-        <v>2963.581839390091</v>
+        <v>2763.101971608458</v>
       </c>
       <c r="N67">
-        <v>-2197.591839390092</v>
+        <v>-1997.111971608459</v>
       </c>
       <c r="O67">
-        <v>-362.6026534993651</v>
+        <v>-329.5234753153957</v>
       </c>
       <c r="P67">
-        <v>-1834.989185890726</v>
+        <v>-1667.588496293063</v>
       </c>
       <c r="Q67">
-        <v>-1441.289185890726</v>
+        <v>-1273.888496293063</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1906020211151483</v>
+        <v>0.1902349928480984</v>
       </c>
       <c r="T67">
-        <v>2.821142794322304</v>
+        <v>2.815306847320252</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.04264716037874319</v>
+        <v>0.04574147146890375</v>
       </c>
       <c r="W67">
-        <v>0.2122801796098871</v>
+        <v>0.1972801796098871</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +7209,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2584676386590496</v>
+        <v>0.2772210392054772</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +7220,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2064521903033539</v>
+        <v>0.1964237304098864</v>
       </c>
       <c r="C68">
-        <v>-3108.151115898023</v>
+        <v>-2787.292050854461</v>
       </c>
       <c r="D68">
-        <v>4855.093780089408</v>
+        <v>5175.95284513297</v>
       </c>
       <c r="E68">
         <v>12231.60717479436</v>
@@ -6863,37 +7253,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M68">
-        <v>3009.175406149939</v>
+        <v>2805.611232710127</v>
       </c>
       <c r="N68">
-        <v>-2243.185406149939</v>
+        <v>-2039.621232710127</v>
       </c>
       <c r="O68">
-        <v>-370.1255920147399</v>
+        <v>-336.537503397171</v>
       </c>
       <c r="P68">
-        <v>-1873.059814135199</v>
+        <v>-1703.083729312956</v>
       </c>
       <c r="Q68">
-        <v>-1479.359814135199</v>
+        <v>-1309.383729312956</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1948609040891232</v>
+        <v>0.1944830808730424</v>
       </c>
       <c r="T68">
-        <v>2.904117582390606</v>
+        <v>2.898109989888495</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.04200099128209557</v>
+        <v>0.04504841887089006</v>
       </c>
       <c r="W68">
-        <v>0.2124234589591696</v>
+        <v>0.1974234589591696</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +7291,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2545514623157307</v>
+        <v>0.2730207204296367</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7302,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2082115564699792</v>
+        <v>0.1980330965765117</v>
       </c>
       <c r="C69">
-        <v>-3366.365581351829</v>
+        <v>-3047.631169104538</v>
       </c>
       <c r="D69">
-        <v>4802.499691847533</v>
+        <v>5121.234104094825</v>
       </c>
       <c r="E69">
         <v>12437.22755200629</v>
@@ -6945,37 +7335,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M69">
-        <v>3054.768972909786</v>
+        <v>2848.120493811796</v>
       </c>
       <c r="N69">
-        <v>-2288.778972909787</v>
+        <v>-2082.130493811796</v>
       </c>
       <c r="O69">
-        <v>-377.6485305301148</v>
+        <v>-343.5515314789463</v>
       </c>
       <c r="P69">
-        <v>-1911.130442379672</v>
+        <v>-1738.57896233285</v>
       </c>
       <c r="Q69">
-        <v>-1517.430442379672</v>
+        <v>-1344.87896233285</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.199377901182733</v>
+        <v>0.1989886287782862</v>
       </c>
       <c r="T69">
-        <v>2.992121145493353</v>
+        <v>2.9859315047336</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.04137411081519862</v>
+        <v>0.04437605441013049</v>
       </c>
       <c r="W69">
-        <v>0.2125624613129512</v>
+        <v>0.1975624613129512</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +7373,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2507521867587795</v>
+        <v>0.2689457843038211</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7384,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2099709226366046</v>
+        <v>0.1996424627431371</v>
       </c>
       <c r="C70">
-        <v>-3623.452779468264</v>
+        <v>-3306.825447510832</v>
       </c>
       <c r="D70">
-        <v>4751.032870943029</v>
+        <v>5067.660202900462</v>
       </c>
       <c r="E70">
         <v>12642.84792921822</v>
@@ -7027,37 +7417,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M70">
-        <v>3100.362539669634</v>
+        <v>2890.629754913464</v>
       </c>
       <c r="N70">
-        <v>-2334.372539669634</v>
+        <v>-2124.639754913464</v>
       </c>
       <c r="O70">
-        <v>-385.1714690454896</v>
+        <v>-350.5655595607216</v>
       </c>
       <c r="P70">
-        <v>-1949.201070624144</v>
+        <v>-1774.074195352743</v>
       </c>
       <c r="Q70">
-        <v>-1555.501070624145</v>
+        <v>-1380.374195352743</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2041772105946934</v>
+        <v>0.2037757734276076</v>
       </c>
       <c r="T70">
-        <v>3.08562493129002</v>
+        <v>3.079241864256526</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.04076566800909277</v>
+        <v>0.0437234653746874</v>
       </c>
       <c r="W70">
-        <v>0.2126973753622098</v>
+        <v>0.1976973753622098</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7455,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2470646546005622</v>
+        <v>0.2649906992405296</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7466,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2117302888032299</v>
+        <v>0.2012518289097624</v>
       </c>
       <c r="C71">
-        <v>-3879.448567643134</v>
+        <v>-3564.910443065952</v>
       </c>
       <c r="D71">
-        <v>4700.65745998009</v>
+        <v>5015.195584557272</v>
       </c>
       <c r="E71">
         <v>12848.46830643015</v>
@@ -7109,37 +7499,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M71">
-        <v>3145.956106429481</v>
+        <v>2933.139016015133</v>
       </c>
       <c r="N71">
-        <v>-2379.966106429481</v>
+        <v>-2167.149016015133</v>
       </c>
       <c r="O71">
-        <v>-392.6944075608645</v>
+        <v>-357.579587642497</v>
       </c>
       <c r="P71">
-        <v>-1987.271698868617</v>
+        <v>-1809.569428372636</v>
       </c>
       <c r="Q71">
-        <v>-1593.571698868617</v>
+        <v>-1415.869428372636</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2092861528719416</v>
+        <v>0.2088717661188208</v>
       </c>
       <c r="T71">
-        <v>3.18516121939615</v>
+        <v>3.178572246974478</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.04017486122635229</v>
+        <v>0.04308979196346005</v>
       </c>
       <c r="W71">
-        <v>0.2128283788593159</v>
+        <v>0.1978283788593159</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7537,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.243484007432438</v>
+        <v>0.2611502543240003</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7548,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2134896549698552</v>
+        <v>0.2028611950763878</v>
       </c>
       <c r="C72">
-        <v>-4134.387298437883</v>
+        <v>-3821.920255388635</v>
       </c>
       <c r="D72">
-        <v>4651.339106397271</v>
+        <v>4963.806149446518</v>
       </c>
       <c r="E72">
         <v>13054.08868364208</v>
@@ -7191,37 +7581,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M72">
-        <v>3191.549673189329</v>
+        <v>2975.648277116802</v>
       </c>
       <c r="N72">
-        <v>-2425.559673189329</v>
+        <v>-2209.658277116802</v>
       </c>
       <c r="O72">
-        <v>-400.2173460762393</v>
+        <v>-364.5936157242723</v>
       </c>
       <c r="P72">
-        <v>-2025.34232711309</v>
+        <v>-1845.06466139253</v>
       </c>
       <c r="Q72">
-        <v>-1631.64232711309</v>
+        <v>-1451.36466139253</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2147356913010063</v>
+        <v>0.2143074916561148</v>
       </c>
       <c r="T72">
-        <v>3.291333260042688</v>
+        <v>3.284524655206961</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.0396009346374044</v>
+        <v>0.04247422350683919</v>
       </c>
       <c r="W72">
-        <v>0.2129556393993619</v>
+        <v>0.1979556393993619</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7619,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2400056644691175</v>
+        <v>0.257419536405086</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7630,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2152490211364805</v>
+        <v>0.2044705612430131</v>
       </c>
       <c r="C73">
-        <v>-4388.301897702031</v>
+        <v>-4077.887600633096</v>
       </c>
       <c r="D73">
-        <v>4603.044884345051</v>
+        <v>4913.459181413986</v>
       </c>
       <c r="E73">
         <v>13259.70906085401</v>
@@ -7273,37 +7663,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M73">
-        <v>3237.143239949176</v>
+        <v>3018.15753821847</v>
       </c>
       <c r="N73">
-        <v>-2471.153239949176</v>
+        <v>-2252.16753821847</v>
       </c>
       <c r="O73">
-        <v>-407.7402845916141</v>
+        <v>-371.6076438060475</v>
       </c>
       <c r="P73">
-        <v>-2063.412955357562</v>
+        <v>-1880.559894412422</v>
       </c>
       <c r="Q73">
-        <v>-1669.712955357562</v>
+        <v>-1486.859894412422</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2205610599665582</v>
+        <v>0.2201180948166704</v>
       </c>
       <c r="T73">
-        <v>3.404827510388986</v>
+        <v>3.397784126076166</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.03904317499462406</v>
+        <v>0.04187599500674287</v>
       </c>
       <c r="W73">
-        <v>0.2130793151354629</v>
+        <v>0.1980793151354629</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7701,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2366253029977216</v>
+        <v>0.2537939091317749</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7712,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2170083873031059</v>
+        <v>0.2060799274096384</v>
       </c>
       <c r="C74">
-        <v>-4641.223937878856</v>
+        <v>-4332.843880945686</v>
       </c>
       <c r="D74">
-        <v>4555.743221380158</v>
+        <v>4864.123278313329</v>
       </c>
       <c r="E74">
         <v>13465.32943806594</v>
@@ -7355,37 +7745,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M74">
-        <v>3282.736806709024</v>
+        <v>3060.666799320138</v>
       </c>
       <c r="N74">
-        <v>-2516.746806709024</v>
+        <v>-2294.676799320138</v>
       </c>
       <c r="O74">
-        <v>-415.263223106989</v>
+        <v>-378.6216718878229</v>
       </c>
       <c r="P74">
-        <v>-2101.483583602035</v>
+        <v>-1916.055127432315</v>
       </c>
       <c r="Q74">
-        <v>-1707.783583602035</v>
+        <v>-1522.355127432315</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2268025263939353</v>
+        <v>0.2263437410601229</v>
       </c>
       <c r="T74">
-        <v>3.526428492902879</v>
+        <v>3.519133559150314</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.03850090867525428</v>
+        <v>0.04129438396498256</v>
       </c>
       <c r="W74">
-        <v>0.21319955543445</v>
+        <v>0.19819955543445</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7783,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2333388404560865</v>
+        <v>0.2502689937271669</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7794,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2187677534697312</v>
+        <v>0.2076892935762638</v>
       </c>
       <c r="C75">
-        <v>-4893.183706837191</v>
+        <v>-4586.819249778631</v>
       </c>
       <c r="D75">
-        <v>4509.403829633755</v>
+        <v>4815.768286692314</v>
       </c>
       <c r="E75">
         <v>13670.94981527787</v>
@@ -7437,37 +7827,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M75">
-        <v>3328.330373468872</v>
+        <v>3103.176060421807</v>
       </c>
       <c r="N75">
-        <v>-2562.340373468872</v>
+        <v>-2337.186060421807</v>
       </c>
       <c r="O75">
-        <v>-422.7861616223639</v>
+        <v>-385.6356999695982</v>
       </c>
       <c r="P75">
-        <v>-2139.554211846508</v>
+        <v>-1951.550360452209</v>
       </c>
       <c r="Q75">
-        <v>-1745.854211846508</v>
+        <v>-1557.850360452209</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2335063236677847</v>
+        <v>0.233030546284572</v>
       </c>
       <c r="T75">
-        <v>3.657036955602985</v>
+        <v>3.649471839118845</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.03797349896737408</v>
+        <v>0.04072870747231155</v>
       </c>
       <c r="W75">
-        <v>0.2133165014786703</v>
+        <v>0.1983165014786703</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7865,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2301424179840853</v>
+        <v>0.2468406513473427</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7876,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2205271196363566</v>
+        <v>0.2092986597428891</v>
       </c>
       <c r="C76">
-        <v>-5144.210272544757</v>
+        <v>-4839.842673346402</v>
       </c>
       <c r="D76">
-        <v>4463.997641138118</v>
+        <v>4768.365240336474</v>
       </c>
       <c r="E76">
         <v>13876.5701924898</v>
@@ -7519,37 +7909,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M76">
-        <v>3373.923940228719</v>
+        <v>3145.685321523476</v>
       </c>
       <c r="N76">
-        <v>-2607.933940228719</v>
+        <v>-2379.695321523476</v>
       </c>
       <c r="O76">
-        <v>-430.3091001377387</v>
+        <v>-392.6497280513735</v>
       </c>
       <c r="P76">
-        <v>-2177.62484009098</v>
+        <v>-1987.045593472102</v>
       </c>
       <c r="Q76">
-        <v>-1783.924840090981</v>
+        <v>-1593.345593472102</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2407257976550072</v>
+        <v>0.2402317211416709</v>
       </c>
       <c r="T76">
-        <v>3.797692223126177</v>
+        <v>3.789836140623415</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.03746034357592309</v>
+        <v>0.04017831953349654</v>
       </c>
       <c r="W76">
-        <v>0.2134302868189928</v>
+        <v>0.1984302868189928</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7947,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2270323853086247</v>
+        <v>0.2435049668696759</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7958,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2222864858029819</v>
+        <v>0.2109080259095145</v>
       </c>
       <c r="C77">
-        <v>-5394.331543873202</v>
+        <v>-5091.941988487826</v>
       </c>
       <c r="D77">
-        <v>4419.496747021605</v>
+        <v>4721.88630240698</v>
       </c>
       <c r="E77">
         <v>14082.19056970173</v>
@@ -7601,37 +7991,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M77">
-        <v>3419.517506988566</v>
+        <v>3188.194582625144</v>
       </c>
       <c r="N77">
-        <v>-2653.527506988567</v>
+        <v>-2422.204582625144</v>
       </c>
       <c r="O77">
-        <v>-437.8320386531135</v>
+        <v>-399.6637561331488</v>
       </c>
       <c r="P77">
-        <v>-2215.695468335453</v>
+        <v>-2022.540826491995</v>
       </c>
       <c r="Q77">
-        <v>-1821.995468335453</v>
+        <v>-1628.840826491995</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2485228295612075</v>
+        <v>0.2480089899873377</v>
       </c>
       <c r="T77">
-        <v>3.949599912051224</v>
+        <v>3.941429586248352</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.03696087232824411</v>
+        <v>0.03964260860638325</v>
       </c>
       <c r="W77">
-        <v>0.2135410378835734</v>
+        <v>0.1985410378835734</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +8029,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.224005286837843</v>
+        <v>0.2402582339780802</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +8040,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2240458519696072</v>
+        <v>0.2125173920761398</v>
       </c>
       <c r="C78">
-        <v>-5643.574327802042</v>
+        <v>-5343.143957176881</v>
       </c>
       <c r="D78">
-        <v>4375.874340304696</v>
+        <v>4676.304710929859</v>
       </c>
       <c r="E78">
         <v>14287.81094691367</v>
@@ -7683,37 +8073,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M78">
-        <v>3465.111073748414</v>
+        <v>3230.703843726813</v>
       </c>
       <c r="N78">
-        <v>-2699.121073748414</v>
+        <v>-2464.713843726813</v>
       </c>
       <c r="O78">
-        <v>-445.3549771684884</v>
+        <v>-406.6777842149242</v>
       </c>
       <c r="P78">
-        <v>-2253.766096579926</v>
+        <v>-2058.036059511889</v>
       </c>
       <c r="Q78">
-        <v>-1860.066096579926</v>
+        <v>-1664.336059511889</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2569696141262579</v>
+        <v>0.2564343645701435</v>
       </c>
       <c r="T78">
-        <v>4.11416657505336</v>
+        <v>4.1056558190087</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.03647454506076721</v>
+        <v>0.03912099533524663</v>
       </c>
       <c r="W78">
-        <v>0.2136488744464544</v>
+        <v>0.1986488744464544</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +8111,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2210578488531346</v>
+        <v>0.2370969414257371</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +8122,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2258052181362326</v>
+        <v>0.2141267582427652</v>
       </c>
       <c r="C79">
-        <v>-5891.964383268018</v>
+        <v>-5593.474317906386</v>
       </c>
       <c r="D79">
-        <v>4333.104662050649</v>
+        <v>4631.594727412282</v>
       </c>
       <c r="E79">
         <v>14493.43132412559</v>
@@ -7765,37 +8155,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M79">
-        <v>3510.704640508261</v>
+        <v>3273.213104828481</v>
       </c>
       <c r="N79">
-        <v>-2744.714640508262</v>
+        <v>-2507.223104828482</v>
       </c>
       <c r="O79">
-        <v>-452.8779156838632</v>
+        <v>-413.6918122966995</v>
       </c>
       <c r="P79">
-        <v>-2291.836724824399</v>
+        <v>-2093.531292531782</v>
       </c>
       <c r="Q79">
-        <v>-1898.136724824399</v>
+        <v>-1699.831292531782</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2661509016969647</v>
+        <v>0.2655923804210193</v>
       </c>
       <c r="T79">
-        <v>4.293043382664375</v>
+        <v>4.28416259374821</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.03600084967036764</v>
+        <v>0.0386129304607629</v>
       </c>
       <c r="W79">
-        <v>0.2137539100596503</v>
+        <v>0.1987539100596503</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +8193,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2181869676991978</v>
+        <v>0.2340177603682599</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +8204,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2275645843028579</v>
+        <v>0.2157361244093905</v>
       </c>
       <c r="C80">
-        <v>-6139.526471887031</v>
+        <v>-5842.957834152021</v>
       </c>
       <c r="D80">
-        <v>4291.162950643569</v>
+        <v>4587.73158837858</v>
       </c>
       <c r="E80">
         <v>14699.05170133753</v>
@@ -7847,37 +8237,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M80">
-        <v>3556.298207268109</v>
+        <v>3315.72236593015</v>
       </c>
       <c r="N80">
-        <v>-2790.30820726811</v>
+        <v>-2549.732365930151</v>
       </c>
       <c r="O80">
-        <v>-460.4008541992381</v>
+        <v>-420.7058403784749</v>
       </c>
       <c r="P80">
-        <v>-2329.907353068872</v>
+        <v>-2129.026525551676</v>
       </c>
       <c r="Q80">
-        <v>-1936.207353068872</v>
+        <v>-1735.326525551676</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2761668517740995</v>
+        <v>0.2755829431674293</v>
       </c>
       <c r="T80">
-        <v>4.488181718240028</v>
+        <v>4.478897257100401</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.03553930031561934</v>
+        <v>0.03811789289075312</v>
       </c>
       <c r="W80">
-        <v>0.2138562524519949</v>
+        <v>0.198856252451995</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +8275,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2153896988825413</v>
+        <v>0.2310175326712309</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8286,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2293239504694833</v>
+        <v>0.2173454905760158</v>
       </c>
       <c r="C81">
-        <v>-6386.284405758599</v>
+        <v>-6091.618340108247</v>
       </c>
       <c r="D81">
-        <v>4250.025393983933</v>
+        <v>4544.691459634285</v>
       </c>
       <c r="E81">
         <v>14904.67207854946</v>
@@ -7929,37 +8319,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M81">
-        <v>3601.891774027957</v>
+        <v>3358.231627031819</v>
       </c>
       <c r="N81">
-        <v>-2835.901774027957</v>
+        <v>-2592.241627031819</v>
       </c>
       <c r="O81">
-        <v>-467.923792714613</v>
+        <v>-427.7198684602502</v>
       </c>
       <c r="P81">
-        <v>-2367.977981313345</v>
+        <v>-2164.521758571569</v>
       </c>
       <c r="Q81">
-        <v>-1974.277981313345</v>
+        <v>-1770.821758571569</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2871367018585804</v>
+        <v>0.286524988080164</v>
       </c>
       <c r="T81">
-        <v>4.70190465720384</v>
+        <v>4.692178078867086</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.03508943575466212</v>
+        <v>0.03763538791745245</v>
       </c>
       <c r="W81">
-        <v>0.213956003897698</v>
+        <v>0.198956003897698</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +8357,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2126632469979522</v>
+        <v>0.2280932601057724</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8368,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2310833166361086</v>
+        <v>0.2189548567426412</v>
       </c>
       <c r="C82">
-        <v>-6632.261092546742</v>
+        <v>-6339.478783873768</v>
       </c>
       <c r="D82">
-        <v>4209.669084407722</v>
+        <v>4502.451393080693</v>
       </c>
       <c r="E82">
         <v>15110.29245576139</v>
@@ -8011,37 +8401,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M82">
-        <v>3647.485340787805</v>
+        <v>3400.740888133488</v>
       </c>
       <c r="N82">
-        <v>-2881.495340787805</v>
+        <v>-2634.750888133488</v>
       </c>
       <c r="O82">
-        <v>-475.4467312299878</v>
+        <v>-434.7338965420255</v>
       </c>
       <c r="P82">
-        <v>-2406.048609557817</v>
+        <v>-2200.016991591463</v>
       </c>
       <c r="Q82">
-        <v>-2012.348609557817</v>
+        <v>-1806.316991591463</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2992035369515095</v>
+        <v>0.2985612374841722</v>
       </c>
       <c r="T82">
-        <v>4.936999890064032</v>
+        <v>4.926786982810441</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.03465081780772884</v>
+        <v>0.03716494556848429</v>
       </c>
       <c r="W82">
-        <v>0.2140532615572584</v>
+        <v>0.1990532615572584</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8439,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2100049564104778</v>
+        <v>0.2252420943544502</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8450,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.232842682802734</v>
+        <v>0.2205642229092665</v>
       </c>
       <c r="C83">
-        <v>-6877.478578016613</v>
+        <v>-6586.561268250853</v>
       </c>
       <c r="D83">
-        <v>4170.071976149778</v>
+        <v>4460.98928591554</v>
       </c>
       <c r="E83">
         <v>15315.91283297332</v>
@@ -8093,37 +8483,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M83">
-        <v>3693.078907547652</v>
+        <v>3443.250149235156</v>
       </c>
       <c r="N83">
-        <v>-2927.088907547653</v>
+        <v>-2677.260149235156</v>
       </c>
       <c r="O83">
-        <v>-482.9696697453627</v>
+        <v>-441.7479246238008</v>
       </c>
       <c r="P83">
-        <v>-2444.11923780229</v>
+        <v>-2235.512224611356</v>
       </c>
       <c r="Q83">
-        <v>-2050.41923780229</v>
+        <v>-1841.812224611356</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3125405652121153</v>
+        <v>0.3118644605096549</v>
       </c>
       <c r="T83">
-        <v>5.196841989541086</v>
+        <v>5.186091560853097</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.03422302993355936</v>
+        <v>0.03670611907998448</v>
       </c>
       <c r="W83">
-        <v>0.214148117793126</v>
+        <v>0.199148117793126</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8521,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2074123026276324</v>
+        <v>0.2224613277574817</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8532,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2346020489693593</v>
+        <v>0.2221735890758919</v>
       </c>
       <c r="C84">
-        <v>-7121.958086192853</v>
+        <v>-6832.887089310963</v>
       </c>
       <c r="D84">
-        <v>4131.212845185469</v>
+        <v>4420.28384206736</v>
       </c>
       <c r="E84">
         <v>15521.53321018525</v>
@@ -8175,37 +8565,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M84">
-        <v>3738.672474307499</v>
+        <v>3485.759410336824</v>
       </c>
       <c r="N84">
-        <v>-2972.682474307499</v>
+        <v>-2719.769410336824</v>
       </c>
       <c r="O84">
-        <v>-490.4926082607374</v>
+        <v>-448.761952705576</v>
       </c>
       <c r="P84">
-        <v>-2482.189866046762</v>
+        <v>-2271.007457631248</v>
       </c>
       <c r="Q84">
-        <v>-2088.489866046762</v>
+        <v>-1877.307457631248</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3273594855016772</v>
+        <v>0.326645819426858</v>
       </c>
       <c r="T84">
-        <v>5.48555543340448</v>
+        <v>5.474207758678268</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.03380567590997937</v>
+        <v>0.0362584834814481</v>
       </c>
       <c r="W84">
-        <v>0.2142406604622651</v>
+        <v>0.1992406604622651</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8603,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2048828843029052</v>
+        <v>0.219748384736049</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8614,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2363614151359847</v>
+        <v>0.2237829552425172</v>
       </c>
       <c r="C85">
-        <v>-7365.720057293354</v>
+        <v>-7078.476772868049</v>
       </c>
       <c r="D85">
-        <v>4093.071251296901</v>
+        <v>4380.314535722206</v>
       </c>
       <c r="E85">
         <v>15727.15358739718</v>
@@ -8257,37 +8647,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M85">
-        <v>3784.266041067347</v>
+        <v>3528.268671438494</v>
       </c>
       <c r="N85">
-        <v>-3018.276041067348</v>
+        <v>-2762.278671438494</v>
       </c>
       <c r="O85">
-        <v>-498.0155467761124</v>
+        <v>-455.7759807873515</v>
       </c>
       <c r="P85">
-        <v>-2520.260494291235</v>
+        <v>-2306.502690651142</v>
       </c>
       <c r="Q85">
-        <v>-2126.560494291235</v>
+        <v>-1912.802690651142</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3439218081782465</v>
+        <v>0.343166161746085</v>
       </c>
       <c r="T85">
-        <v>5.808235164781214</v>
+        <v>5.796219979776991</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.03339837860985913</v>
+        <v>0.03582163428287642</v>
       </c>
       <c r="W85">
-        <v>0.2143309731875696</v>
+        <v>0.1993309731875696</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8685,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.202414415817328</v>
+        <v>0.2171008138356146</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8696,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.23812078130261</v>
+        <v>0.2253923214091425</v>
       </c>
       <c r="C86">
-        <v>-7608.784183580879</v>
+        <v>-7323.350108990777</v>
       </c>
       <c r="D86">
-        <v>4055.627502221302</v>
+        <v>4341.061576811406</v>
       </c>
       <c r="E86">
         <v>15932.77396460911</v>
@@ -8339,37 +8729,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M86">
-        <v>3829.859607827194</v>
+        <v>3570.777932540161</v>
       </c>
       <c r="N86">
-        <v>-3063.869607827194</v>
+        <v>-2804.787932540161</v>
       </c>
       <c r="O86">
-        <v>-505.5384852914871</v>
+        <v>-462.7900088691267</v>
       </c>
       <c r="P86">
-        <v>-2558.331122535707</v>
+        <v>-2341.997923671035</v>
       </c>
       <c r="Q86">
-        <v>-2164.631122535707</v>
+        <v>-1948.297923671035</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3625544211893867</v>
+        <v>0.3617515468552151</v>
       </c>
       <c r="T86">
-        <v>6.171249862580037</v>
+        <v>6.158483728513048</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.03300077886450367</v>
+        <v>0.03539518625569933</v>
       </c>
       <c r="W86">
-        <v>0.2144191356098906</v>
+        <v>0.1994191356098906</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8767,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2000047203909313</v>
+        <v>0.2145162803375716</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8778,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.265552346200659</v>
+        <v>0.2270016875757679</v>
       </c>
       <c r="C87">
-        <v>-8320.666318416597</v>
+        <v>-7567.52618467564</v>
       </c>
       <c r="D87">
-        <v>3549.365744597518</v>
+        <v>4302.505878338474</v>
       </c>
       <c r="E87">
         <v>16138.39434182104</v>
@@ -8421,45 +8811,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M87">
-        <v>4399.785136477466</v>
+        <v>3613.28719364183</v>
       </c>
       <c r="N87">
-        <v>-3633.795136477466</v>
+        <v>-2847.29719364183</v>
       </c>
       <c r="O87">
-        <v>-599.576197518782</v>
+        <v>-469.804036950902</v>
       </c>
       <c r="P87">
-        <v>-3034.218938958684</v>
+        <v>-2377.493156690928</v>
       </c>
       <c r="Q87">
-        <v>-2640.518938958684</v>
+        <v>-1983.793156690928</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3848193741448372</v>
+        <v>0.3828149833122295</v>
       </c>
       <c r="T87">
-        <v>6.605032561968224</v>
+        <v>6.56904931041392</v>
       </c>
       <c r="U87">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.02872602776716238</v>
+        <v>0.03497877229974992</v>
       </c>
       <c r="W87">
-        <v>0.2445052236222746</v>
+        <v>0.1995052236222746</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.1740971379828022</v>
+        <v>0.2119925593924238</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8860,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2676117123672844</v>
+        <v>0.2286110537423932</v>
       </c>
       <c r="C88">
-        <v>-8559.240066978458</v>
+        <v>-7811.02341479419</v>
       </c>
       <c r="D88">
-        <v>3516.412373247586</v>
+        <v>4264.629025431855</v>
       </c>
       <c r="E88">
         <v>16344.01471903297</v>
@@ -8503,45 +8893,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M88">
-        <v>4451.547314553671</v>
+        <v>3655.796454743499</v>
       </c>
       <c r="N88">
-        <v>-3685.557314553671</v>
+        <v>-2889.806454743499</v>
       </c>
       <c r="O88">
-        <v>-608.1169569013557</v>
+        <v>-476.8180650326773</v>
       </c>
       <c r="P88">
-        <v>-3077.440357652315</v>
+        <v>-2412.988389710822</v>
       </c>
       <c r="Q88">
-        <v>-2683.740357652316</v>
+        <v>-2019.288389710822</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4090350437266113</v>
+        <v>0.4068874821202459</v>
       </c>
       <c r="T88">
-        <v>7.076820602108812</v>
+        <v>7.038267118300628</v>
       </c>
       <c r="U88">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.02839200418847444</v>
+        <v>0.03457204238928772</v>
       </c>
       <c r="W88">
-        <v>0.244589309587859</v>
+        <v>0.1995893095878591</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.1720727526574208</v>
+        <v>0.2095275296320467</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8942,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2696710785339097</v>
+        <v>0.2302204199090185</v>
       </c>
       <c r="C89">
-        <v>-8797.207546445814</v>
+        <v>-8053.85957141994</v>
       </c>
       <c r="D89">
-        <v>3484.065270992161</v>
+        <v>4227.413246018034</v>
       </c>
       <c r="E89">
         <v>16549.6350962449</v>
@@ -8585,45 +8975,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M89">
-        <v>4503.309492629876</v>
+        <v>3698.305715845167</v>
       </c>
       <c r="N89">
-        <v>-3737.319492629877</v>
+        <v>-2932.315715845167</v>
       </c>
       <c r="O89">
-        <v>-616.6577162839296</v>
+        <v>-483.8320931144526</v>
       </c>
       <c r="P89">
-        <v>-3120.661776345947</v>
+        <v>-2448.483622730715</v>
       </c>
       <c r="Q89">
-        <v>-2726.961776345947</v>
+        <v>-2054.783622730715</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4369762009363506</v>
+        <v>0.4346634422833417</v>
       </c>
       <c r="T89">
-        <v>7.621191417655644</v>
+        <v>7.579672281246831</v>
       </c>
       <c r="U89">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.02806565931274485</v>
+        <v>0.0341746625917097</v>
       </c>
       <c r="W89">
-        <v>0.2446714625427404</v>
+        <v>0.1996714625427404</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.1700949049257263</v>
+        <v>0.207119167222483</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +9024,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2717304447005351</v>
+        <v>0.2318297860756439</v>
       </c>
       <c r="C90">
-        <v>-9034.585335328875</v>
+        <v>-8296.051811632989</v>
       </c>
       <c r="D90">
-        <v>3452.307859321033</v>
+        <v>4190.841383016918</v>
       </c>
       <c r="E90">
         <v>16755.25547345683</v>
@@ -8667,45 +9057,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M90">
-        <v>4555.071670706082</v>
+        <v>3740.814976946836</v>
       </c>
       <c r="N90">
-        <v>-3789.081670706082</v>
+        <v>-2974.824976946836</v>
       </c>
       <c r="O90">
-        <v>-625.1984756665036</v>
+        <v>-490.846121196228</v>
       </c>
       <c r="P90">
-        <v>-3163.883195039579</v>
+        <v>-2483.978855750608</v>
       </c>
       <c r="Q90">
-        <v>-2770.183195039579</v>
+        <v>-2090.278855750608</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4695742176810466</v>
+        <v>0.4670687291402868</v>
       </c>
       <c r="T90">
-        <v>8.256290702460282</v>
+        <v>8.211311638017399</v>
       </c>
       <c r="U90">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.02774673136600912</v>
+        <v>0.03378631415316754</v>
       </c>
       <c r="W90">
-        <v>0.2447517483850108</v>
+        <v>0.1997517483850108</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.1681620082788431</v>
+        <v>0.2047655403222275</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +9106,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2737898108671604</v>
+        <v>0.2334391522422692</v>
       </c>
       <c r="C91">
-        <v>-9271.389413142244</v>
+        <v>-8537.616703893744</v>
       </c>
       <c r="D91">
-        <v>3421.124158719594</v>
+        <v>4154.896867968094</v>
       </c>
       <c r="E91">
         <v>16960.87585066876</v>
@@ -8749,45 +9139,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M91">
-        <v>4606.833848782288</v>
+        <v>3783.324238048504</v>
       </c>
       <c r="N91">
-        <v>-3840.843848782288</v>
+        <v>-3017.334238048505</v>
       </c>
       <c r="O91">
-        <v>-633.7392350490775</v>
+        <v>-497.8601492780033</v>
       </c>
       <c r="P91">
-        <v>-3207.10461373321</v>
+        <v>-2519.474088770501</v>
       </c>
       <c r="Q91">
-        <v>-2813.404613733211</v>
+        <v>-2125.774088770501</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5080991465611416</v>
+        <v>0.5053658863348585</v>
       </c>
       <c r="T91">
-        <v>9.006862584502125</v>
+        <v>8.957794514200801</v>
       </c>
       <c r="U91">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.02743497033942474</v>
+        <v>0.03340669264582858</v>
       </c>
       <c r="W91">
-        <v>0.2448302300510503</v>
+        <v>0.1998302300510503</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.1662725475116651</v>
+        <v>0.2024648039141126</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +9188,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2758491770337858</v>
+        <v>0.2350485184088946</v>
       </c>
       <c r="C92">
-        <v>-9507.635187215546</v>
+        <v>-8778.570253071002</v>
       </c>
       <c r="D92">
-        <v>3390.498761858221</v>
+        <v>4119.563696002765</v>
       </c>
       <c r="E92">
         <v>17166.49622788069</v>
@@ -8831,45 +9221,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M92">
-        <v>4658.596026858492</v>
+        <v>3825.833499150173</v>
       </c>
       <c r="N92">
-        <v>-3892.606026858492</v>
+        <v>-3059.843499150173</v>
       </c>
       <c r="O92">
-        <v>-642.2799944316513</v>
+        <v>-504.8741773597786</v>
       </c>
       <c r="P92">
-        <v>-3250.326032426841</v>
+        <v>-2554.969321790395</v>
       </c>
       <c r="Q92">
-        <v>-2856.626032426841</v>
+        <v>-2161.269321790395</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.5543290612172559</v>
+        <v>0.5513224749683444</v>
       </c>
       <c r="T92">
-        <v>9.907548842952339</v>
+        <v>9.853573965620884</v>
       </c>
       <c r="U92">
-        <v>0.2517366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.02713013733565336</v>
+        <v>0.03303550717198604</v>
       </c>
       <c r="W92">
-        <v>0.2449069676800668</v>
+        <v>0.1999069676800668</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.1644250747615355</v>
+        <v>0.2002151949817336</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +9270,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2779085432004111</v>
+        <v>0.2687321683383852</v>
       </c>
       <c r="C93">
-        <v>-9743.337518076754</v>
+        <v>-9606.630821093673</v>
       </c>
       <c r="D93">
-        <v>3360.416808208946</v>
+        <v>3497.123505192028</v>
       </c>
       <c r="E93">
         <v>17372.11660509263</v>
@@ -8913,37 +9303,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M93">
-        <v>4710.358204934699</v>
+        <v>4523.243661671841</v>
       </c>
       <c r="N93">
-        <v>-3944.368204934699</v>
+        <v>-3757.253661671842</v>
       </c>
       <c r="O93">
-        <v>-650.8207538142253</v>
+        <v>-619.9468541758539</v>
       </c>
       <c r="P93">
-        <v>-3293.547451120474</v>
+        <v>-3137.306807495988</v>
       </c>
       <c r="Q93">
-        <v>-2899.847451120474</v>
+        <v>-2743.606807495988</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6108322902413955</v>
+        <v>0.6099836806633305</v>
       </c>
       <c r="T93">
-        <v>11.00838760328038</v>
+        <v>10.99699005066091</v>
       </c>
       <c r="U93">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.02683200395833848</v>
+        <v>0.02794197249884289</v>
       </c>
       <c r="W93">
-        <v>0.2449820187677862</v>
+        <v>0.2349820187677862</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9341,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.162618205808112</v>
+        <v>0.1693452878717751</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9352,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2799679093670364</v>
+        <v>0.2706915345050105</v>
       </c>
       <c r="C94">
-        <v>-9978.510743496156</v>
+        <v>-9842.719866197727</v>
       </c>
       <c r="D94">
-        <v>3330.863960001475</v>
+        <v>3466.654837299902</v>
       </c>
       <c r="E94">
         <v>17577.73698230456</v>
@@ -8995,37 +9385,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M94">
-        <v>4762.120383010904</v>
+        <v>4572.949635975928</v>
       </c>
       <c r="N94">
-        <v>-3996.130383010905</v>
+        <v>-3806.959635975928</v>
       </c>
       <c r="O94">
-        <v>-659.3615131967993</v>
+        <v>-628.1483399360282</v>
       </c>
       <c r="P94">
-        <v>-3336.768869814106</v>
+        <v>-3178.8112960399</v>
       </c>
       <c r="Q94">
-        <v>-2943.068869814106</v>
+        <v>-2785.1112960399</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.6814613265215701</v>
+        <v>0.680506640746247</v>
       </c>
       <c r="T94">
-        <v>12.38443605369043</v>
+        <v>12.37161380699352</v>
       </c>
       <c r="U94">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.02654035174140002</v>
+        <v>0.02763825540646415</v>
       </c>
       <c r="W94">
-        <v>0.2450554383101205</v>
+        <v>0.2350554383101205</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9423,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1608506166145456</v>
+        <v>0.1675045782209948</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9434,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2820272755336617</v>
+        <v>0.2726509006716359</v>
       </c>
       <c r="C95">
-        <v>-10213.16870127266</v>
+        <v>-10078.28258077514</v>
       </c>
       <c r="D95">
-        <v>3301.8263794369</v>
+        <v>3436.712499934421</v>
       </c>
       <c r="E95">
         <v>17783.35735951649</v>
@@ -9077,37 +9467,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M95">
-        <v>4813.882561087109</v>
+        <v>4622.655610280013</v>
       </c>
       <c r="N95">
-        <v>-4047.892561087109</v>
+        <v>-3856.665610280013</v>
       </c>
       <c r="O95">
-        <v>-667.9022725793731</v>
+        <v>-636.3498256962023</v>
       </c>
       <c r="P95">
-        <v>-3379.990288507736</v>
+        <v>-3220.315784583811</v>
       </c>
       <c r="Q95">
-        <v>-2986.290288507736</v>
+        <v>-2826.615784583812</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.772270087453223</v>
+        <v>0.7711790179957109</v>
       </c>
       <c r="T95">
-        <v>14.15364120421763</v>
+        <v>14.1389872079926</v>
       </c>
       <c r="U95">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.02625497161514841</v>
+        <v>0.02734106986445917</v>
       </c>
       <c r="W95">
-        <v>0.2451272789375658</v>
+        <v>0.2351272789375658</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9505,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1591210400918085</v>
+        <v>0.165703453723995</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9516,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2840866417002871</v>
+        <v>0.2746102668382613</v>
       </c>
       <c r="C96">
-        <v>-10447.32475083855</v>
+        <v>-10313.33248617144</v>
       </c>
       <c r="D96">
-        <v>3273.290707082946</v>
+        <v>3407.28297175005</v>
       </c>
       <c r="E96">
         <v>17988.97773672842</v>
@@ -9159,37 +9549,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M96">
-        <v>4865.644739163316</v>
+        <v>4672.3615845841</v>
       </c>
       <c r="N96">
-        <v>-4099.654739163316</v>
+        <v>-3906.371584584101</v>
       </c>
       <c r="O96">
-        <v>-676.4430319619471</v>
+        <v>-644.5513114563767</v>
       </c>
       <c r="P96">
-        <v>-3423.211707201369</v>
+        <v>-3261.820273127724</v>
       </c>
       <c r="Q96">
-        <v>-3029.511707201369</v>
+        <v>-2868.120273127724</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.8933484353620939</v>
+        <v>0.8920755209949964</v>
       </c>
       <c r="T96">
-        <v>16.51258140492058</v>
+        <v>16.49548507599137</v>
       </c>
       <c r="U96">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.02597566340647662</v>
+        <v>0.02705020741909258</v>
       </c>
       <c r="W96">
-        <v>0.2451975910410229</v>
+        <v>0.2351975910410229</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9587,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1574282630695553</v>
+        <v>0.1639406510248035</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9598,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2861460078669125</v>
+        <v>0.2765696330048866</v>
       </c>
       <c r="C97">
-        <v>-10680.99179375348</v>
+        <v>-10547.88264451634</v>
       </c>
       <c r="D97">
-        <v>3245.244041379939</v>
+        <v>3378.353190617087</v>
       </c>
       <c r="E97">
         <v>18194.59811394035</v>
@@ -9241,37 +9631,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M97">
-        <v>4917.40691723952</v>
+        <v>4722.067558888186</v>
       </c>
       <c r="N97">
-        <v>-4151.41691723952</v>
+        <v>-3956.077558888186</v>
       </c>
       <c r="O97">
-        <v>-684.9837913445209</v>
+        <v>-652.7527972165508</v>
       </c>
       <c r="P97">
-        <v>-3466.433125895</v>
+        <v>-3303.324761671635</v>
       </c>
       <c r="Q97">
-        <v>-3072.733125895</v>
+        <v>-2909.624761671635</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.062858122434513</v>
+        <v>1.061330625193996</v>
       </c>
       <c r="T97">
-        <v>19.8150976859047</v>
+        <v>19.79458209118965</v>
       </c>
       <c r="U97">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.02570223537061897</v>
+        <v>0.02676546839362845</v>
       </c>
       <c r="W97">
-        <v>0.2452664228896704</v>
+        <v>0.2352664228896704</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9669,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1557711234582968</v>
+        <v>0.1622149599613845</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9680,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2882053740335378</v>
+        <v>0.2785289991715119</v>
       </c>
       <c r="C98">
-        <v>-10914.18229315394</v>
+        <v>-10781.9456780546</v>
       </c>
       <c r="D98">
-        <v>3217.673919191412</v>
+        <v>3349.910534290758</v>
       </c>
       <c r="E98">
         <v>18400.21849115228</v>
@@ -9323,37 +9713,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M98">
-        <v>4969.169095315726</v>
+        <v>4771.773533192272</v>
       </c>
       <c r="N98">
-        <v>-4203.179095315726</v>
+        <v>-4005.783533192272</v>
       </c>
       <c r="O98">
-        <v>-693.5245507270948</v>
+        <v>-660.954282976725</v>
       </c>
       <c r="P98">
-        <v>-3509.654544588631</v>
+        <v>-3344.829250215547</v>
       </c>
       <c r="Q98">
-        <v>-3115.954544588632</v>
+        <v>-2951.129250215547</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.317122653043139</v>
+        <v>1.315213281492492</v>
       </c>
       <c r="T98">
-        <v>24.76887210738082</v>
+        <v>24.74322761398701</v>
       </c>
       <c r="U98">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.02543450375217502</v>
+        <v>0.02648666143119482</v>
       </c>
       <c r="W98">
-        <v>0.245333820741471</v>
+        <v>0.235333820741471</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9751,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1541485075889395</v>
+        <v>0.1605252207951201</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9762,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2902647402001631</v>
+        <v>0.2804883653381373</v>
       </c>
       <c r="C99">
-        <v>-11146.90829221952</v>
+        <v>-11015.53378750862</v>
       </c>
       <c r="D99">
-        <v>3190.568297337764</v>
+        <v>3321.942802048666</v>
       </c>
       <c r="E99">
         <v>18605.83886836421</v>
@@ -9405,37 +9795,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M99">
-        <v>5020.931273391931</v>
+        <v>4821.479507496358</v>
       </c>
       <c r="N99">
-        <v>-4254.941273391932</v>
+        <v>-4055.489507496358</v>
       </c>
       <c r="O99">
-        <v>-702.0653101096688</v>
+        <v>-669.1557687368991</v>
       </c>
       <c r="P99">
-        <v>-3552.875963282263</v>
+        <v>-3386.333738759459</v>
       </c>
       <c r="Q99">
-        <v>-3159.175963282263</v>
+        <v>-2992.633738759459</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.740896870724185</v>
+        <v>1.73835104198999</v>
       </c>
       <c r="T99">
-        <v>33.0251628098411</v>
+        <v>32.99097015198269</v>
       </c>
       <c r="U99">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.02517229237328662</v>
+        <v>0.02621360306592477</v>
       </c>
       <c r="W99">
-        <v>0.2453998289468428</v>
+        <v>0.2353998289468428</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9833,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1525593477168886</v>
+        <v>0.1588703216116653</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9844,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2923241063667885</v>
+        <v>0.2824477315047626</v>
       </c>
       <c r="C100">
-        <v>-11379.18143171373</v>
+        <v>-11248.65876952876</v>
       </c>
       <c r="D100">
-        <v>3163.915535055488</v>
+        <v>3294.438197240454</v>
       </c>
       <c r="E100">
         <v>18811.45924557614</v>
@@ -9487,37 +9877,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M100">
-        <v>5072.693451468136</v>
+        <v>4871.185481800444</v>
       </c>
       <c r="N100">
-        <v>-4306.703451468136</v>
+        <v>-4105.195481800444</v>
       </c>
       <c r="O100">
-        <v>-710.6060694922426</v>
+        <v>-677.3572544970733</v>
       </c>
       <c r="P100">
-        <v>-3596.097381975894</v>
+        <v>-3427.838227303371</v>
       </c>
       <c r="Q100">
-        <v>-3202.397381975894</v>
+        <v>-3034.138227303371</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.588445306086276</v>
+        <v>2.584626562984984</v>
       </c>
       <c r="T100">
-        <v>49.53774421476164</v>
+        <v>49.48645522797402</v>
       </c>
       <c r="U100">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.02491543224702859</v>
+        <v>0.02594611732035411</v>
       </c>
       <c r="W100">
-        <v>0.2454644900459825</v>
+        <v>0.2354644900459825</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9915,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1510026196789611</v>
+        <v>0.157249195880934</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9926,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2943834725334138</v>
+        <v>0.2844070976713879</v>
       </c>
       <c r="C101">
-        <v>-11611.01296665288</v>
+        <v>-11481.33203328391</v>
       </c>
       <c r="D101">
-        <v>3137.704377328267</v>
+        <v>3267.385310697232</v>
       </c>
       <c r="E101">
         <v>19017.07962278807</v>
@@ -9569,37 +9959,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M101">
-        <v>5124.455629544343</v>
+        <v>4920.89145610453</v>
       </c>
       <c r="N101">
-        <v>-4358.465629544343</v>
+        <v>-4154.901456104531</v>
       </c>
       <c r="O101">
-        <v>-719.1468288748166</v>
+        <v>-685.5587402572476</v>
       </c>
       <c r="P101">
-        <v>-3639.318800669526</v>
+        <v>-3469.342715847283</v>
       </c>
       <c r="Q101">
-        <v>-3245.618800669527</v>
+        <v>-3075.642715847283</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.131090612172554</v>
+        <v>5.123453125969969</v>
       </c>
       <c r="T101">
-        <v>99.07548842952329</v>
+        <v>98.97291045594804</v>
       </c>
       <c r="U101">
-        <v>0.2517366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V101">
-        <v>0.02466376121423032</v>
+        <v>0.02568403532721922</v>
       </c>
       <c r="W101">
-        <v>0.2455278448602911</v>
+        <v>0.2355278448602911</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9997,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.149477340692305</v>
+        <v>0.155660820164965</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_auto_truck.xlsx
@@ -1668,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1805,22 +1805,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09790132172561736</v>
+        <v>0.09782693029390224</v>
       </c>
       <c r="C2">
-        <v>20571.2613865102</v>
+        <v>20387.03686619029</v>
       </c>
       <c r="D2">
-        <v>14963.5613865102</v>
+        <v>14984.95724340222</v>
       </c>
       <c r="E2">
-        <v>-1339.337721193073</v>
+        <v>-1133.717343981143</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>205.6203772119308</v>
       </c>
       <c r="G2">
         <v>5607.7</v>
@@ -1841,28 +1841,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>11.56339433127301</v>
       </c>
       <c r="N2">
-        <v>765.9899999999999</v>
+        <v>754.4266056687269</v>
       </c>
       <c r="O2">
-        <v>126.38835</v>
+        <v>124.4803899353399</v>
       </c>
       <c r="P2">
-        <v>639.6016499999999</v>
+        <v>629.9462157333869</v>
       </c>
       <c r="Q2">
-        <v>1033.30165</v>
+        <v>1023.646215733387</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09790132172561736</v>
+        <v>0.09834076216643443</v>
       </c>
       <c r="T2">
-        <v>1.015551736571413</v>
+        <v>1.024117248693</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>66.24266007502594</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1887,22 +1887,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09782693029390224</v>
+        <v>0.09775253886218713</v>
       </c>
       <c r="C3">
-        <v>20387.03686619029</v>
+        <v>20202.8736198124</v>
       </c>
       <c r="D3">
-        <v>14984.95724340222</v>
+        <v>15006.41437423626</v>
       </c>
       <c r="E3">
-        <v>-1133.717343981143</v>
+        <v>-928.0969667692118</v>
       </c>
       <c r="F3">
-        <v>205.6203772119308</v>
+        <v>411.2407544238615</v>
       </c>
       <c r="G3">
         <v>5607.7</v>
@@ -1923,28 +1923,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M3">
-        <v>11.56339433127301</v>
+        <v>23.12678866254602</v>
       </c>
       <c r="N3">
-        <v>754.4266056687269</v>
+        <v>742.8632113374539</v>
       </c>
       <c r="O3">
-        <v>124.4803899353399</v>
+        <v>122.5724298706799</v>
       </c>
       <c r="P3">
-        <v>629.9462157333869</v>
+        <v>620.290781466774</v>
       </c>
       <c r="Q3">
-        <v>1023.646215733387</v>
+        <v>1013.990781466774</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09834076216643443</v>
+        <v>0.09878917077951307</v>
       </c>
       <c r="T3">
-        <v>1.024117248693</v>
+        <v>1.032857567184416</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>66.24266007502594</v>
+        <v>33.12133003751297</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1969,22 +1969,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09775253886218713</v>
+        <v>0.09767814743047203</v>
       </c>
       <c r="C4">
-        <v>20202.8736198124</v>
+        <v>20018.77191097053</v>
       </c>
       <c r="D4">
-        <v>15006.41437423626</v>
+        <v>15027.93304260632</v>
       </c>
       <c r="E4">
-        <v>-928.0969667692118</v>
+        <v>-722.476589557281</v>
       </c>
       <c r="F4">
-        <v>411.2407544238615</v>
+        <v>616.8611316357923</v>
       </c>
       <c r="G4">
         <v>5607.7</v>
@@ -2005,28 +2005,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M4">
-        <v>23.12678866254602</v>
+        <v>34.69018299381904</v>
       </c>
       <c r="N4">
-        <v>742.8632113374539</v>
+        <v>731.2998170061809</v>
       </c>
       <c r="O4">
-        <v>122.5724298706799</v>
+        <v>120.6644698060199</v>
       </c>
       <c r="P4">
-        <v>620.290781466774</v>
+        <v>610.635347200161</v>
       </c>
       <c r="Q4">
-        <v>1013.990781466774</v>
+        <v>1004.335347200161</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09878917077951307</v>
+        <v>0.09924682493100573</v>
       </c>
       <c r="T4">
-        <v>1.032857567184416</v>
+        <v>1.041778098428232</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>33.12133003751297</v>
+        <v>22.08088669167531</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2051,22 +2051,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09767814743047203</v>
+        <v>0.09760375599875691</v>
       </c>
       <c r="C5">
-        <v>20018.77191097053</v>
+        <v>19834.73200477281</v>
       </c>
       <c r="D5">
-        <v>15027.93304260632</v>
+        <v>15049.51351362054</v>
       </c>
       <c r="E5">
-        <v>-722.476589557281</v>
+        <v>-516.8562123453503</v>
       </c>
       <c r="F5">
-        <v>616.8611316357923</v>
+        <v>822.481508847723</v>
       </c>
       <c r="G5">
         <v>5607.7</v>
@@ -2087,28 +2087,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M5">
-        <v>34.69018299381904</v>
+        <v>46.25357732509205</v>
       </c>
       <c r="N5">
-        <v>731.2998170061809</v>
+        <v>719.7364226749079</v>
       </c>
       <c r="O5">
-        <v>120.6644698060199</v>
+        <v>118.7565097413598</v>
       </c>
       <c r="P5">
-        <v>610.635347200161</v>
+        <v>600.9799129335481</v>
       </c>
       <c r="Q5">
-        <v>1004.335347200161</v>
+        <v>994.6799129335481</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09924682493100573</v>
+        <v>0.09971401354398779</v>
       </c>
       <c r="T5">
-        <v>1.041778098428232</v>
+        <v>1.05088447407296</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.08088669167531</v>
+        <v>16.56066501875648</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09760375599875691</v>
+        <v>0.09752936456704181</v>
       </c>
       <c r="C6">
-        <v>19834.73200477281</v>
+        <v>19650.75416785234</v>
       </c>
       <c r="D6">
-        <v>15049.51351362054</v>
+        <v>15071.156053912</v>
       </c>
       <c r="E6">
-        <v>-516.8562123453503</v>
+        <v>-311.2358351334194</v>
       </c>
       <c r="F6">
-        <v>822.481508847723</v>
+        <v>1028.101886059654</v>
       </c>
       <c r="G6">
         <v>5607.7</v>
@@ -2169,28 +2169,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M6">
-        <v>46.25357732509205</v>
+        <v>57.81697165636507</v>
       </c>
       <c r="N6">
-        <v>719.7364226749079</v>
+        <v>708.1730283436348</v>
       </c>
       <c r="O6">
-        <v>118.7565097413598</v>
+        <v>116.8485496766997</v>
       </c>
       <c r="P6">
-        <v>600.9799129335481</v>
+        <v>591.324478666935</v>
       </c>
       <c r="Q6">
-        <v>994.6799129335481</v>
+        <v>985.0244786669349</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09971401354398779</v>
+        <v>0.1001910377067169</v>
       </c>
       <c r="T6">
-        <v>1.05088447407296</v>
+        <v>1.060182562889157</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.56066501875648</v>
+        <v>13.24853201500518</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2215,22 +2215,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09752936456704181</v>
+        <v>0.09745497313532669</v>
       </c>
       <c r="C7">
-        <v>19650.75416785234</v>
+        <v>19466.83866837823</v>
       </c>
       <c r="D7">
-        <v>15071.156053912</v>
+        <v>15092.86093164981</v>
       </c>
       <c r="E7">
-        <v>-311.2358351334194</v>
+        <v>-105.6154579214888</v>
       </c>
       <c r="F7">
-        <v>1028.101886059654</v>
+        <v>1233.722263271585</v>
       </c>
       <c r="G7">
         <v>5607.7</v>
@@ -2251,28 +2251,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M7">
-        <v>57.81697165636507</v>
+        <v>69.38036598763807</v>
       </c>
       <c r="N7">
-        <v>708.1730283436348</v>
+        <v>696.6096340123618</v>
       </c>
       <c r="O7">
-        <v>116.8485496766997</v>
+        <v>114.9405896120397</v>
       </c>
       <c r="P7">
-        <v>591.324478666935</v>
+        <v>581.669044400322</v>
       </c>
       <c r="Q7">
-        <v>985.0244786669349</v>
+        <v>975.369044400322</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1001910377067169</v>
+        <v>0.1006782113197168</v>
       </c>
       <c r="T7">
-        <v>1.060182562889157</v>
+        <v>1.069678483382294</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>13.24853201500518</v>
+        <v>11.04044334583765</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2297,22 +2297,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09745497313532669</v>
+        <v>0.09738058170361158</v>
       </c>
       <c r="C8">
-        <v>19466.83866837823</v>
+        <v>19282.98577606661</v>
       </c>
       <c r="D8">
-        <v>15092.86093164981</v>
+        <v>15114.62841655012</v>
       </c>
       <c r="E8">
-        <v>-105.6154579214888</v>
+        <v>100.0049192904419</v>
       </c>
       <c r="F8">
-        <v>1233.722263271585</v>
+        <v>1439.342640483515</v>
       </c>
       <c r="G8">
         <v>5607.7</v>
@@ -2333,28 +2333,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M8">
-        <v>69.38036598763807</v>
+        <v>80.94376031891107</v>
       </c>
       <c r="N8">
-        <v>696.6096340123618</v>
+        <v>685.0462396810888</v>
       </c>
       <c r="O8">
-        <v>114.9405896120397</v>
+        <v>113.0326295473797</v>
       </c>
       <c r="P8">
-        <v>581.669044400322</v>
+        <v>572.0136101337091</v>
       </c>
       <c r="Q8">
-        <v>975.369044400322</v>
+        <v>965.713610133709</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1006782113197168</v>
+        <v>0.1011758617846091</v>
       </c>
       <c r="T8">
-        <v>1.069678483382294</v>
+        <v>1.079378617219369</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.04044334583765</v>
+        <v>9.463237153575133</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2379,22 +2379,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09738058170361158</v>
+        <v>0.09740639027189649</v>
       </c>
       <c r="C9">
-        <v>19282.98577606661</v>
+        <v>19069.80651094304</v>
       </c>
       <c r="D9">
-        <v>15114.62841655012</v>
+        <v>15107.06952863849</v>
       </c>
       <c r="E9">
-        <v>100.0049192904421</v>
+        <v>305.6252965023727</v>
       </c>
       <c r="F9">
-        <v>1439.342640483515</v>
+        <v>1644.963017695446</v>
       </c>
       <c r="G9">
         <v>5607.7</v>
@@ -2415,45 +2415,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M9">
-        <v>80.94376031891109</v>
+        <v>94.97459917672725</v>
       </c>
       <c r="N9">
-        <v>685.0462396810888</v>
+        <v>671.0154008232727</v>
       </c>
       <c r="O9">
-        <v>113.0326295473797</v>
+        <v>110.71754113584</v>
       </c>
       <c r="P9">
-        <v>572.0136101337091</v>
+        <v>560.2978596874327</v>
       </c>
       <c r="Q9">
-        <v>965.713610133709</v>
+        <v>953.9978596874327</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1011758617846091</v>
+        <v>0.1016843307378687</v>
       </c>
       <c r="T9">
-        <v>1.079378617219369</v>
+        <v>1.089289623531164</v>
       </c>
       <c r="U9">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V9">
         <v>0.165</v>
       </c>
       <c r="W9">
-        <v>0.04695757491321597</v>
+        <v>0.04821007491321597</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.463237153575131</v>
+        <v>8.065209083690448</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2461,22 +2461,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09740639027189649</v>
+        <v>0.09734452384018137</v>
       </c>
       <c r="C10">
-        <v>19069.80651094304</v>
+        <v>18882.31842821708</v>
       </c>
       <c r="D10">
-        <v>15107.06952863849</v>
+        <v>15125.20182312445</v>
       </c>
       <c r="E10">
-        <v>305.6252965023727</v>
+        <v>511.2456737143034</v>
       </c>
       <c r="F10">
-        <v>1644.963017695446</v>
+        <v>1850.583394907377</v>
       </c>
       <c r="G10">
         <v>5607.7</v>
@@ -2497,28 +2497,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M10">
-        <v>94.97459917672725</v>
+        <v>106.8464240738182</v>
       </c>
       <c r="N10">
-        <v>671.0154008232727</v>
+        <v>659.1435759261817</v>
       </c>
       <c r="O10">
-        <v>110.71754113584</v>
+        <v>108.75869002782</v>
       </c>
       <c r="P10">
-        <v>560.2978596874327</v>
+        <v>550.3848858983617</v>
       </c>
       <c r="Q10">
-        <v>953.9978596874327</v>
+        <v>944.0848858983617</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1016843307378687</v>
+        <v>0.1022039748329582</v>
       </c>
       <c r="T10">
-        <v>1.089289623531164</v>
+        <v>1.099418454157503</v>
       </c>
       <c r="U10">
         <v>0.05773661666253409</v>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.065209083690448</v>
+        <v>7.169074741058175</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2543,22 +2543,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09734452384018137</v>
+        <v>0.09742460740846627</v>
       </c>
       <c r="C11">
-        <v>18882.31842821708</v>
+        <v>18653.23481915059</v>
       </c>
       <c r="D11">
-        <v>15125.20182312445</v>
+        <v>15101.7385912699</v>
       </c>
       <c r="E11">
-        <v>511.2456737143034</v>
+        <v>716.866050926234</v>
       </c>
       <c r="F11">
-        <v>1850.583394907377</v>
+        <v>2056.203772119307</v>
       </c>
       <c r="G11">
         <v>5607.7</v>
@@ -2579,45 +2579,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M11">
-        <v>106.8464240738182</v>
+        <v>122.2137953835119</v>
       </c>
       <c r="N11">
-        <v>659.1435759261817</v>
+        <v>643.776204616488</v>
       </c>
       <c r="O11">
-        <v>108.75869002782</v>
+        <v>106.2230737617205</v>
       </c>
       <c r="P11">
-        <v>550.3848858983617</v>
+        <v>537.5531308547675</v>
       </c>
       <c r="Q11">
-        <v>944.0848858983617</v>
+        <v>931.2531308547674</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1022039748329582</v>
+        <v>0.1027351665746052</v>
       </c>
       <c r="T11">
-        <v>1.099418454157503</v>
+        <v>1.109772369908872</v>
       </c>
       <c r="U11">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V11">
         <v>0.165</v>
       </c>
       <c r="W11">
-        <v>0.04821007491321597</v>
+        <v>0.04962957491321596</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.169074741058175</v>
+        <v>6.267623042032955</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2625,22 +2625,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09742460740846627</v>
+        <v>0.09737693597675115</v>
       </c>
       <c r="C12">
-        <v>18653.23481915059</v>
+        <v>18461.57264799335</v>
       </c>
       <c r="D12">
-        <v>15101.7385912699</v>
+        <v>15115.69679732459</v>
       </c>
       <c r="E12">
-        <v>716.8660509262345</v>
+        <v>922.4864281381651</v>
       </c>
       <c r="F12">
-        <v>2056.203772119308</v>
+        <v>2261.824149331238</v>
       </c>
       <c r="G12">
         <v>5607.7</v>
@@ -2661,28 +2661,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M12">
-        <v>122.2137953835119</v>
+        <v>134.4351749218631</v>
       </c>
       <c r="N12">
-        <v>643.776204616488</v>
+        <v>631.5548250781368</v>
       </c>
       <c r="O12">
-        <v>106.2230737617205</v>
+        <v>104.2065461378926</v>
       </c>
       <c r="P12">
-        <v>537.5531308547675</v>
+        <v>527.3482789402442</v>
       </c>
       <c r="Q12">
-        <v>931.2531308547674</v>
+        <v>921.0482789402441</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1027351665746052</v>
+        <v>0.1032782952093229</v>
       </c>
       <c r="T12">
-        <v>1.109772369908872</v>
+        <v>1.120358957924317</v>
       </c>
       <c r="U12">
         <v>0.05943661666253409</v>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.267623042032954</v>
+        <v>5.697839129120868</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2707,22 +2707,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09737693597675115</v>
+        <v>0.09740942454503604</v>
       </c>
       <c r="C13">
-        <v>18461.57264799335</v>
+        <v>18246.4368120856</v>
       </c>
       <c r="D13">
-        <v>15115.69679732459</v>
+        <v>15106.18133862877</v>
       </c>
       <c r="E13">
-        <v>922.4864281381651</v>
+        <v>1128.106805350096</v>
       </c>
       <c r="F13">
-        <v>2261.824149331238</v>
+        <v>2467.444526543169</v>
       </c>
       <c r="G13">
         <v>5607.7</v>
@@ -2743,45 +2743,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M13">
-        <v>134.4351749218631</v>
+        <v>148.6305100814488</v>
       </c>
       <c r="N13">
-        <v>631.5548250781368</v>
+        <v>617.359489918551</v>
       </c>
       <c r="O13">
-        <v>104.2065461378926</v>
+        <v>101.8643158365609</v>
       </c>
       <c r="P13">
-        <v>527.3482789402442</v>
+        <v>515.4951740819902</v>
       </c>
       <c r="Q13">
-        <v>921.0482789402441</v>
+        <v>909.1951740819901</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1032782952093229</v>
+        <v>0.1038337676766479</v>
       </c>
       <c r="T13">
-        <v>1.120358957924317</v>
+        <v>1.13118615021284</v>
       </c>
       <c r="U13">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V13">
         <v>0.165</v>
       </c>
       <c r="W13">
-        <v>0.04962957491321596</v>
+        <v>0.05029757491321597</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>5.697839129120868</v>
+        <v>5.153652500958525</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2789,22 +2789,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09740942454503604</v>
+        <v>0.09736843311332093</v>
       </c>
       <c r="C14">
-        <v>18246.4368120856</v>
+        <v>18052.82424592074</v>
       </c>
       <c r="D14">
-        <v>15106.18133862877</v>
+        <v>15118.18914967585</v>
       </c>
       <c r="E14">
-        <v>1128.106805350096</v>
+        <v>1333.727182562026</v>
       </c>
       <c r="F14">
-        <v>2467.444526543169</v>
+        <v>2673.0649037551</v>
       </c>
       <c r="G14">
         <v>5607.7</v>
@@ -2825,28 +2825,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M14">
-        <v>148.6305100814488</v>
+        <v>161.0163859215695</v>
       </c>
       <c r="N14">
-        <v>617.359489918551</v>
+        <v>604.9736140784304</v>
       </c>
       <c r="O14">
-        <v>101.8643158365609</v>
+        <v>99.82064632294102</v>
       </c>
       <c r="P14">
-        <v>515.4951740819902</v>
+        <v>505.1529677554894</v>
       </c>
       <c r="Q14">
-        <v>909.1951740819901</v>
+        <v>898.8529677554893</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1038337676766479</v>
+        <v>0.1044020096259803</v>
       </c>
       <c r="T14">
-        <v>1.13118615021284</v>
+        <v>1.142262243473513</v>
       </c>
       <c r="U14">
         <v>0.0602366166625341</v>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.153652500958525</v>
+        <v>4.757217693192485</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2871,22 +2871,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09736843311332093</v>
+        <v>0.09732744168160583</v>
       </c>
       <c r="C15">
-        <v>18052.82424592074</v>
+        <v>17859.23078481332</v>
       </c>
       <c r="D15">
-        <v>15118.18914967585</v>
+        <v>15130.21606578036</v>
       </c>
       <c r="E15">
-        <v>1333.727182562026</v>
+        <v>1539.347559773958</v>
       </c>
       <c r="F15">
-        <v>2673.0649037551</v>
+        <v>2878.685280967031</v>
       </c>
       <c r="G15">
         <v>5607.7</v>
@@ -2907,28 +2907,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M15">
-        <v>161.0163859215695</v>
+        <v>173.4022617616903</v>
       </c>
       <c r="N15">
-        <v>604.9736140784304</v>
+        <v>592.5877382383096</v>
       </c>
       <c r="O15">
-        <v>99.82064632294102</v>
+        <v>97.77697680932108</v>
       </c>
       <c r="P15">
-        <v>505.1529677554894</v>
+        <v>494.8107614289885</v>
       </c>
       <c r="Q15">
-        <v>898.8529677554893</v>
+        <v>888.5107614289884</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1044020096259803</v>
+        <v>0.104983466504367</v>
       </c>
       <c r="T15">
-        <v>1.142262243473513</v>
+        <v>1.153595920298388</v>
       </c>
       <c r="U15">
         <v>0.0602366166625341</v>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.757217693192485</v>
+        <v>4.41741642939302</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2953,22 +2953,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09732744168160583</v>
+        <v>0.09741170024989071</v>
       </c>
       <c r="C16">
-        <v>17859.23078481332</v>
+        <v>17628.90960647741</v>
       </c>
       <c r="D16">
-        <v>15130.21606578036</v>
+        <v>15105.51526465637</v>
       </c>
       <c r="E16">
-        <v>1539.347559773958</v>
+        <v>1744.967936985889</v>
       </c>
       <c r="F16">
-        <v>2878.685280967031</v>
+        <v>3084.305658178962</v>
       </c>
       <c r="G16">
         <v>5607.7</v>
@@ -2989,45 +2989,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M16">
-        <v>173.4022617616903</v>
+        <v>188.87244325999</v>
       </c>
       <c r="N16">
-        <v>592.5877382383096</v>
+        <v>577.1175567400098</v>
       </c>
       <c r="O16">
-        <v>97.77697680932108</v>
+        <v>95.22439686210163</v>
       </c>
       <c r="P16">
-        <v>494.8107614289885</v>
+        <v>481.8931598779082</v>
       </c>
       <c r="Q16">
-        <v>888.5107614289884</v>
+        <v>875.5931598779082</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.104983466504367</v>
+        <v>0.1055786047210686</v>
       </c>
       <c r="T16">
-        <v>1.153595920298388</v>
+        <v>1.165196271872083</v>
       </c>
       <c r="U16">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V16">
         <v>0.165</v>
       </c>
       <c r="W16">
-        <v>0.05029757491321597</v>
+        <v>0.05113257491321597</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.41741642939302</v>
+        <v>4.055594277168247</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3035,22 +3035,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09741170024989071</v>
+        <v>0.09737905881817562</v>
       </c>
       <c r="C17">
-        <v>17628.90960647741</v>
+        <v>17432.84864458499</v>
       </c>
       <c r="D17">
-        <v>15105.51526465637</v>
+        <v>15115.07467997588</v>
       </c>
       <c r="E17">
-        <v>1744.967936985888</v>
+        <v>1950.588314197819</v>
       </c>
       <c r="F17">
-        <v>3084.305658178961</v>
+        <v>3289.926035390892</v>
       </c>
       <c r="G17">
         <v>5607.7</v>
@@ -3071,28 +3071,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M17">
-        <v>188.87244325999</v>
+        <v>201.4639394773226</v>
       </c>
       <c r="N17">
-        <v>577.1175567400099</v>
+        <v>564.5260605226772</v>
       </c>
       <c r="O17">
-        <v>95.22439686210164</v>
+        <v>93.14679998624175</v>
       </c>
       <c r="P17">
-        <v>481.8931598779083</v>
+        <v>471.3792605364355</v>
       </c>
       <c r="Q17">
-        <v>875.5931598779082</v>
+        <v>865.0792605364354</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1055786047210686</v>
+        <v>0.1061879128953108</v>
       </c>
       <c r="T17">
-        <v>1.165196271872083</v>
+        <v>1.177072822292771</v>
       </c>
       <c r="U17">
         <v>0.0612366166625341</v>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.055594277168248</v>
+        <v>3.802119634845232</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3117,22 +3117,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09737905881817562</v>
+        <v>0.09734641738646049</v>
       </c>
       <c r="C18">
-        <v>17432.84864458499</v>
+        <v>17236.79978956705</v>
       </c>
       <c r="D18">
-        <v>15115.07467997588</v>
+        <v>15124.64620216988</v>
       </c>
       <c r="E18">
-        <v>1950.588314197819</v>
+        <v>2156.20869140975</v>
       </c>
       <c r="F18">
-        <v>3289.926035390892</v>
+        <v>3495.546412602823</v>
       </c>
       <c r="G18">
         <v>5607.7</v>
@@ -3153,28 +3153,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M18">
-        <v>201.4639394773226</v>
+        <v>214.0554356946553</v>
       </c>
       <c r="N18">
-        <v>564.5260605226772</v>
+        <v>551.9345643053446</v>
       </c>
       <c r="O18">
-        <v>93.14679998624175</v>
+        <v>91.06920311038186</v>
       </c>
       <c r="P18">
-        <v>471.3792605364355</v>
+        <v>460.8653611949627</v>
       </c>
       <c r="Q18">
-        <v>865.0792605364354</v>
+        <v>854.5653611949626</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1061879128953108</v>
+        <v>0.1068119031942335</v>
       </c>
       <c r="T18">
-        <v>1.177072822292771</v>
+        <v>1.189235554651307</v>
       </c>
       <c r="U18">
         <v>0.0612366166625341</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.802119634845232</v>
+        <v>3.578465538677865</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09734641738646049</v>
+        <v>0.09731377595474539</v>
       </c>
       <c r="C19">
-        <v>17236.79978956705</v>
+        <v>17040.76306443796</v>
       </c>
       <c r="D19">
-        <v>15124.64620216988</v>
+        <v>15134.22985425271</v>
       </c>
       <c r="E19">
-        <v>2156.20869140975</v>
+        <v>2361.829068621681</v>
       </c>
       <c r="F19">
-        <v>3495.546412602823</v>
+        <v>3701.166789814754</v>
       </c>
       <c r="G19">
         <v>5607.7</v>
@@ -3235,28 +3235,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M19">
-        <v>214.0554356946553</v>
+        <v>226.646931911988</v>
       </c>
       <c r="N19">
-        <v>551.9345643053446</v>
+        <v>539.3430680880119</v>
       </c>
       <c r="O19">
-        <v>91.06920311038186</v>
+        <v>88.99160623452197</v>
       </c>
       <c r="P19">
-        <v>460.8653611949627</v>
+        <v>450.35146185349</v>
       </c>
       <c r="Q19">
-        <v>854.5653611949626</v>
+        <v>844.0514618534899</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1068119031942335</v>
+        <v>0.1074511127687397</v>
       </c>
       <c r="T19">
-        <v>1.189235554651307</v>
+        <v>1.201694939018588</v>
       </c>
       <c r="U19">
         <v>0.0612366166625341</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.578465538677865</v>
+        <v>3.379661897640206</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3281,22 +3281,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0973137759547454</v>
+        <v>0.09728113452303028</v>
       </c>
       <c r="C20">
-        <v>17040.76306443795</v>
+        <v>16844.73849227044</v>
       </c>
       <c r="D20">
-        <v>15134.2298542527</v>
+        <v>15143.82565929712</v>
       </c>
       <c r="E20">
-        <v>2361.82906862168</v>
+        <v>2567.449445833611</v>
       </c>
       <c r="F20">
-        <v>3701.166789814753</v>
+        <v>3906.787167026685</v>
       </c>
       <c r="G20">
         <v>5607.7</v>
@@ -3317,28 +3317,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M20">
-        <v>226.646931911988</v>
+        <v>239.2384281293207</v>
       </c>
       <c r="N20">
-        <v>539.3430680880119</v>
+        <v>526.7515718706793</v>
       </c>
       <c r="O20">
-        <v>88.99160623452197</v>
+        <v>86.91400935866208</v>
       </c>
       <c r="P20">
-        <v>450.35146185349</v>
+        <v>439.8375625120172</v>
       </c>
       <c r="Q20">
-        <v>844.0514618534899</v>
+        <v>833.5375625120171</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1074511127687397</v>
+        <v>0.1081061052957028</v>
       </c>
       <c r="T20">
-        <v>1.201694939018588</v>
+        <v>1.214461962506048</v>
       </c>
       <c r="U20">
         <v>0.0612366166625341</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.379661897640207</v>
+        <v>3.201784955659143</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3363,22 +3363,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09728113452303028</v>
+        <v>0.09724849309131518</v>
       </c>
       <c r="C21">
-        <v>16844.73849227044</v>
+        <v>16648.72609619579</v>
       </c>
       <c r="D21">
-        <v>15143.82565929712</v>
+        <v>15153.43364043441</v>
       </c>
       <c r="E21">
-        <v>2567.449445833611</v>
+        <v>2773.069823045542</v>
       </c>
       <c r="F21">
-        <v>3906.787167026685</v>
+        <v>4112.407544238616</v>
       </c>
       <c r="G21">
         <v>5607.7</v>
@@ -3399,28 +3399,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M21">
-        <v>239.2384281293207</v>
+        <v>251.8299243466533</v>
       </c>
       <c r="N21">
-        <v>526.7515718706793</v>
+        <v>514.1600756533466</v>
       </c>
       <c r="O21">
-        <v>86.91400935866208</v>
+        <v>84.83641248280219</v>
       </c>
       <c r="P21">
-        <v>439.8375625120172</v>
+        <v>429.3236631705444</v>
       </c>
       <c r="Q21">
-        <v>833.5375625120171</v>
+        <v>823.0236631705443</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1081061052957028</v>
+        <v>0.10877747263584</v>
       </c>
       <c r="T21">
-        <v>1.214461962506048</v>
+        <v>1.227548161580696</v>
       </c>
       <c r="U21">
         <v>0.0612366166625341</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.201784955659143</v>
+        <v>3.041695707876185</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3445,22 +3445,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09724849309131518</v>
+        <v>0.09765422665960008</v>
       </c>
       <c r="C22">
-        <v>16648.72609619579</v>
+        <v>16324.53762726277</v>
       </c>
       <c r="D22">
-        <v>15153.43364043441</v>
+        <v>15034.86554871332</v>
       </c>
       <c r="E22">
-        <v>2773.069823045542</v>
+        <v>2978.690200257473</v>
       </c>
       <c r="F22">
-        <v>4112.407544238616</v>
+        <v>4318.027921450546</v>
       </c>
       <c r="G22">
         <v>5607.7</v>
@@ -3481,45 +3481,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M22">
-        <v>251.8299243466533</v>
+        <v>275.2164903676123</v>
       </c>
       <c r="N22">
-        <v>514.1600756533466</v>
+        <v>490.7735096323876</v>
       </c>
       <c r="O22">
-        <v>84.83641248280219</v>
+        <v>80.97762908934395</v>
       </c>
       <c r="P22">
-        <v>429.3236631705444</v>
+        <v>409.7958805430436</v>
       </c>
       <c r="Q22">
-        <v>823.0236631705443</v>
+        <v>803.4958805430435</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.10877747263584</v>
+        <v>0.1094658366174996</v>
       </c>
       <c r="T22">
-        <v>1.227548161580696</v>
+        <v>1.240965656834448</v>
       </c>
       <c r="U22">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V22">
         <v>0.165</v>
       </c>
       <c r="W22">
-        <v>0.05113257491321597</v>
+        <v>0.05322007491321597</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.041695707876185</v>
+        <v>2.783227120500125</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3527,22 +3527,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09765422665960008</v>
+        <v>0.09764246022788495</v>
       </c>
       <c r="C23">
-        <v>16324.53762726277</v>
+        <v>16122.32964055175</v>
       </c>
       <c r="D23">
-        <v>15034.86554871332</v>
+        <v>15038.27793921422</v>
       </c>
       <c r="E23">
-        <v>2978.690200257472</v>
+        <v>3184.310577469404</v>
       </c>
       <c r="F23">
-        <v>4318.027921450545</v>
+        <v>4523.648298662477</v>
       </c>
       <c r="G23">
         <v>5607.7</v>
@@ -3563,28 +3563,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M23">
-        <v>275.2164903676123</v>
+        <v>288.3220375279748</v>
       </c>
       <c r="N23">
-        <v>490.7735096323876</v>
+        <v>477.6679624720251</v>
       </c>
       <c r="O23">
-        <v>80.97762908934396</v>
+        <v>78.81521380788413</v>
       </c>
       <c r="P23">
-        <v>409.7958805430437</v>
+        <v>398.8527486641409</v>
       </c>
       <c r="Q23">
-        <v>803.4958805430435</v>
+        <v>792.5527486641408</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1094658366174996</v>
+        <v>0.1101718509576634</v>
       </c>
       <c r="T23">
-        <v>1.240965656834448</v>
+        <v>1.254727190428039</v>
       </c>
       <c r="U23">
         <v>0.06373661666253409</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.783227120500125</v>
+        <v>2.656716796841028</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3609,22 +3609,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09764246022788495</v>
+        <v>0.09763069379616984</v>
       </c>
       <c r="C24">
-        <v>16122.32964055175</v>
+        <v>15920.12320317979</v>
       </c>
       <c r="D24">
-        <v>15038.27793921422</v>
+        <v>15041.6918790542</v>
       </c>
       <c r="E24">
-        <v>3184.310577469404</v>
+        <v>3389.930954681334</v>
       </c>
       <c r="F24">
-        <v>4523.648298662477</v>
+        <v>4729.268675874408</v>
       </c>
       <c r="G24">
         <v>5607.7</v>
@@ -3645,28 +3645,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M24">
-        <v>288.3220375279748</v>
+        <v>301.4275846883373</v>
       </c>
       <c r="N24">
-        <v>477.6679624720251</v>
+        <v>464.5624153116626</v>
       </c>
       <c r="O24">
-        <v>78.81521380788413</v>
+        <v>76.65279852642432</v>
       </c>
       <c r="P24">
-        <v>398.8527486641409</v>
+        <v>387.9096167852383</v>
       </c>
       <c r="Q24">
-        <v>792.5527486641408</v>
+        <v>781.6096167852381</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1101718509576634</v>
+        <v>0.1108962033326366</v>
       </c>
       <c r="T24">
-        <v>1.254727190428039</v>
+        <v>1.268846166452634</v>
       </c>
       <c r="U24">
         <v>0.06373661666253409</v>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.656716796841028</v>
+        <v>2.541207370891418</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3691,22 +3691,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09763069379616984</v>
+        <v>0.09832032736445473</v>
       </c>
       <c r="C25">
-        <v>15920.12320317979</v>
+        <v>15516.99347741391</v>
       </c>
       <c r="D25">
-        <v>15041.6918790542</v>
+        <v>14844.18253050025</v>
       </c>
       <c r="E25">
-        <v>3389.930954681334</v>
+        <v>3595.551331893265</v>
       </c>
       <c r="F25">
-        <v>4729.268675874408</v>
+        <v>4934.889053086338</v>
       </c>
       <c r="G25">
         <v>5607.7</v>
@@ -3727,45 +3727,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M25">
-        <v>301.4275846883373</v>
+        <v>331.805243534502</v>
       </c>
       <c r="N25">
-        <v>464.5624153116626</v>
+        <v>434.1847564654979</v>
       </c>
       <c r="O25">
-        <v>76.65279852642432</v>
+        <v>71.64048481680716</v>
       </c>
       <c r="P25">
-        <v>387.9096167852383</v>
+        <v>362.5442716486908</v>
       </c>
       <c r="Q25">
-        <v>781.6096167852381</v>
+        <v>756.2442716486908</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1108962033326366</v>
+        <v>0.1116396176122143</v>
       </c>
       <c r="T25">
-        <v>1.268846166452634</v>
+        <v>1.283336694477875</v>
       </c>
       <c r="U25">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V25">
         <v>0.165</v>
       </c>
       <c r="W25">
-        <v>0.05322007491321597</v>
+        <v>0.05614257491321597</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.541207370891418</v>
+        <v>2.308553029001033</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3773,22 +3773,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09832032736445473</v>
+        <v>0.09892228593273962</v>
       </c>
       <c r="C26">
-        <v>15516.99347741391</v>
+        <v>15143.16529990639</v>
       </c>
       <c r="D26">
-        <v>14844.18253050025</v>
+        <v>14675.97473020466</v>
       </c>
       <c r="E26">
-        <v>3595.551331893265</v>
+        <v>3801.171709105196</v>
       </c>
       <c r="F26">
-        <v>4934.889053086338</v>
+        <v>5140.509430298269</v>
       </c>
       <c r="G26">
         <v>5607.7</v>
@@ -3809,45 +3809,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M26">
-        <v>331.805243534502</v>
+        <v>360.0238884199414</v>
       </c>
       <c r="N26">
-        <v>434.1847564654979</v>
+        <v>405.9661115800585</v>
       </c>
       <c r="O26">
-        <v>71.64048481680716</v>
+        <v>66.98440841070966</v>
       </c>
       <c r="P26">
-        <v>362.5442716486908</v>
+        <v>338.9817031693489</v>
       </c>
       <c r="Q26">
-        <v>756.2442716486908</v>
+        <v>732.6817031693488</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1116396176122143</v>
+        <v>0.1124028562725808</v>
       </c>
       <c r="T26">
-        <v>1.283336694477875</v>
+        <v>1.29821363658379</v>
       </c>
       <c r="U26">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V26">
         <v>0.165</v>
       </c>
       <c r="W26">
-        <v>0.05614257491321597</v>
+        <v>0.05848057491321597</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.308553029001033</v>
+        <v>2.127608818852956</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3855,22 +3855,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09892228593273962</v>
+        <v>0.09896312450102451</v>
       </c>
       <c r="C27">
-        <v>15143.16529990639</v>
+        <v>14926.27120991343</v>
       </c>
       <c r="D27">
-        <v>14675.97473020466</v>
+        <v>14664.70101742362</v>
       </c>
       <c r="E27">
-        <v>3801.171709105196</v>
+        <v>4006.792086317126</v>
       </c>
       <c r="F27">
-        <v>5140.509430298269</v>
+        <v>5346.129807510199</v>
       </c>
       <c r="G27">
         <v>5607.7</v>
@@ -3891,28 +3891,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M27">
-        <v>360.0238884199414</v>
+        <v>374.424843956739</v>
       </c>
       <c r="N27">
-        <v>405.9661115800585</v>
+        <v>391.5651560432609</v>
       </c>
       <c r="O27">
-        <v>66.98440841070966</v>
+        <v>64.60825074713804</v>
       </c>
       <c r="P27">
-        <v>338.9817031693489</v>
+        <v>326.9569052961228</v>
       </c>
       <c r="Q27">
-        <v>732.6817031693488</v>
+        <v>720.6569052961228</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1124028562725808</v>
+        <v>0.1131867230048491</v>
       </c>
       <c r="T27">
-        <v>1.29821363658379</v>
+        <v>1.31349265820608</v>
       </c>
       <c r="U27">
         <v>0.07003661666253409</v>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.127608818852956</v>
+        <v>2.045777710435535</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3937,22 +3937,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09896312450102451</v>
+        <v>0.1007624730693094</v>
       </c>
       <c r="C28">
-        <v>14926.27120991343</v>
+        <v>14240.56128602566</v>
       </c>
       <c r="D28">
-        <v>14664.70101742362</v>
+        <v>14184.61147074779</v>
       </c>
       <c r="E28">
-        <v>4006.792086317126</v>
+        <v>4212.412463529057</v>
       </c>
       <c r="F28">
-        <v>5346.129807510199</v>
+        <v>5551.750184722131</v>
       </c>
       <c r="G28">
         <v>5607.7</v>
@@ -3973,45 +3973,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M28">
-        <v>374.424843956739</v>
+        <v>432.1294509343695</v>
       </c>
       <c r="N28">
-        <v>391.5651560432609</v>
+        <v>333.8605490656304</v>
       </c>
       <c r="O28">
-        <v>64.60825074713804</v>
+        <v>55.08699059582902</v>
       </c>
       <c r="P28">
-        <v>326.9569052961228</v>
+        <v>278.7735584698014</v>
       </c>
       <c r="Q28">
-        <v>720.6569052961228</v>
+        <v>672.4735584698013</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1131867230048491</v>
+        <v>0.1139920655380015</v>
       </c>
       <c r="T28">
-        <v>1.31349265820608</v>
+        <v>1.329190283160488</v>
       </c>
       <c r="U28">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V28">
         <v>0.165</v>
       </c>
       <c r="W28">
-        <v>0.05848057491321597</v>
+        <v>0.06499357491321597</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.045777710435535</v>
+        <v>1.77259383349999</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4019,22 +4019,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1007624730693094</v>
+        <v>0.1017802616375943</v>
       </c>
       <c r="C29">
-        <v>14240.56128602566</v>
+        <v>13777.04759109486</v>
       </c>
       <c r="D29">
-        <v>14184.61147074779</v>
+        <v>13926.71815302892</v>
       </c>
       <c r="E29">
-        <v>4212.412463529057</v>
+        <v>4418.032840740989</v>
       </c>
       <c r="F29">
-        <v>5551.750184722131</v>
+        <v>5757.370561934062</v>
       </c>
       <c r="G29">
         <v>5607.7</v>
@@ -4055,45 +4055,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M29">
-        <v>432.1294509343695</v>
+        <v>470.5879906049629</v>
       </c>
       <c r="N29">
-        <v>333.8605490656304</v>
+        <v>295.402009395037</v>
       </c>
       <c r="O29">
-        <v>55.08699059582902</v>
+        <v>48.74133155018111</v>
       </c>
       <c r="P29">
-        <v>278.7735584698014</v>
+        <v>246.6606778448559</v>
       </c>
       <c r="Q29">
-        <v>672.4735584698013</v>
+        <v>640.3606778448558</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1139920655380015</v>
+        <v>0.1148197786970748</v>
       </c>
       <c r="T29">
-        <v>1.329190283160488</v>
+        <v>1.345323953252519</v>
       </c>
       <c r="U29">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V29">
         <v>0.165</v>
       </c>
       <c r="W29">
-        <v>0.06499357491321597</v>
+        <v>0.06825007491321597</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>1.77259383349999</v>
+        <v>1.62772959636153</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4101,22 +4101,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1017802616375943</v>
+        <v>0.1019187952058792</v>
       </c>
       <c r="C30">
-        <v>13777.04759109486</v>
+        <v>13537.04803747404</v>
       </c>
       <c r="D30">
-        <v>13926.71815302892</v>
+        <v>13892.33897662003</v>
       </c>
       <c r="E30">
-        <v>4418.032840740989</v>
+        <v>4623.653217952919</v>
       </c>
       <c r="F30">
-        <v>5757.370561934062</v>
+        <v>5962.990939145992</v>
       </c>
       <c r="G30">
         <v>5607.7</v>
@@ -4137,28 +4137,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M30">
-        <v>470.5879906049629</v>
+        <v>487.3947045551402</v>
       </c>
       <c r="N30">
-        <v>295.402009395037</v>
+        <v>278.5952954448597</v>
       </c>
       <c r="O30">
-        <v>48.74133155018111</v>
+        <v>45.96822374840186</v>
       </c>
       <c r="P30">
-        <v>246.6606778448559</v>
+        <v>232.6270716964579</v>
       </c>
       <c r="Q30">
-        <v>640.3606778448558</v>
+        <v>626.3270716964578</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1148197786970748</v>
+        <v>0.1156708077197839</v>
       </c>
       <c r="T30">
-        <v>1.345323953252519</v>
+        <v>1.361912092924607</v>
       </c>
       <c r="U30">
         <v>0.0817366166625341</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.62772959636153</v>
+        <v>1.571600989590443</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4183,22 +4183,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1019187952058792</v>
+        <v>0.1020573287741641</v>
       </c>
       <c r="C31">
-        <v>13537.04803747404</v>
+        <v>13297.21780117015</v>
       </c>
       <c r="D31">
-        <v>13892.33897662003</v>
+        <v>13858.12911752807</v>
       </c>
       <c r="E31">
-        <v>4623.653217952919</v>
+        <v>4829.273595164848</v>
       </c>
       <c r="F31">
-        <v>5962.990939145991</v>
+        <v>6168.611316357922</v>
       </c>
       <c r="G31">
         <v>5607.7</v>
@@ -4219,28 +4219,28 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M31">
-        <v>487.3947045551401</v>
+        <v>504.2014185053173</v>
       </c>
       <c r="N31">
-        <v>278.5952954448598</v>
+        <v>261.7885814946826</v>
       </c>
       <c r="O31">
-        <v>45.96822374840187</v>
+        <v>43.19511594662263</v>
       </c>
       <c r="P31">
-        <v>232.6270716964579</v>
+        <v>218.59346554806</v>
       </c>
       <c r="Q31">
-        <v>626.3270716964579</v>
+        <v>612.2934655480599</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1156708077197839</v>
+        <v>0.1165461518574276</v>
       </c>
       <c r="T31">
-        <v>1.361912092924607</v>
+        <v>1.378974179444469</v>
       </c>
       <c r="U31">
         <v>0.0817366166625341</v>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.571600989590443</v>
+        <v>1.519214289937429</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1020573287741641</v>
+        <v>0.105871532342449</v>
       </c>
       <c r="C32">
-        <v>13297.21780117015</v>
+        <v>12211.68436916043</v>
       </c>
       <c r="D32">
-        <v>13858.12911752807</v>
+        <v>12978.21606273028</v>
       </c>
       <c r="E32">
-        <v>4829.273595164848</v>
+        <v>5034.89397237678</v>
       </c>
       <c r="F32">
-        <v>6168.611316357922</v>
+        <v>6374.231693569854</v>
       </c>
       <c r="G32">
         <v>5607.7</v>
@@ -4301,45 +4301,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M32">
-        <v>504.2014185053173</v>
+        <v>611.5222225041865</v>
       </c>
       <c r="N32">
-        <v>261.7885814946826</v>
+        <v>154.4677774958134</v>
       </c>
       <c r="O32">
-        <v>43.19511594662263</v>
+        <v>25.48718328680921</v>
       </c>
       <c r="P32">
-        <v>218.59346554806</v>
+        <v>128.9805942090042</v>
       </c>
       <c r="Q32">
-        <v>612.2934655480599</v>
+        <v>522.6805942090041</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1165461518574276</v>
+        <v>0.117446868288916</v>
       </c>
       <c r="T32">
-        <v>1.378974179444469</v>
+        <v>1.39653081919679</v>
       </c>
       <c r="U32">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V32">
         <v>0.165</v>
       </c>
       <c r="W32">
-        <v>0.06825007491321597</v>
+        <v>0.08010707491321598</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.519214289937429</v>
+        <v>1.252595526068157</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4347,22 +4347,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.105871532342449</v>
+        <v>0.1143788191986282</v>
       </c>
       <c r="C33">
-        <v>12211.68436916043</v>
+        <v>10396.10032944601</v>
       </c>
       <c r="D33">
-        <v>12978.21606273028</v>
+        <v>11368.25240022779</v>
       </c>
       <c r="E33">
-        <v>5034.89397237678</v>
+        <v>5240.514349588711</v>
       </c>
       <c r="F33">
-        <v>6374.231693569854</v>
+        <v>6579.852070781784</v>
       </c>
       <c r="G33">
         <v>5607.7</v>
@@ -4383,45 +4383,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M33">
-        <v>611.5222225041865</v>
+        <v>819.4325150351323</v>
       </c>
       <c r="N33">
-        <v>154.4677774958134</v>
+        <v>-53.44251503513237</v>
       </c>
       <c r="O33">
-        <v>25.48718328680921</v>
+        <v>-8.818014980796843</v>
       </c>
       <c r="P33">
-        <v>128.9805942090042</v>
+        <v>-44.62450005433553</v>
       </c>
       <c r="Q33">
-        <v>522.6805942090041</v>
+        <v>349.0754999456644</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.117446868288916</v>
+        <v>0.118637920515938</v>
       </c>
       <c r="T33">
-        <v>1.39653081919679</v>
+        <v>1.419746644005794</v>
       </c>
       <c r="U33">
-        <v>0.0959366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V33">
-        <v>0.165</v>
+        <v>0.1542388759061888</v>
       </c>
       <c r="W33">
-        <v>0.08010707491321598</v>
+        <v>0.1053282288993449</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.252595526068157</v>
+        <v>0.9347810660981142</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4429,22 +4429,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1143788191986282</v>
+        <v>0.1151661853652536</v>
       </c>
       <c r="C34">
-        <v>10396.10032944601</v>
+        <v>10061.44046034816</v>
       </c>
       <c r="D34">
-        <v>11368.25240022779</v>
+        <v>11239.21290834187</v>
       </c>
       <c r="E34">
-        <v>5240.514349588711</v>
+        <v>5446.134726800641</v>
       </c>
       <c r="F34">
-        <v>6579.852070781784</v>
+        <v>6785.472447993715</v>
       </c>
       <c r="G34">
         <v>5607.7</v>
@@ -4465,37 +4465,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M34">
-        <v>819.4325150351323</v>
+        <v>845.0397811299802</v>
       </c>
       <c r="N34">
-        <v>-53.44251503513237</v>
+        <v>-79.04978112998026</v>
       </c>
       <c r="O34">
-        <v>-8.818014980796843</v>
+        <v>-13.04321388644674</v>
       </c>
       <c r="P34">
-        <v>-44.62450005433553</v>
+        <v>-66.00656724353351</v>
       </c>
       <c r="Q34">
-        <v>349.0754999456644</v>
+        <v>327.6934327564664</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.118637920515938</v>
+        <v>0.119725053657967</v>
       </c>
       <c r="T34">
-        <v>1.419746644005794</v>
+        <v>1.440936892423792</v>
       </c>
       <c r="U34">
         <v>0.1245366166625341</v>
       </c>
       <c r="V34">
-        <v>0.1542388759061888</v>
+        <v>0.1495649705756983</v>
       </c>
       <c r="W34">
-        <v>0.1053282288993449</v>
+        <v>0.1059103012558052</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.9347810660981142</v>
+        <v>0.906454367125444</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4511,22 +4511,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1151661853652536</v>
+        <v>0.1159535515318789</v>
       </c>
       <c r="C35">
-        <v>10061.44046034816</v>
+        <v>9729.677132561497</v>
       </c>
       <c r="D35">
-        <v>11239.21290834187</v>
+        <v>11113.06995776714</v>
       </c>
       <c r="E35">
-        <v>5446.134726800641</v>
+        <v>5651.755104012573</v>
       </c>
       <c r="F35">
-        <v>6785.472447993715</v>
+        <v>6991.092825205646</v>
       </c>
       <c r="G35">
         <v>5607.7</v>
@@ -4547,37 +4547,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M35">
-        <v>845.0397811299802</v>
+        <v>870.6470472248282</v>
       </c>
       <c r="N35">
-        <v>-79.04978112998026</v>
+        <v>-104.6570472248283</v>
       </c>
       <c r="O35">
-        <v>-13.04321388644674</v>
+        <v>-17.26841279209667</v>
       </c>
       <c r="P35">
-        <v>-66.00656724353351</v>
+        <v>-87.38863443273159</v>
       </c>
       <c r="Q35">
-        <v>327.6934327564664</v>
+        <v>306.3113655672684</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.119725053657967</v>
+        <v>0.1208451302285422</v>
       </c>
       <c r="T35">
-        <v>1.440936892423792</v>
+        <v>1.462769269581728</v>
       </c>
       <c r="U35">
         <v>0.1245366166625341</v>
       </c>
       <c r="V35">
-        <v>0.1495649705756983</v>
+        <v>0.1451660008528836</v>
       </c>
       <c r="W35">
-        <v>0.1059103012558052</v>
+        <v>0.1064581340618854</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.906454367125444</v>
+        <v>0.8797939445629308</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4593,22 +4593,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1159535515318789</v>
+        <v>0.1167409176985042</v>
       </c>
       <c r="C36">
-        <v>9729.677132561497</v>
+        <v>9400.713900817103</v>
       </c>
       <c r="D36">
-        <v>11113.06995776714</v>
+        <v>10989.72710323468</v>
       </c>
       <c r="E36">
-        <v>5651.755104012573</v>
+        <v>5857.375481224504</v>
       </c>
       <c r="F36">
-        <v>6991.092825205646</v>
+        <v>7196.713202417577</v>
       </c>
       <c r="G36">
         <v>5607.7</v>
@@ -4629,37 +4629,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M36">
-        <v>870.6470472248282</v>
+        <v>896.2543133196759</v>
       </c>
       <c r="N36">
-        <v>-104.6570472248283</v>
+        <v>-130.264313319676</v>
       </c>
       <c r="O36">
-        <v>-17.26841279209667</v>
+        <v>-21.49361169774655</v>
       </c>
       <c r="P36">
-        <v>-87.38863443273159</v>
+        <v>-108.7707016219295</v>
       </c>
       <c r="Q36">
-        <v>306.3113655672684</v>
+        <v>284.9292983780704</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1208451302285422</v>
+        <v>0.1219996706935967</v>
       </c>
       <c r="T36">
-        <v>1.462769269581728</v>
+        <v>1.485273412190677</v>
       </c>
       <c r="U36">
         <v>0.1245366166625341</v>
       </c>
       <c r="V36">
-        <v>0.1451660008528836</v>
+        <v>0.1410184008285155</v>
       </c>
       <c r="W36">
-        <v>0.1064581340618854</v>
+        <v>0.1069746621361897</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8797939445629308</v>
+        <v>0.8546569747182757</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4675,22 +4675,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1167409176985042</v>
+        <v>0.1175282838651296</v>
       </c>
       <c r="C37">
-        <v>9400.713900817103</v>
+        <v>9074.458554590685</v>
       </c>
       <c r="D37">
-        <v>10989.72710323468</v>
+        <v>10869.09213422019</v>
       </c>
       <c r="E37">
-        <v>5857.375481224504</v>
+        <v>6062.995858436434</v>
       </c>
       <c r="F37">
-        <v>7196.713202417577</v>
+        <v>7402.333579629508</v>
       </c>
       <c r="G37">
         <v>5607.7</v>
@@ -4711,37 +4711,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M37">
-        <v>896.2543133196759</v>
+        <v>921.8615794145238</v>
       </c>
       <c r="N37">
-        <v>-130.264313319676</v>
+        <v>-155.8715794145239</v>
       </c>
       <c r="O37">
-        <v>-21.49361169774655</v>
+        <v>-25.71881060339645</v>
       </c>
       <c r="P37">
-        <v>-108.7707016219295</v>
+        <v>-130.1527688111275</v>
       </c>
       <c r="Q37">
-        <v>284.9292983780704</v>
+        <v>263.5472311888724</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1219996706935967</v>
+        <v>0.1231902905481841</v>
       </c>
       <c r="T37">
-        <v>1.485273412190677</v>
+        <v>1.508480809256157</v>
       </c>
       <c r="U37">
         <v>0.1245366166625341</v>
       </c>
       <c r="V37">
-        <v>0.1410184008285155</v>
+        <v>0.1371012230277234</v>
       </c>
       <c r="W37">
-        <v>0.1069746621361897</v>
+        <v>0.1074624942063659</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8546569747182757</v>
+        <v>0.8309165031983237</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4757,22 +4757,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1175282838651296</v>
+        <v>0.1183156500317549</v>
       </c>
       <c r="C38">
-        <v>9074.458554590685</v>
+        <v>8750.822888200884</v>
       </c>
       <c r="D38">
-        <v>10869.09213422019</v>
+        <v>10751.07684504232</v>
       </c>
       <c r="E38">
-        <v>6062.995858436434</v>
+        <v>6268.616235648364</v>
       </c>
       <c r="F38">
-        <v>7402.333579629507</v>
+        <v>7607.953956841438</v>
       </c>
       <c r="G38">
         <v>5607.7</v>
@@ -4793,37 +4793,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M38">
-        <v>921.8615794145237</v>
+        <v>947.4688455093716</v>
       </c>
       <c r="N38">
-        <v>-155.8715794145238</v>
+        <v>-181.4788455093717</v>
       </c>
       <c r="O38">
-        <v>-25.71881060339643</v>
+        <v>-29.94400950904633</v>
       </c>
       <c r="P38">
-        <v>-130.1527688111274</v>
+        <v>-151.5348360003254</v>
       </c>
       <c r="Q38">
-        <v>263.5472311888726</v>
+        <v>242.1651639996746</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1231902905481841</v>
+        <v>0.1244187078584728</v>
       </c>
       <c r="T38">
-        <v>1.508480809256157</v>
+        <v>1.532424949085619</v>
       </c>
       <c r="U38">
         <v>0.1245366166625341</v>
       </c>
       <c r="V38">
-        <v>0.1371012230277234</v>
+        <v>0.1333957845675147</v>
       </c>
       <c r="W38">
-        <v>0.1074624942063659</v>
+        <v>0.1079239569754515</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8309165031983238</v>
+        <v>0.8084593004091799</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4839,22 +4839,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1183156500317549</v>
+        <v>0.1513614777443769</v>
       </c>
       <c r="C39">
-        <v>8750.822888200884</v>
+        <v>5179.59755037298</v>
       </c>
       <c r="D39">
-        <v>10751.07684504232</v>
+        <v>7385.471884426348</v>
       </c>
       <c r="E39">
-        <v>6268.616235648364</v>
+        <v>6474.236612860295</v>
       </c>
       <c r="F39">
-        <v>7607.953956841438</v>
+        <v>7813.574334053369</v>
       </c>
       <c r="G39">
         <v>5607.7</v>
@@ -4875,45 +4875,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M39">
-        <v>947.4688455093716</v>
+        <v>1615.351921863406</v>
       </c>
       <c r="N39">
-        <v>-181.4788455093717</v>
+        <v>-849.3619218634066</v>
       </c>
       <c r="O39">
-        <v>-29.94400950904633</v>
+        <v>-140.1447171074621</v>
       </c>
       <c r="P39">
-        <v>-151.5348360003254</v>
+        <v>-709.2172047559445</v>
       </c>
       <c r="Q39">
-        <v>242.1651639996746</v>
+        <v>-315.5172047559446</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1244187078584728</v>
+        <v>0.1273358830594104</v>
       </c>
       <c r="T39">
-        <v>1.532424949085619</v>
+        <v>1.589286123487239</v>
       </c>
       <c r="U39">
-        <v>0.1245366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V39">
-        <v>0.1333957845675147</v>
+        <v>0.07824199067049326</v>
       </c>
       <c r="W39">
-        <v>0.1079239569754515</v>
+        <v>0.1905611322303748</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.8084593004091799</v>
+        <v>0.4741938828514742</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4921,22 +4921,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1513614777443769</v>
+        <v>0.1529708439110022</v>
       </c>
       <c r="C40">
-        <v>5179.59755037298</v>
+        <v>4863.070809624069</v>
       </c>
       <c r="D40">
-        <v>7385.471884426348</v>
+        <v>7274.565520889369</v>
       </c>
       <c r="E40">
-        <v>6474.236612860295</v>
+        <v>6679.856990072227</v>
       </c>
       <c r="F40">
-        <v>7813.574334053369</v>
+        <v>8019.1947112653</v>
       </c>
       <c r="G40">
         <v>5607.7</v>
@@ -4957,37 +4957,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M40">
-        <v>1615.351921863406</v>
+        <v>1657.861182965075</v>
       </c>
       <c r="N40">
-        <v>-849.3619218634066</v>
+        <v>-891.8711829650753</v>
       </c>
       <c r="O40">
-        <v>-140.1447171074621</v>
+        <v>-147.1587451892374</v>
       </c>
       <c r="P40">
-        <v>-709.2172047559445</v>
+        <v>-744.7124377758378</v>
       </c>
       <c r="Q40">
-        <v>-315.5172047559446</v>
+        <v>-351.0124377758378</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1273358830594104</v>
+        <v>0.1286725368800564</v>
       </c>
       <c r="T40">
-        <v>1.589286123487239</v>
+        <v>1.615339994364079</v>
       </c>
       <c r="U40">
         <v>0.2067366166625341</v>
       </c>
       <c r="V40">
-        <v>0.07824199067049326</v>
+        <v>0.07623578578150624</v>
       </c>
       <c r="W40">
-        <v>0.1905611322303748</v>
+        <v>0.1909758882414558</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4741938828514742</v>
+        <v>0.4620350653424621</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5003,22 +5003,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1529708439110022</v>
+        <v>0.1545802100776275</v>
       </c>
       <c r="C41">
-        <v>4863.070809624069</v>
+        <v>4549.825712641292</v>
       </c>
       <c r="D41">
-        <v>7274.565520889369</v>
+        <v>7166.940801118523</v>
       </c>
       <c r="E41">
-        <v>6679.856990072227</v>
+        <v>6885.477367284158</v>
       </c>
       <c r="F41">
-        <v>8019.1947112653</v>
+        <v>8224.815088477231</v>
       </c>
       <c r="G41">
         <v>5607.7</v>
@@ -5039,37 +5039,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M41">
-        <v>1657.861182965075</v>
+        <v>1700.370444066744</v>
       </c>
       <c r="N41">
-        <v>-891.8711829650753</v>
+        <v>-934.380444066744</v>
       </c>
       <c r="O41">
-        <v>-147.1587451892374</v>
+        <v>-154.1727732710128</v>
       </c>
       <c r="P41">
-        <v>-744.7124377758378</v>
+        <v>-780.2076707957312</v>
       </c>
       <c r="Q41">
-        <v>-351.0124377758378</v>
+        <v>-386.5076707957313</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1286725368800564</v>
+        <v>0.1300537458280574</v>
       </c>
       <c r="T41">
-        <v>1.615339994364079</v>
+        <v>1.64226232760348</v>
       </c>
       <c r="U41">
         <v>0.2067366166625341</v>
       </c>
       <c r="V41">
-        <v>0.07623578578150624</v>
+        <v>0.07432989113696857</v>
       </c>
       <c r="W41">
-        <v>0.1909758882414558</v>
+        <v>0.1913699064519827</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4620350653424621</v>
+        <v>0.4504841887089005</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5085,22 +5085,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1545802100776275</v>
+        <v>0.1561895762442529</v>
       </c>
       <c r="C42">
-        <v>4549.825712641292</v>
+        <v>4239.718730480306</v>
       </c>
       <c r="D42">
-        <v>7166.940801118523</v>
+        <v>7062.454196169467</v>
       </c>
       <c r="E42">
-        <v>6885.477367284158</v>
+        <v>7091.097744496088</v>
       </c>
       <c r="F42">
-        <v>8224.815088477231</v>
+        <v>8430.435465689161</v>
       </c>
       <c r="G42">
         <v>5607.7</v>
@@ -5121,37 +5121,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M42">
-        <v>1700.370444066744</v>
+        <v>1742.879705168412</v>
       </c>
       <c r="N42">
-        <v>-934.380444066744</v>
+        <v>-976.8897051684122</v>
       </c>
       <c r="O42">
-        <v>-154.1727732710128</v>
+        <v>-161.186801352788</v>
       </c>
       <c r="P42">
-        <v>-780.2076707957312</v>
+        <v>-815.7029038156242</v>
       </c>
       <c r="Q42">
-        <v>-386.5076707957313</v>
+        <v>-422.0029038156242</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1300537458280574</v>
+        <v>0.1314817754183635</v>
       </c>
       <c r="T42">
-        <v>1.64226232760348</v>
+        <v>1.670097282308624</v>
       </c>
       <c r="U42">
         <v>0.2067366166625341</v>
       </c>
       <c r="V42">
-        <v>0.07432989113696857</v>
+        <v>0.0725169669628962</v>
       </c>
       <c r="W42">
-        <v>0.1913699064519827</v>
+        <v>0.1917447042619962</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4504841887089005</v>
+        <v>0.439496769472098</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5167,22 +5167,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1561895762442529</v>
+        <v>0.1577989424108782</v>
       </c>
       <c r="C43">
-        <v>4239.718730480306</v>
+        <v>3932.61458393992</v>
       </c>
       <c r="D43">
-        <v>7062.454196169467</v>
+        <v>6960.970426841012</v>
       </c>
       <c r="E43">
-        <v>7091.097744496088</v>
+        <v>7296.71812170802</v>
       </c>
       <c r="F43">
-        <v>8430.435465689161</v>
+        <v>8636.055842901093</v>
       </c>
       <c r="G43">
         <v>5607.7</v>
@@ -5203,37 +5203,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M43">
-        <v>1742.879705168412</v>
+        <v>1785.388966270081</v>
       </c>
       <c r="N43">
-        <v>-976.8897051684122</v>
+        <v>-1019.398966270081</v>
       </c>
       <c r="O43">
-        <v>-161.186801352788</v>
+        <v>-168.2008294345634</v>
       </c>
       <c r="P43">
-        <v>-815.7029038156242</v>
+        <v>-851.1981368355177</v>
       </c>
       <c r="Q43">
-        <v>-422.0029038156242</v>
+        <v>-457.4981368355178</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1314817754183635</v>
+        <v>0.1329590474083352</v>
       </c>
       <c r="T43">
-        <v>1.670097282308624</v>
+        <v>1.698892063038083</v>
       </c>
       <c r="U43">
         <v>0.2067366166625341</v>
       </c>
       <c r="V43">
-        <v>0.0725169669628962</v>
+        <v>0.07079037251139865</v>
       </c>
       <c r="W43">
-        <v>0.1917447042619962</v>
+        <v>0.1921016545572471</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.439496769472098</v>
+        <v>0.4290325606751433</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5249,22 +5249,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1577989424108782</v>
+        <v>0.1594083085775035</v>
       </c>
       <c r="C44">
-        <v>3932.614583939921</v>
+        <v>3628.385659236104</v>
       </c>
       <c r="D44">
-        <v>6960.970426841012</v>
+        <v>6862.361879349128</v>
       </c>
       <c r="E44">
-        <v>7296.718121708018</v>
+        <v>7502.338498919949</v>
       </c>
       <c r="F44">
-        <v>8636.055842901091</v>
+        <v>8841.676220113022</v>
       </c>
       <c r="G44">
         <v>5607.7</v>
@@ -5285,37 +5285,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M44">
-        <v>1785.388966270081</v>
+        <v>1827.898227371749</v>
       </c>
       <c r="N44">
-        <v>-1019.398966270081</v>
+        <v>-1061.908227371749</v>
       </c>
       <c r="O44">
-        <v>-168.2008294345633</v>
+        <v>-175.2148575163387</v>
       </c>
       <c r="P44">
-        <v>-851.1981368355173</v>
+        <v>-886.6933698554108</v>
       </c>
       <c r="Q44">
-        <v>-457.4981368355174</v>
+        <v>-492.9933698554108</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1329590474083352</v>
+        <v>0.1344881535032183</v>
       </c>
       <c r="T44">
-        <v>1.698892063038083</v>
+        <v>1.728697186951032</v>
       </c>
       <c r="U44">
         <v>0.2067366166625341</v>
       </c>
       <c r="V44">
-        <v>0.07079037251139866</v>
+        <v>0.06914408477857543</v>
       </c>
       <c r="W44">
-        <v>0.1921016545572471</v>
+        <v>0.192442002513184</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4290325606751434</v>
+        <v>0.4190550592640935</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1594083085775035</v>
+        <v>0.1610176747441289</v>
       </c>
       <c r="C45">
-        <v>3628.385659236104</v>
+        <v>3326.911472647354</v>
       </c>
       <c r="D45">
-        <v>6862.361879349128</v>
+        <v>6766.508069972309</v>
       </c>
       <c r="E45">
-        <v>7502.338498919949</v>
+        <v>7707.958876131881</v>
       </c>
       <c r="F45">
-        <v>8841.676220113022</v>
+        <v>9047.296597324954</v>
       </c>
       <c r="G45">
         <v>5607.7</v>
@@ -5367,37 +5367,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M45">
-        <v>1827.898227371749</v>
+        <v>1870.407488473418</v>
       </c>
       <c r="N45">
-        <v>-1061.908227371749</v>
+        <v>-1104.417488473418</v>
       </c>
       <c r="O45">
-        <v>-175.2148575163387</v>
+        <v>-182.228885598114</v>
       </c>
       <c r="P45">
-        <v>-886.6933698554108</v>
+        <v>-922.188602875304</v>
       </c>
       <c r="Q45">
-        <v>-492.9933698554108</v>
+        <v>-528.4886028753041</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1344881535032183</v>
+        <v>0.1360718705300615</v>
       </c>
       <c r="T45">
-        <v>1.728697186951032</v>
+        <v>1.759566779575157</v>
       </c>
       <c r="U45">
         <v>0.2067366166625341</v>
       </c>
       <c r="V45">
-        <v>0.06914408477857543</v>
+        <v>0.06757262830633508</v>
       </c>
       <c r="W45">
-        <v>0.192442002513184</v>
+        <v>0.1927668801074874</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4190550592640935</v>
+        <v>0.4095310806444551</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5413,22 +5413,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1610176747441289</v>
+        <v>0.1626270409107542</v>
       </c>
       <c r="C46">
-        <v>3326.911472647354</v>
+        <v>3028.078179409165</v>
       </c>
       <c r="D46">
-        <v>6766.508069972309</v>
+        <v>6673.295153946048</v>
       </c>
       <c r="E46">
-        <v>7707.958876131881</v>
+        <v>7913.579253343811</v>
       </c>
       <c r="F46">
-        <v>9047.296597324954</v>
+        <v>9252.916974536884</v>
       </c>
       <c r="G46">
         <v>5607.7</v>
@@ -5449,37 +5449,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M46">
-        <v>1870.407488473418</v>
+        <v>1912.916749575086</v>
       </c>
       <c r="N46">
-        <v>-1104.417488473418</v>
+        <v>-1146.926749575086</v>
       </c>
       <c r="O46">
-        <v>-182.228885598114</v>
+        <v>-189.2429136798893</v>
       </c>
       <c r="P46">
-        <v>-922.188602875304</v>
+        <v>-957.6838358951971</v>
       </c>
       <c r="Q46">
-        <v>-528.4886028753041</v>
+        <v>-563.9838358951972</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1360718705300615</v>
+        <v>0.1377131772669717</v>
       </c>
       <c r="T46">
-        <v>1.759566779575157</v>
+        <v>1.79155890284016</v>
       </c>
       <c r="U46">
         <v>0.2067366166625341</v>
       </c>
       <c r="V46">
-        <v>0.06757262830633508</v>
+        <v>0.06607101434397208</v>
       </c>
       <c r="W46">
-        <v>0.1927668801074874</v>
+        <v>0.1930773186975995</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4095310806444551</v>
+        <v>0.4004303899634672</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5495,22 +5495,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1626270409107542</v>
+        <v>0.1642364070773796</v>
       </c>
       <c r="C47">
-        <v>3028.078179409165</v>
+        <v>2731.778122648622</v>
       </c>
       <c r="D47">
-        <v>6673.295153946048</v>
+        <v>6582.615474397438</v>
       </c>
       <c r="E47">
-        <v>7913.579253343811</v>
+        <v>8119.199630555742</v>
       </c>
       <c r="F47">
-        <v>9252.916974536884</v>
+        <v>9458.537351748815</v>
       </c>
       <c r="G47">
         <v>5607.7</v>
@@ -5531,37 +5531,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M47">
-        <v>1912.916749575086</v>
+        <v>1955.426010676755</v>
       </c>
       <c r="N47">
-        <v>-1146.926749575086</v>
+        <v>-1189.436010676755</v>
       </c>
       <c r="O47">
-        <v>-189.2429136798893</v>
+        <v>-196.2569417616646</v>
       </c>
       <c r="P47">
-        <v>-957.6838358951971</v>
+        <v>-993.1790689150907</v>
       </c>
       <c r="Q47">
-        <v>-563.9838358951972</v>
+        <v>-599.4790689150908</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1377131772669717</v>
+        <v>0.139415273142286</v>
       </c>
       <c r="T47">
-        <v>1.79155890284016</v>
+        <v>1.824735919559422</v>
       </c>
       <c r="U47">
         <v>0.2067366166625341</v>
       </c>
       <c r="V47">
-        <v>0.06607101434397208</v>
+        <v>0.06463468794519008</v>
       </c>
       <c r="W47">
-        <v>0.1930773186975995</v>
+        <v>0.1933742599577068</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4004303899634672</v>
+        <v>0.3917253814860004</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5577,22 +5577,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1642364070773796</v>
+        <v>0.1658457732440049</v>
       </c>
       <c r="C48">
-        <v>2731.778122648622</v>
+        <v>2437.909418601672</v>
       </c>
       <c r="D48">
-        <v>6582.615474397438</v>
+        <v>6494.367147562418</v>
       </c>
       <c r="E48">
-        <v>8119.199630555742</v>
+        <v>8324.820007767674</v>
       </c>
       <c r="F48">
-        <v>9458.537351748815</v>
+        <v>9664.157728960747</v>
       </c>
       <c r="G48">
         <v>5607.7</v>
@@ -5613,37 +5613,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M48">
-        <v>1955.426010676755</v>
+        <v>1997.935271778424</v>
       </c>
       <c r="N48">
-        <v>-1189.436010676755</v>
+        <v>-1231.945271778424</v>
       </c>
       <c r="O48">
-        <v>-196.2569417616646</v>
+        <v>-203.27096984344</v>
       </c>
       <c r="P48">
-        <v>-993.1790689150907</v>
+        <v>-1028.674301934984</v>
       </c>
       <c r="Q48">
-        <v>-599.4790689150908</v>
+        <v>-634.9743019349843</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.139415273142286</v>
+        <v>0.141181599050631</v>
       </c>
       <c r="T48">
-        <v>1.824735919559422</v>
+        <v>1.859164899173751</v>
       </c>
       <c r="U48">
         <v>0.2067366166625341</v>
       </c>
       <c r="V48">
-        <v>0.06463468794519008</v>
+        <v>0.06325948181869666</v>
       </c>
       <c r="W48">
-        <v>0.1933742599577068</v>
+        <v>0.1936585654195117</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3917253814860004</v>
+        <v>0.3833907989011918</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5659,22 +5659,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1658457732440049</v>
+        <v>0.1674551394106302</v>
       </c>
       <c r="C49">
-        <v>2437.909418601672</v>
+        <v>2146.375574753109</v>
       </c>
       <c r="D49">
-        <v>6494.367147562418</v>
+        <v>6408.453680925786</v>
       </c>
       <c r="E49">
-        <v>8324.820007767674</v>
+        <v>8530.440384979604</v>
       </c>
       <c r="F49">
-        <v>9664.157728960747</v>
+        <v>9869.778106172676</v>
       </c>
       <c r="G49">
         <v>5607.7</v>
@@ -5695,37 +5695,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M49">
-        <v>1997.935271778424</v>
+        <v>2040.444532880092</v>
       </c>
       <c r="N49">
-        <v>-1231.945271778424</v>
+        <v>-1274.454532880092</v>
       </c>
       <c r="O49">
-        <v>-203.27096984344</v>
+        <v>-210.2849979252152</v>
       </c>
       <c r="P49">
-        <v>-1028.674301934984</v>
+        <v>-1064.169534954877</v>
       </c>
       <c r="Q49">
-        <v>-634.9743019349843</v>
+        <v>-670.4695349548771</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.141181599050631</v>
+        <v>0.1430158605708354</v>
       </c>
       <c r="T49">
-        <v>1.859164899173751</v>
+        <v>1.894918070311708</v>
       </c>
       <c r="U49">
         <v>0.2067366166625341</v>
       </c>
       <c r="V49">
-        <v>0.06325948181869666</v>
+        <v>0.06194157594747383</v>
       </c>
       <c r="W49">
-        <v>0.1936585654195117</v>
+        <v>0.1939310248204079</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3833907989011918</v>
+        <v>0.3754034905907505</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5741,22 +5741,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1674551394106302</v>
+        <v>0.1690645055772556</v>
       </c>
       <c r="C50">
-        <v>2146.375574753109</v>
+        <v>1857.085137890443</v>
       </c>
       <c r="D50">
-        <v>6408.453680925786</v>
+        <v>6324.783621275048</v>
       </c>
       <c r="E50">
-        <v>8530.440384979604</v>
+        <v>8736.060762191533</v>
       </c>
       <c r="F50">
-        <v>9869.778106172676</v>
+        <v>10075.39848338461</v>
       </c>
       <c r="G50">
         <v>5607.7</v>
@@ -5777,37 +5777,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M50">
-        <v>2040.444532880092</v>
+        <v>2082.953793981761</v>
       </c>
       <c r="N50">
-        <v>-1274.454532880092</v>
+        <v>-1316.963793981761</v>
       </c>
       <c r="O50">
-        <v>-210.2849979252152</v>
+        <v>-217.2990260069905</v>
       </c>
       <c r="P50">
-        <v>-1064.169534954877</v>
+        <v>-1099.66476797477</v>
       </c>
       <c r="Q50">
-        <v>-670.4695349548771</v>
+        <v>-705.9647679747703</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1430158605708354</v>
+        <v>0.1449220539153616</v>
       </c>
       <c r="T50">
-        <v>1.894918070311708</v>
+        <v>1.93207332659233</v>
       </c>
       <c r="U50">
         <v>0.2067366166625341</v>
       </c>
       <c r="V50">
-        <v>0.06194157594747383</v>
+        <v>0.06067746215262743</v>
       </c>
       <c r="W50">
-        <v>0.1939310248204079</v>
+        <v>0.1941923634294309</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3754034905907505</v>
+        <v>0.3677421948644086</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5823,22 +5823,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1690645055772556</v>
+        <v>0.1706738717438809</v>
       </c>
       <c r="C51">
-        <v>1857.085137890443</v>
+        <v>1569.951369372895</v>
       </c>
       <c r="D51">
-        <v>6324.783621275048</v>
+        <v>6243.270229969432</v>
       </c>
       <c r="E51">
-        <v>8736.060762191533</v>
+        <v>8941.681139403465</v>
       </c>
       <c r="F51">
-        <v>10075.39848338461</v>
+        <v>10281.01886059654</v>
       </c>
       <c r="G51">
         <v>5607.7</v>
@@ -5859,37 +5859,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M51">
-        <v>2082.953793981761</v>
+        <v>2125.463055083429</v>
       </c>
       <c r="N51">
-        <v>-1316.963793981761</v>
+        <v>-1359.47305508343</v>
       </c>
       <c r="O51">
-        <v>-217.2990260069905</v>
+        <v>-224.3130540887659</v>
       </c>
       <c r="P51">
-        <v>-1099.66476797477</v>
+        <v>-1135.160000994664</v>
       </c>
       <c r="Q51">
-        <v>-705.9647679747703</v>
+        <v>-741.4600009946638</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1449220539153616</v>
+        <v>0.1469044949936689</v>
       </c>
       <c r="T51">
-        <v>1.93207332659233</v>
+        <v>1.970714793124176</v>
       </c>
       <c r="U51">
         <v>0.2067366166625341</v>
       </c>
       <c r="V51">
-        <v>0.06067746215262743</v>
+        <v>0.05946391290957487</v>
       </c>
       <c r="W51">
-        <v>0.1941923634294309</v>
+        <v>0.194443248494093</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3677421948644086</v>
+        <v>0.3603873509671204</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5905,22 +5905,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1706738717438809</v>
+        <v>0.1722832379105063</v>
       </c>
       <c r="C52">
-        <v>1569.951369372895</v>
+        <v>1284.891945191584</v>
       </c>
       <c r="D52">
-        <v>6243.270229969432</v>
+        <v>6163.831183000053</v>
       </c>
       <c r="E52">
-        <v>8941.681139403465</v>
+        <v>9147.301516615396</v>
       </c>
       <c r="F52">
-        <v>10281.01886059654</v>
+        <v>10486.63923780847</v>
       </c>
       <c r="G52">
         <v>5607.7</v>
@@ -5941,37 +5941,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M52">
-        <v>2125.463055083429</v>
+        <v>2167.972316185098</v>
       </c>
       <c r="N52">
-        <v>-1359.47305508343</v>
+        <v>-1401.982316185099</v>
       </c>
       <c r="O52">
-        <v>-224.3130540887659</v>
+        <v>-231.3270821705413</v>
       </c>
       <c r="P52">
-        <v>-1135.160000994664</v>
+        <v>-1170.655234014557</v>
       </c>
       <c r="Q52">
-        <v>-741.4600009946638</v>
+        <v>-776.9552340145575</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1469044949936689</v>
+        <v>0.148967852034356</v>
       </c>
       <c r="T52">
-        <v>1.970714793124176</v>
+        <v>2.010933462371608</v>
       </c>
       <c r="U52">
         <v>0.2067366166625341</v>
       </c>
       <c r="V52">
-        <v>0.05946391290957487</v>
+        <v>0.05829795383291653</v>
       </c>
       <c r="W52">
-        <v>0.194443248494093</v>
+        <v>0.1946842949287683</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3603873509671204</v>
+        <v>0.3533209323207062</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5987,22 +5987,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1722832379105063</v>
+        <v>0.1738926040771316</v>
       </c>
       <c r="C53">
-        <v>1284.891945191584</v>
+        <v>1001.828678640491</v>
       </c>
       <c r="D53">
-        <v>6163.831183000053</v>
+        <v>6086.38829366089</v>
       </c>
       <c r="E53">
-        <v>9147.301516615396</v>
+        <v>9352.921893827326</v>
       </c>
       <c r="F53">
-        <v>10486.63923780847</v>
+        <v>10692.2596150204</v>
       </c>
       <c r="G53">
         <v>5607.7</v>
@@ -6023,37 +6023,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M53">
-        <v>2167.972316185098</v>
+        <v>2210.481577286766</v>
       </c>
       <c r="N53">
-        <v>-1401.982316185099</v>
+        <v>-1444.491577286767</v>
       </c>
       <c r="O53">
-        <v>-231.3270821705413</v>
+        <v>-238.3411102523165</v>
       </c>
       <c r="P53">
-        <v>-1170.655234014557</v>
+        <v>-1206.15046703445</v>
       </c>
       <c r="Q53">
-        <v>-776.9552340145575</v>
+        <v>-812.4504670344503</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.148967852034356</v>
+        <v>0.1511171822850717</v>
       </c>
       <c r="T53">
-        <v>2.010933462371608</v>
+        <v>2.05282790950435</v>
       </c>
       <c r="U53">
         <v>0.2067366166625341</v>
       </c>
       <c r="V53">
-        <v>0.05829795383291653</v>
+        <v>0.05717683933612969</v>
       </c>
       <c r="W53">
-        <v>0.1946842949287683</v>
+        <v>0.1949160703467253</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3533209323207062</v>
+        <v>0.3465262990068465</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6069,22 +6069,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1738926040771316</v>
+        <v>0.175501970243757</v>
       </c>
       <c r="C54">
-        <v>1001.828678640491</v>
+        <v>720.6872636343469</v>
       </c>
       <c r="D54">
-        <v>6086.38829366089</v>
+        <v>6010.867255866679</v>
       </c>
       <c r="E54">
-        <v>9352.921893827326</v>
+        <v>9558.542271039258</v>
       </c>
       <c r="F54">
-        <v>10692.2596150204</v>
+        <v>10897.87999223233</v>
       </c>
       <c r="G54">
         <v>5607.7</v>
@@ -6105,37 +6105,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M54">
-        <v>2210.481577286766</v>
+        <v>2252.990838388435</v>
       </c>
       <c r="N54">
-        <v>-1444.491577286767</v>
+        <v>-1487.000838388436</v>
       </c>
       <c r="O54">
-        <v>-238.3411102523165</v>
+        <v>-245.3551383340919</v>
       </c>
       <c r="P54">
-        <v>-1206.15046703445</v>
+        <v>-1241.645700054344</v>
       </c>
       <c r="Q54">
-        <v>-812.4504670344503</v>
+        <v>-847.9457000543438</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1511171822850717</v>
+        <v>0.1533579733975201</v>
       </c>
       <c r="T54">
-        <v>2.05282790950435</v>
+        <v>2.096505099068273</v>
       </c>
       <c r="U54">
         <v>0.2067366166625341</v>
       </c>
       <c r="V54">
-        <v>0.05717683933612969</v>
+        <v>0.05609803104676874</v>
       </c>
       <c r="W54">
-        <v>0.1949160703467253</v>
+        <v>0.1951390995224953</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3465262990068465</v>
+        <v>0.3399880669501135</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6151,22 +6151,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.175501970243757</v>
+        <v>0.1771113364103823</v>
       </c>
       <c r="C55">
-        <v>720.6872636343469</v>
+        <v>441.3970369020735</v>
       </c>
       <c r="D55">
-        <v>6010.867255866679</v>
+        <v>5937.197406346336</v>
       </c>
       <c r="E55">
-        <v>9558.542271039258</v>
+        <v>9764.162648251189</v>
       </c>
       <c r="F55">
-        <v>10897.87999223233</v>
+        <v>11103.50036944426</v>
       </c>
       <c r="G55">
         <v>5607.7</v>
@@ -6187,37 +6187,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M55">
-        <v>2252.990838388435</v>
+        <v>2295.500099490104</v>
       </c>
       <c r="N55">
-        <v>-1487.000838388436</v>
+        <v>-1529.510099490104</v>
       </c>
       <c r="O55">
-        <v>-245.3551383340919</v>
+        <v>-252.3691664158673</v>
       </c>
       <c r="P55">
-        <v>-1241.645700054344</v>
+        <v>-1277.140933074237</v>
       </c>
       <c r="Q55">
-        <v>-847.9457000543438</v>
+        <v>-883.4409330742373</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1533579733975201</v>
+        <v>0.1556961902105096</v>
       </c>
       <c r="T55">
-        <v>2.096505099068273</v>
+        <v>2.142081296874105</v>
       </c>
       <c r="U55">
         <v>0.2067366166625341</v>
       </c>
       <c r="V55">
-        <v>0.05609803104676874</v>
+        <v>0.05505917861997672</v>
       </c>
       <c r="W55">
-        <v>0.1951390995224953</v>
+        <v>0.195353868358422</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3399880669501135</v>
+        <v>0.3336919916362225</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6233,22 +6233,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1771113364103823</v>
+        <v>0.1787207025770076</v>
       </c>
       <c r="C56">
-        <v>441.3970369020735</v>
+        <v>163.8907574559616</v>
       </c>
       <c r="D56">
-        <v>5937.197406346336</v>
+        <v>5865.311504112154</v>
       </c>
       <c r="E56">
-        <v>9764.162648251189</v>
+        <v>9969.783025463119</v>
       </c>
       <c r="F56">
-        <v>11103.50036944426</v>
+        <v>11309.12074665619</v>
       </c>
       <c r="G56">
         <v>5607.7</v>
@@ -6269,37 +6269,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M56">
-        <v>2295.500099490104</v>
+        <v>2338.009360591772</v>
       </c>
       <c r="N56">
-        <v>-1529.510099490104</v>
+        <v>-1572.019360591773</v>
       </c>
       <c r="O56">
-        <v>-252.3691664158673</v>
+        <v>-259.3831944976425</v>
       </c>
       <c r="P56">
-        <v>-1277.140933074237</v>
+        <v>-1312.63616609413</v>
       </c>
       <c r="Q56">
-        <v>-883.4409330742373</v>
+        <v>-918.93616609413</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1556961902105096</v>
+        <v>0.1581383277707432</v>
       </c>
       <c r="T56">
-        <v>2.142081296874105</v>
+        <v>2.189683103471307</v>
       </c>
       <c r="U56">
         <v>0.2067366166625341</v>
       </c>
       <c r="V56">
-        <v>0.05505917861997672</v>
+        <v>0.05405810264506807</v>
       </c>
       <c r="W56">
-        <v>0.195353868358422</v>
+        <v>0.1955608274184967</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3336919916362225</v>
+        <v>0.3276248645155639</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6315,22 +6315,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1787207025770076</v>
+        <v>0.180330068743633</v>
       </c>
       <c r="C57">
-        <v>163.8907574559616</v>
+        <v>-111.8955981100353</v>
       </c>
       <c r="D57">
-        <v>5865.311504112154</v>
+        <v>5795.145525758088</v>
       </c>
       <c r="E57">
-        <v>9969.783025463119</v>
+        <v>10175.40340267505</v>
       </c>
       <c r="F57">
-        <v>11309.12074665619</v>
+        <v>11514.74112386812</v>
       </c>
       <c r="G57">
         <v>5607.7</v>
@@ -6351,37 +6351,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M57">
-        <v>2338.009360591772</v>
+        <v>2380.518621693441</v>
       </c>
       <c r="N57">
-        <v>-1572.019360591773</v>
+        <v>-1614.528621693441</v>
       </c>
       <c r="O57">
-        <v>-259.3831944976425</v>
+        <v>-266.3972225794179</v>
       </c>
       <c r="P57">
-        <v>-1312.63616609413</v>
+        <v>-1348.131399114024</v>
       </c>
       <c r="Q57">
-        <v>-918.93616609413</v>
+        <v>-954.4313991140237</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1581383277707432</v>
+        <v>0.1606914715837146</v>
       </c>
       <c r="T57">
-        <v>2.189683103471307</v>
+        <v>2.2394486285502</v>
       </c>
       <c r="U57">
         <v>0.2067366166625341</v>
       </c>
       <c r="V57">
-        <v>0.05405810264506807</v>
+        <v>0.05309277938354898</v>
       </c>
       <c r="W57">
-        <v>0.1955608274184967</v>
+        <v>0.1957603950835688</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3276248645155639</v>
+        <v>0.3217744205063574</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.180330068743633</v>
+        <v>0.1819394349102583</v>
       </c>
       <c r="C58">
-        <v>-111.8955981100353</v>
+        <v>-386.0230258027696</v>
       </c>
       <c r="D58">
-        <v>5795.145525758088</v>
+        <v>5726.638475277286</v>
       </c>
       <c r="E58">
-        <v>10175.40340267505</v>
+        <v>10381.02377988698</v>
       </c>
       <c r="F58">
-        <v>11514.74112386812</v>
+        <v>11720.36150108005</v>
       </c>
       <c r="G58">
         <v>5607.7</v>
@@ -6433,37 +6433,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M58">
-        <v>2380.518621693441</v>
+        <v>2423.02788279511</v>
       </c>
       <c r="N58">
-        <v>-1614.528621693441</v>
+        <v>-1657.03788279511</v>
       </c>
       <c r="O58">
-        <v>-266.3972225794179</v>
+        <v>-273.4112506611932</v>
       </c>
       <c r="P58">
-        <v>-1348.131399114024</v>
+        <v>-1383.626632133917</v>
       </c>
       <c r="Q58">
-        <v>-954.4313991140237</v>
+        <v>-989.9266321339172</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1606914715837146</v>
+        <v>0.163363366271708</v>
       </c>
       <c r="T58">
-        <v>2.2394486285502</v>
+        <v>2.291528829214159</v>
       </c>
       <c r="U58">
         <v>0.2067366166625341</v>
       </c>
       <c r="V58">
-        <v>0.05309277938354898</v>
+        <v>0.05216132711366216</v>
       </c>
       <c r="W58">
-        <v>0.1957603950835688</v>
+        <v>0.1959529603744279</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3217744205063574</v>
+        <v>0.316129255234316</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6479,22 +6479,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1819394349102583</v>
+        <v>0.1835488010768836</v>
       </c>
       <c r="C59">
-        <v>-386.0230258027696</v>
+        <v>-658.5496710805983</v>
       </c>
       <c r="D59">
-        <v>5726.638475277286</v>
+        <v>5659.732207211386</v>
       </c>
       <c r="E59">
-        <v>10381.02377988698</v>
+        <v>10586.64415709891</v>
       </c>
       <c r="F59">
-        <v>11720.36150108005</v>
+        <v>11925.98187829198</v>
       </c>
       <c r="G59">
         <v>5607.7</v>
@@ -6515,37 +6515,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M59">
-        <v>2423.02788279511</v>
+        <v>2465.537143896778</v>
       </c>
       <c r="N59">
-        <v>-1657.03788279511</v>
+        <v>-1699.547143896778</v>
       </c>
       <c r="O59">
-        <v>-273.4112506611932</v>
+        <v>-280.4252787429684</v>
       </c>
       <c r="P59">
-        <v>-1383.626632133917</v>
+        <v>-1419.12186515381</v>
       </c>
       <c r="Q59">
-        <v>-989.9266321339172</v>
+        <v>-1025.42186515381</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.163363366271708</v>
+        <v>0.166162494040082</v>
       </c>
       <c r="T59">
-        <v>2.291528829214159</v>
+        <v>2.346089039433543</v>
       </c>
       <c r="U59">
         <v>0.2067366166625341</v>
       </c>
       <c r="V59">
-        <v>0.05216132711366216</v>
+        <v>0.05126199388756454</v>
       </c>
       <c r="W59">
-        <v>0.1959529603744279</v>
+        <v>0.1961388854828435</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.316129255234316</v>
+        <v>0.3106787508337244</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6561,22 +6561,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1835488010768836</v>
+        <v>0.185158167243509</v>
       </c>
       <c r="C60">
-        <v>-658.5496710805965</v>
+        <v>-929.5309934499801</v>
       </c>
       <c r="D60">
-        <v>5659.732207211386</v>
+        <v>5594.371262053935</v>
       </c>
       <c r="E60">
-        <v>10586.64415709891</v>
+        <v>10792.26453431084</v>
       </c>
       <c r="F60">
-        <v>11925.98187829198</v>
+        <v>12131.60225550391</v>
       </c>
       <c r="G60">
         <v>5607.7</v>
@@ -6597,37 +6597,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M60">
-        <v>2465.537143896778</v>
+        <v>2508.046404998447</v>
       </c>
       <c r="N60">
-        <v>-1699.547143896778</v>
+        <v>-1742.056404998447</v>
       </c>
       <c r="O60">
-        <v>-280.4252787429684</v>
+        <v>-287.4393068247438</v>
       </c>
       <c r="P60">
-        <v>-1419.12186515381</v>
+        <v>-1454.617098173703</v>
       </c>
       <c r="Q60">
-        <v>-1025.42186515381</v>
+        <v>-1060.917098173703</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.166162494040082</v>
+        <v>0.1690981646264254</v>
       </c>
       <c r="T60">
-        <v>2.346089039433543</v>
+        <v>2.403310723322166</v>
       </c>
       <c r="U60">
         <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.05126199388756454</v>
+        <v>0.05039314653353803</v>
       </c>
       <c r="W60">
-        <v>0.1961388854828435</v>
+        <v>0.1963185080452111</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3106787508337244</v>
+        <v>0.3054130092941698</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6643,22 +6643,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.185158167243509</v>
+        <v>0.1867675334101343</v>
       </c>
       <c r="C61">
-        <v>-929.5309934499801</v>
+        <v>-1199.019919787303</v>
       </c>
       <c r="D61">
-        <v>5594.371262053935</v>
+        <v>5530.502712928542</v>
       </c>
       <c r="E61">
-        <v>10792.26453431084</v>
+        <v>10997.88491152277</v>
       </c>
       <c r="F61">
-        <v>12131.60225550391</v>
+        <v>12337.22263271584</v>
       </c>
       <c r="G61">
         <v>5607.7</v>
@@ -6679,37 +6679,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M61">
-        <v>2508.046404998447</v>
+        <v>2550.555666100115</v>
       </c>
       <c r="N61">
-        <v>-1742.056404998447</v>
+        <v>-1784.565666100115</v>
       </c>
       <c r="O61">
-        <v>-287.4393068247438</v>
+        <v>-294.453334906519</v>
       </c>
       <c r="P61">
-        <v>-1454.617098173703</v>
+        <v>-1490.112331193596</v>
       </c>
       <c r="Q61">
-        <v>-1060.917098173703</v>
+        <v>-1096.412331193596</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1690981646264254</v>
+        <v>0.1721806187420861</v>
       </c>
       <c r="T61">
-        <v>2.403310723322166</v>
+        <v>2.46339349140522</v>
       </c>
       <c r="U61">
         <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.05039314653353803</v>
+        <v>0.04955326075797906</v>
       </c>
       <c r="W61">
-        <v>0.1963185080452111</v>
+        <v>0.1964921431888332</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3054130092941698</v>
+        <v>0.3003227924726003</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6725,22 +6725,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1867675334101343</v>
+        <v>0.1883768995767597</v>
       </c>
       <c r="C62">
-        <v>-1199.019919787303</v>
+        <v>-1467.066987276819</v>
       </c>
       <c r="D62">
-        <v>5530.502712928542</v>
+        <v>5468.076022650956</v>
       </c>
       <c r="E62">
-        <v>10997.88491152277</v>
+        <v>11203.5052887347</v>
       </c>
       <c r="F62">
-        <v>12337.22263271584</v>
+        <v>12542.84300992778</v>
       </c>
       <c r="G62">
         <v>5607.7</v>
@@ -6761,37 +6761,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M62">
-        <v>2550.555666100115</v>
+        <v>2593.064927201784</v>
       </c>
       <c r="N62">
-        <v>-1784.565666100115</v>
+        <v>-1827.074927201784</v>
       </c>
       <c r="O62">
-        <v>-294.453334906519</v>
+        <v>-301.4673629882944</v>
       </c>
       <c r="P62">
-        <v>-1490.112331193596</v>
+        <v>-1525.60756421349</v>
       </c>
       <c r="Q62">
-        <v>-1096.412331193596</v>
+        <v>-1131.90756421349</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1721806187420861</v>
+        <v>0.1754211474277806</v>
       </c>
       <c r="T62">
-        <v>2.46339349140522</v>
+        <v>2.526557427082277</v>
       </c>
       <c r="U62">
         <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.04955326075797906</v>
+        <v>0.04874091222096301</v>
       </c>
       <c r="W62">
-        <v>0.1964921431888332</v>
+        <v>0.1966600853769266</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3003227924726003</v>
+        <v>0.2953994680058364</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6807,22 +6807,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1883768995767597</v>
+        <v>0.189986265743385</v>
       </c>
       <c r="C63">
-        <v>-1467.066987276819</v>
+        <v>-1733.720476775963</v>
       </c>
       <c r="D63">
-        <v>5468.076022650956</v>
+        <v>5407.042910363745</v>
       </c>
       <c r="E63">
-        <v>11203.5052887347</v>
+        <v>11409.12566594663</v>
       </c>
       <c r="F63">
-        <v>12542.84300992778</v>
+        <v>12748.46338713971</v>
       </c>
       <c r="G63">
         <v>5607.7</v>
@@ -6843,37 +6843,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M63">
-        <v>2593.064927201784</v>
+        <v>2635.574188303453</v>
       </c>
       <c r="N63">
-        <v>-1827.074927201784</v>
+        <v>-1869.584188303453</v>
       </c>
       <c r="O63">
-        <v>-301.4673629882944</v>
+        <v>-308.4813910700697</v>
       </c>
       <c r="P63">
-        <v>-1525.60756421349</v>
+        <v>-1561.102797233383</v>
       </c>
       <c r="Q63">
-        <v>-1131.90756421349</v>
+        <v>-1167.402797233383</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1754211474277806</v>
+        <v>0.1788322302548274</v>
       </c>
       <c r="T63">
-        <v>2.526557427082277</v>
+        <v>2.593045780426547</v>
       </c>
       <c r="U63">
         <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.04874091222096301</v>
+        <v>0.04795476847546361</v>
       </c>
       <c r="W63">
-        <v>0.1966600853769266</v>
+        <v>0.1968226100750816</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2953994680058364</v>
+        <v>0.2906349604573552</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6889,22 +6889,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.189986265743385</v>
+        <v>0.1915956319100104</v>
       </c>
       <c r="C64">
-        <v>-1733.720476775963</v>
+        <v>-1999.026537347747</v>
       </c>
       <c r="D64">
-        <v>5407.042910363745</v>
+        <v>5347.35722700389</v>
       </c>
       <c r="E64">
-        <v>11409.12566594663</v>
+        <v>11614.74604315856</v>
       </c>
       <c r="F64">
-        <v>12748.46338713971</v>
+        <v>12954.08376435164</v>
       </c>
       <c r="G64">
         <v>5607.7</v>
@@ -6925,37 +6925,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M64">
-        <v>2635.574188303453</v>
+        <v>2678.083449405121</v>
       </c>
       <c r="N64">
-        <v>-1869.584188303453</v>
+        <v>-1912.093449405121</v>
       </c>
       <c r="O64">
-        <v>-308.4813910700697</v>
+        <v>-315.495419151845</v>
       </c>
       <c r="P64">
-        <v>-1561.102797233383</v>
+        <v>-1596.598030253276</v>
       </c>
       <c r="Q64">
-        <v>-1167.402797233383</v>
+        <v>-1202.898030253276</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1788322302548274</v>
+        <v>0.1824276959373903</v>
       </c>
       <c r="T64">
-        <v>2.593045780426547</v>
+        <v>2.663128098816454</v>
       </c>
       <c r="U64">
         <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.04795476847546361</v>
+        <v>0.04719358167426578</v>
       </c>
       <c r="W64">
-        <v>0.1968226100750816</v>
+        <v>0.1969799752590094</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2906349604573552</v>
+        <v>0.2860217071167622</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6971,22 +6971,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1915956319100104</v>
+        <v>0.1932049980766357</v>
       </c>
       <c r="C65">
-        <v>-1999.026537347747</v>
+        <v>-2263.029302635321</v>
       </c>
       <c r="D65">
-        <v>5347.35722700389</v>
+        <v>5288.974838928248</v>
       </c>
       <c r="E65">
-        <v>11614.74604315856</v>
+        <v>11820.3664203705</v>
       </c>
       <c r="F65">
-        <v>12954.08376435164</v>
+        <v>13159.70414156357</v>
       </c>
       <c r="G65">
         <v>5607.7</v>
@@ -7007,37 +7007,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M65">
-        <v>2678.083449405121</v>
+        <v>2720.59271050679</v>
       </c>
       <c r="N65">
-        <v>-1912.093449405121</v>
+        <v>-1954.60271050679</v>
       </c>
       <c r="O65">
-        <v>-315.495419151845</v>
+        <v>-322.5094472336204</v>
       </c>
       <c r="P65">
-        <v>-1596.598030253276</v>
+        <v>-1632.09326327317</v>
       </c>
       <c r="Q65">
-        <v>-1202.898030253276</v>
+        <v>-1238.39326327317</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1824276959373903</v>
+        <v>0.186222909713429</v>
       </c>
       <c r="T65">
-        <v>2.663128098816454</v>
+        <v>2.737103879339133</v>
       </c>
       <c r="U65">
         <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.04719358167426578</v>
+        <v>0.04645618196060537</v>
       </c>
       <c r="W65">
-        <v>0.1969799752590094</v>
+        <v>0.1971324227809395</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2860217071167622</v>
+        <v>0.2815526179430627</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7053,22 +7053,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1932049980766357</v>
+        <v>0.194814364243261</v>
       </c>
       <c r="C66">
-        <v>-2263.029302635321</v>
+        <v>-2525.770999695376</v>
       </c>
       <c r="D66">
-        <v>5288.974838928248</v>
+        <v>5231.853519080125</v>
       </c>
       <c r="E66">
-        <v>11820.3664203705</v>
+        <v>12025.98679758243</v>
       </c>
       <c r="F66">
-        <v>13159.70414156357</v>
+        <v>13365.3245187755</v>
       </c>
       <c r="G66">
         <v>5607.7</v>
@@ -7089,37 +7089,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M66">
-        <v>2720.59271050679</v>
+        <v>2763.101971608458</v>
       </c>
       <c r="N66">
-        <v>-1954.60271050679</v>
+        <v>-1997.111971608459</v>
       </c>
       <c r="O66">
-        <v>-322.5094472336204</v>
+        <v>-329.5234753153957</v>
       </c>
       <c r="P66">
-        <v>-1632.09326327317</v>
+        <v>-1667.588496293063</v>
       </c>
       <c r="Q66">
-        <v>-1238.39326327317</v>
+        <v>-1273.888496293063</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.186222909713429</v>
+        <v>0.1902349928480984</v>
       </c>
       <c r="T66">
-        <v>2.737103879339133</v>
+        <v>2.815306847320252</v>
       </c>
       <c r="U66">
         <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.04645618196060537</v>
+        <v>0.04574147146890375</v>
       </c>
       <c r="W66">
-        <v>0.1971324227809395</v>
+        <v>0.1972801796098871</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2815526179430627</v>
+        <v>0.2772210392054772</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7135,22 +7135,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.194814364243261</v>
+        <v>0.1964237304098864</v>
       </c>
       <c r="C67">
-        <v>-2525.770999695376</v>
+        <v>-2787.292050854461</v>
       </c>
       <c r="D67">
-        <v>5231.853519080125</v>
+        <v>5175.95284513297</v>
       </c>
       <c r="E67">
-        <v>12025.98679758243</v>
+        <v>12231.60717479436</v>
       </c>
       <c r="F67">
-        <v>13365.3245187755</v>
+        <v>13570.94489598743</v>
       </c>
       <c r="G67">
         <v>5607.7</v>
@@ -7171,37 +7171,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M67">
-        <v>2763.101971608458</v>
+        <v>2805.611232710127</v>
       </c>
       <c r="N67">
-        <v>-1997.111971608459</v>
+        <v>-2039.621232710127</v>
       </c>
       <c r="O67">
-        <v>-329.5234753153957</v>
+        <v>-336.537503397171</v>
       </c>
       <c r="P67">
-        <v>-1667.588496293063</v>
+        <v>-1703.083729312956</v>
       </c>
       <c r="Q67">
-        <v>-1273.888496293063</v>
+        <v>-1309.383729312956</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1902349928480984</v>
+        <v>0.1944830808730424</v>
       </c>
       <c r="T67">
-        <v>2.815306847320252</v>
+        <v>2.898109989888495</v>
       </c>
       <c r="U67">
         <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.04574147146890375</v>
+        <v>0.04504841887089006</v>
       </c>
       <c r="W67">
-        <v>0.1972801796098871</v>
+        <v>0.1974234589591696</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2772210392054772</v>
+        <v>0.2730207204296367</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7217,22 +7217,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1964237304098864</v>
+        <v>0.1980330965765117</v>
       </c>
       <c r="C68">
-        <v>-2787.292050854461</v>
+        <v>-3047.631169104538</v>
       </c>
       <c r="D68">
-        <v>5175.95284513297</v>
+        <v>5121.234104094825</v>
       </c>
       <c r="E68">
-        <v>12231.60717479436</v>
+        <v>12437.22755200629</v>
       </c>
       <c r="F68">
-        <v>13570.94489598743</v>
+        <v>13776.56527319936</v>
       </c>
       <c r="G68">
         <v>5607.7</v>
@@ -7253,37 +7253,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M68">
-        <v>2805.611232710127</v>
+        <v>2848.120493811796</v>
       </c>
       <c r="N68">
-        <v>-2039.621232710127</v>
+        <v>-2082.130493811796</v>
       </c>
       <c r="O68">
-        <v>-336.537503397171</v>
+        <v>-343.5515314789463</v>
       </c>
       <c r="P68">
-        <v>-1703.083729312956</v>
+        <v>-1738.57896233285</v>
       </c>
       <c r="Q68">
-        <v>-1309.383729312956</v>
+        <v>-1344.87896233285</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1944830808730424</v>
+        <v>0.1989886287782862</v>
       </c>
       <c r="T68">
-        <v>2.898109989888495</v>
+        <v>2.9859315047336</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.04504841887089006</v>
+        <v>0.04437605441013049</v>
       </c>
       <c r="W68">
-        <v>0.1974234589591696</v>
+        <v>0.1975624613129512</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2730207204296367</v>
+        <v>0.2689457843038211</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7299,22 +7299,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1980330965765117</v>
+        <v>0.1996424627431371</v>
       </c>
       <c r="C69">
-        <v>-3047.631169104538</v>
+        <v>-3306.825447510832</v>
       </c>
       <c r="D69">
-        <v>5121.234104094825</v>
+        <v>5067.660202900462</v>
       </c>
       <c r="E69">
-        <v>12437.22755200629</v>
+        <v>12642.84792921822</v>
       </c>
       <c r="F69">
-        <v>13776.56527319936</v>
+        <v>13982.18565041129</v>
       </c>
       <c r="G69">
         <v>5607.7</v>
@@ -7335,37 +7335,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M69">
-        <v>2848.120493811796</v>
+        <v>2890.629754913464</v>
       </c>
       <c r="N69">
-        <v>-2082.130493811796</v>
+        <v>-2124.639754913464</v>
       </c>
       <c r="O69">
-        <v>-343.5515314789463</v>
+        <v>-350.5655595607216</v>
       </c>
       <c r="P69">
-        <v>-1738.57896233285</v>
+        <v>-1774.074195352743</v>
       </c>
       <c r="Q69">
-        <v>-1344.87896233285</v>
+        <v>-1380.374195352743</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1989886287782862</v>
+        <v>0.2037757734276076</v>
       </c>
       <c r="T69">
-        <v>2.9859315047336</v>
+        <v>3.079241864256526</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.04437605441013049</v>
+        <v>0.0437234653746874</v>
       </c>
       <c r="W69">
-        <v>0.1975624613129512</v>
+        <v>0.1976973753622098</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2689457843038211</v>
+        <v>0.2649906992405296</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7381,22 +7381,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1996424627431371</v>
+        <v>0.2012518289097624</v>
       </c>
       <c r="C70">
-        <v>-3306.825447510832</v>
+        <v>-3564.910443065952</v>
       </c>
       <c r="D70">
-        <v>5067.660202900462</v>
+        <v>5015.195584557272</v>
       </c>
       <c r="E70">
-        <v>12642.84792921822</v>
+        <v>12848.46830643015</v>
       </c>
       <c r="F70">
-        <v>13982.18565041129</v>
+        <v>14187.80602762322</v>
       </c>
       <c r="G70">
         <v>5607.7</v>
@@ -7417,37 +7417,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M70">
-        <v>2890.629754913464</v>
+        <v>2933.139016015133</v>
       </c>
       <c r="N70">
-        <v>-2124.639754913464</v>
+        <v>-2167.149016015133</v>
       </c>
       <c r="O70">
-        <v>-350.5655595607216</v>
+        <v>-357.579587642497</v>
       </c>
       <c r="P70">
-        <v>-1774.074195352743</v>
+        <v>-1809.569428372636</v>
       </c>
       <c r="Q70">
-        <v>-1380.374195352743</v>
+        <v>-1415.869428372636</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2037757734276076</v>
+        <v>0.2088717661188208</v>
       </c>
       <c r="T70">
-        <v>3.079241864256526</v>
+        <v>3.178572246974478</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.0437234653746874</v>
+        <v>0.04308979196346005</v>
       </c>
       <c r="W70">
-        <v>0.1976973753622098</v>
+        <v>0.1978283788593159</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2649906992405296</v>
+        <v>0.2611502543240003</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7463,22 +7463,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2012518289097624</v>
+        <v>0.2028611950763878</v>
       </c>
       <c r="C71">
-        <v>-3564.910443065952</v>
+        <v>-3821.920255388635</v>
       </c>
       <c r="D71">
-        <v>5015.195584557272</v>
+        <v>4963.806149446518</v>
       </c>
       <c r="E71">
-        <v>12848.46830643015</v>
+        <v>13054.08868364208</v>
       </c>
       <c r="F71">
-        <v>14187.80602762322</v>
+        <v>14393.42640483515</v>
       </c>
       <c r="G71">
         <v>5607.7</v>
@@ -7499,37 +7499,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M71">
-        <v>2933.139016015133</v>
+        <v>2975.648277116802</v>
       </c>
       <c r="N71">
-        <v>-2167.149016015133</v>
+        <v>-2209.658277116802</v>
       </c>
       <c r="O71">
-        <v>-357.579587642497</v>
+        <v>-364.5936157242723</v>
       </c>
       <c r="P71">
-        <v>-1809.569428372636</v>
+        <v>-1845.06466139253</v>
       </c>
       <c r="Q71">
-        <v>-1415.869428372636</v>
+        <v>-1451.36466139253</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2088717661188208</v>
+        <v>0.2143074916561148</v>
       </c>
       <c r="T71">
-        <v>3.178572246974478</v>
+        <v>3.284524655206961</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.04308979196346005</v>
+        <v>0.04247422350683919</v>
       </c>
       <c r="W71">
-        <v>0.1978283788593159</v>
+        <v>0.1979556393993619</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2611502543240003</v>
+        <v>0.257419536405086</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7545,22 +7545,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2028611950763878</v>
+        <v>0.2044705612430131</v>
       </c>
       <c r="C72">
-        <v>-3821.920255388635</v>
+        <v>-4077.887600633099</v>
       </c>
       <c r="D72">
-        <v>4963.806149446518</v>
+        <v>4913.459181413986</v>
       </c>
       <c r="E72">
-        <v>13054.08868364208</v>
+        <v>13259.70906085401</v>
       </c>
       <c r="F72">
-        <v>14393.42640483515</v>
+        <v>14599.04678204709</v>
       </c>
       <c r="G72">
         <v>5607.7</v>
@@ -7581,37 +7581,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M72">
-        <v>2975.648277116802</v>
+        <v>3018.15753821847</v>
       </c>
       <c r="N72">
-        <v>-2209.658277116802</v>
+        <v>-2252.16753821847</v>
       </c>
       <c r="O72">
-        <v>-364.5936157242723</v>
+        <v>-371.6076438060476</v>
       </c>
       <c r="P72">
-        <v>-1845.06466139253</v>
+        <v>-1880.559894412423</v>
       </c>
       <c r="Q72">
-        <v>-1451.36466139253</v>
+        <v>-1486.859894412423</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2143074916561148</v>
+        <v>0.2201180948166705</v>
       </c>
       <c r="T72">
-        <v>3.284524655206961</v>
+        <v>3.397784126076167</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.04247422350683919</v>
+        <v>0.04187599500674286</v>
       </c>
       <c r="W72">
-        <v>0.1979556393993619</v>
+        <v>0.1980793151354629</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.257419536405086</v>
+        <v>0.2537939091317749</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7627,22 +7627,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2044705612430131</v>
+        <v>0.2060799274096384</v>
       </c>
       <c r="C73">
-        <v>-4077.887600633096</v>
+        <v>-4332.843880945686</v>
       </c>
       <c r="D73">
-        <v>4913.459181413986</v>
+        <v>4864.123278313329</v>
       </c>
       <c r="E73">
-        <v>13259.70906085401</v>
+        <v>13465.32943806594</v>
       </c>
       <c r="F73">
-        <v>14599.04678204708</v>
+        <v>14804.66715925901</v>
       </c>
       <c r="G73">
         <v>5607.7</v>
@@ -7663,37 +7663,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M73">
-        <v>3018.15753821847</v>
+        <v>3060.666799320138</v>
       </c>
       <c r="N73">
-        <v>-2252.16753821847</v>
+        <v>-2294.676799320138</v>
       </c>
       <c r="O73">
-        <v>-371.6076438060475</v>
+        <v>-378.6216718878229</v>
       </c>
       <c r="P73">
-        <v>-1880.559894412422</v>
+        <v>-1916.055127432315</v>
       </c>
       <c r="Q73">
-        <v>-1486.859894412422</v>
+        <v>-1522.355127432315</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2201180948166704</v>
+        <v>0.2263437410601229</v>
       </c>
       <c r="T73">
-        <v>3.397784126076166</v>
+        <v>3.519133559150314</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.04187599500674287</v>
+        <v>0.04129438396498256</v>
       </c>
       <c r="W73">
-        <v>0.1980793151354629</v>
+        <v>0.19819955543445</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2537939091317749</v>
+        <v>0.2502689937271669</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7709,22 +7709,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2060799274096384</v>
+        <v>0.2076892935762638</v>
       </c>
       <c r="C74">
-        <v>-4332.843880945686</v>
+        <v>-4586.819249778631</v>
       </c>
       <c r="D74">
-        <v>4864.123278313329</v>
+        <v>4815.768286692314</v>
       </c>
       <c r="E74">
-        <v>13465.32943806594</v>
+        <v>13670.94981527787</v>
       </c>
       <c r="F74">
-        <v>14804.66715925901</v>
+        <v>15010.28753647095</v>
       </c>
       <c r="G74">
         <v>5607.7</v>
@@ -7745,37 +7745,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M74">
-        <v>3060.666799320138</v>
+        <v>3103.176060421807</v>
       </c>
       <c r="N74">
-        <v>-2294.676799320138</v>
+        <v>-2337.186060421807</v>
       </c>
       <c r="O74">
-        <v>-378.6216718878229</v>
+        <v>-385.6356999695982</v>
       </c>
       <c r="P74">
-        <v>-1916.055127432315</v>
+        <v>-1951.550360452209</v>
       </c>
       <c r="Q74">
-        <v>-1522.355127432315</v>
+        <v>-1557.850360452209</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2263437410601229</v>
+        <v>0.233030546284572</v>
       </c>
       <c r="T74">
-        <v>3.519133559150314</v>
+        <v>3.649471839118845</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.04129438396498256</v>
+        <v>0.04072870747231155</v>
       </c>
       <c r="W74">
-        <v>0.19819955543445</v>
+        <v>0.1983165014786703</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2502689937271669</v>
+        <v>0.2468406513473427</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7791,22 +7791,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2076892935762638</v>
+        <v>0.2092986597428891</v>
       </c>
       <c r="C75">
-        <v>-4586.819249778631</v>
+        <v>-4839.842673346402</v>
       </c>
       <c r="D75">
-        <v>4815.768286692314</v>
+        <v>4768.365240336474</v>
       </c>
       <c r="E75">
-        <v>13670.94981527787</v>
+        <v>13876.5701924898</v>
       </c>
       <c r="F75">
-        <v>15010.28753647095</v>
+        <v>15215.90791368288</v>
       </c>
       <c r="G75">
         <v>5607.7</v>
@@ -7827,37 +7827,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M75">
-        <v>3103.176060421807</v>
+        <v>3145.685321523476</v>
       </c>
       <c r="N75">
-        <v>-2337.186060421807</v>
+        <v>-2379.695321523476</v>
       </c>
       <c r="O75">
-        <v>-385.6356999695982</v>
+        <v>-392.6497280513735</v>
       </c>
       <c r="P75">
-        <v>-1951.550360452209</v>
+        <v>-1987.045593472102</v>
       </c>
       <c r="Q75">
-        <v>-1557.850360452209</v>
+        <v>-1593.345593472102</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.233030546284572</v>
+        <v>0.2402317211416709</v>
       </c>
       <c r="T75">
-        <v>3.649471839118845</v>
+        <v>3.789836140623415</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.04072870747231155</v>
+        <v>0.04017831953349654</v>
       </c>
       <c r="W75">
-        <v>0.1983165014786703</v>
+        <v>0.1984302868189928</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2468406513473427</v>
+        <v>0.2435049668696759</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7873,22 +7873,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2092986597428891</v>
+        <v>0.2109080259095145</v>
       </c>
       <c r="C76">
-        <v>-4839.842673346402</v>
+        <v>-5091.941988487826</v>
       </c>
       <c r="D76">
-        <v>4768.365240336474</v>
+        <v>4721.88630240698</v>
       </c>
       <c r="E76">
-        <v>13876.5701924898</v>
+        <v>14082.19056970173</v>
       </c>
       <c r="F76">
-        <v>15215.90791368288</v>
+        <v>15421.52829089481</v>
       </c>
       <c r="G76">
         <v>5607.7</v>
@@ -7909,37 +7909,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M76">
-        <v>3145.685321523476</v>
+        <v>3188.194582625144</v>
       </c>
       <c r="N76">
-        <v>-2379.695321523476</v>
+        <v>-2422.204582625144</v>
       </c>
       <c r="O76">
-        <v>-392.6497280513735</v>
+        <v>-399.6637561331488</v>
       </c>
       <c r="P76">
-        <v>-1987.045593472102</v>
+        <v>-2022.540826491995</v>
       </c>
       <c r="Q76">
-        <v>-1593.345593472102</v>
+        <v>-1628.840826491995</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2402317211416709</v>
+        <v>0.2480089899873377</v>
       </c>
       <c r="T76">
-        <v>3.789836140623415</v>
+        <v>3.941429586248352</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.04017831953349654</v>
+        <v>0.03964260860638325</v>
       </c>
       <c r="W76">
-        <v>0.1984302868189928</v>
+        <v>0.1985410378835734</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2435049668696759</v>
+        <v>0.2402582339780802</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7955,22 +7955,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2109080259095145</v>
+        <v>0.2125173920761398</v>
       </c>
       <c r="C77">
-        <v>-5091.941988487826</v>
+        <v>-5343.143957176881</v>
       </c>
       <c r="D77">
-        <v>4721.88630240698</v>
+        <v>4676.304710929859</v>
       </c>
       <c r="E77">
-        <v>14082.19056970173</v>
+        <v>14287.81094691367</v>
       </c>
       <c r="F77">
-        <v>15421.52829089481</v>
+        <v>15627.14866810674</v>
       </c>
       <c r="G77">
         <v>5607.7</v>
@@ -7991,37 +7991,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M77">
-        <v>3188.194582625144</v>
+        <v>3230.703843726813</v>
       </c>
       <c r="N77">
-        <v>-2422.204582625144</v>
+        <v>-2464.713843726813</v>
       </c>
       <c r="O77">
-        <v>-399.6637561331488</v>
+        <v>-406.6777842149242</v>
       </c>
       <c r="P77">
-        <v>-2022.540826491995</v>
+        <v>-2058.036059511889</v>
       </c>
       <c r="Q77">
-        <v>-1628.840826491995</v>
+        <v>-1664.336059511889</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2480089899873377</v>
+        <v>0.2564343645701435</v>
       </c>
       <c r="T77">
-        <v>3.941429586248352</v>
+        <v>4.1056558190087</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.03964260860638325</v>
+        <v>0.03912099533524663</v>
       </c>
       <c r="W77">
-        <v>0.1985410378835734</v>
+        <v>0.1986488744464544</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2402582339780802</v>
+        <v>0.2370969414257371</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8037,22 +8037,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2125173920761398</v>
+        <v>0.2141267582427652</v>
       </c>
       <c r="C78">
-        <v>-5343.143957176881</v>
+        <v>-5593.474317906386</v>
       </c>
       <c r="D78">
-        <v>4676.304710929859</v>
+        <v>4631.594727412282</v>
       </c>
       <c r="E78">
-        <v>14287.81094691367</v>
+        <v>14493.43132412559</v>
       </c>
       <c r="F78">
-        <v>15627.14866810674</v>
+        <v>15832.76904531867</v>
       </c>
       <c r="G78">
         <v>5607.7</v>
@@ -8073,37 +8073,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M78">
-        <v>3230.703843726813</v>
+        <v>3273.213104828481</v>
       </c>
       <c r="N78">
-        <v>-2464.713843726813</v>
+        <v>-2507.223104828482</v>
       </c>
       <c r="O78">
-        <v>-406.6777842149242</v>
+        <v>-413.6918122966995</v>
       </c>
       <c r="P78">
-        <v>-2058.036059511889</v>
+        <v>-2093.531292531782</v>
       </c>
       <c r="Q78">
-        <v>-1664.336059511889</v>
+        <v>-1699.831292531782</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2564343645701435</v>
+        <v>0.2655923804210193</v>
       </c>
       <c r="T78">
-        <v>4.1056558190087</v>
+        <v>4.28416259374821</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.03912099533524663</v>
+        <v>0.0386129304607629</v>
       </c>
       <c r="W78">
-        <v>0.1986488744464544</v>
+        <v>0.1987539100596503</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2370969414257371</v>
+        <v>0.2340177603682599</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8119,22 +8119,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2141267582427652</v>
+        <v>0.2157361244093905</v>
       </c>
       <c r="C79">
-        <v>-5593.474317906386</v>
+        <v>-5842.957834152021</v>
       </c>
       <c r="D79">
-        <v>4631.594727412282</v>
+        <v>4587.73158837858</v>
       </c>
       <c r="E79">
-        <v>14493.43132412559</v>
+        <v>14699.05170133753</v>
       </c>
       <c r="F79">
-        <v>15832.76904531867</v>
+        <v>16038.3894225306</v>
       </c>
       <c r="G79">
         <v>5607.7</v>
@@ -8155,37 +8155,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M79">
-        <v>3273.213104828481</v>
+        <v>3315.72236593015</v>
       </c>
       <c r="N79">
-        <v>-2507.223104828482</v>
+        <v>-2549.732365930151</v>
       </c>
       <c r="O79">
-        <v>-413.6918122966995</v>
+        <v>-420.7058403784749</v>
       </c>
       <c r="P79">
-        <v>-2093.531292531782</v>
+        <v>-2129.026525551676</v>
       </c>
       <c r="Q79">
-        <v>-1699.831292531782</v>
+        <v>-1735.326525551676</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2655923804210193</v>
+        <v>0.2755829431674293</v>
       </c>
       <c r="T79">
-        <v>4.28416259374821</v>
+        <v>4.478897257100401</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.0386129304607629</v>
+        <v>0.03811789289075312</v>
       </c>
       <c r="W79">
-        <v>0.1987539100596503</v>
+        <v>0.198856252451995</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2340177603682599</v>
+        <v>0.2310175326712309</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8201,22 +8201,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2157361244093905</v>
+        <v>0.2173454905760158</v>
       </c>
       <c r="C80">
-        <v>-5842.957834152021</v>
+        <v>-6091.618340108247</v>
       </c>
       <c r="D80">
-        <v>4587.73158837858</v>
+        <v>4544.691459634285</v>
       </c>
       <c r="E80">
-        <v>14699.05170133753</v>
+        <v>14904.67207854946</v>
       </c>
       <c r="F80">
-        <v>16038.3894225306</v>
+        <v>16244.00979974253</v>
       </c>
       <c r="G80">
         <v>5607.7</v>
@@ -8237,37 +8237,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M80">
-        <v>3315.72236593015</v>
+        <v>3358.231627031819</v>
       </c>
       <c r="N80">
-        <v>-2549.732365930151</v>
+        <v>-2592.241627031819</v>
       </c>
       <c r="O80">
-        <v>-420.7058403784749</v>
+        <v>-427.7198684602502</v>
       </c>
       <c r="P80">
-        <v>-2129.026525551676</v>
+        <v>-2164.521758571569</v>
       </c>
       <c r="Q80">
-        <v>-1735.326525551676</v>
+        <v>-1770.821758571569</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2755829431674293</v>
+        <v>0.286524988080164</v>
       </c>
       <c r="T80">
-        <v>4.478897257100401</v>
+        <v>4.692178078867086</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.03811789289075312</v>
+        <v>0.03763538791745245</v>
       </c>
       <c r="W80">
-        <v>0.198856252451995</v>
+        <v>0.198956003897698</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2310175326712309</v>
+        <v>0.2280932601057724</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8283,22 +8283,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2173454905760158</v>
+        <v>0.2189548567426412</v>
       </c>
       <c r="C81">
-        <v>-6091.618340108247</v>
+        <v>-6339.478783873768</v>
       </c>
       <c r="D81">
-        <v>4544.691459634285</v>
+        <v>4502.451393080693</v>
       </c>
       <c r="E81">
-        <v>14904.67207854946</v>
+        <v>15110.29245576139</v>
       </c>
       <c r="F81">
-        <v>16244.00979974253</v>
+        <v>16449.63017695446</v>
       </c>
       <c r="G81">
         <v>5607.7</v>
@@ -8319,37 +8319,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M81">
-        <v>3358.231627031819</v>
+        <v>3400.740888133488</v>
       </c>
       <c r="N81">
-        <v>-2592.241627031819</v>
+        <v>-2634.750888133488</v>
       </c>
       <c r="O81">
-        <v>-427.7198684602502</v>
+        <v>-434.7338965420255</v>
       </c>
       <c r="P81">
-        <v>-2164.521758571569</v>
+        <v>-2200.016991591463</v>
       </c>
       <c r="Q81">
-        <v>-1770.821758571569</v>
+        <v>-1806.316991591463</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.286524988080164</v>
+        <v>0.2985612374841722</v>
       </c>
       <c r="T81">
-        <v>4.692178078867086</v>
+        <v>4.926786982810441</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.03763538791745245</v>
+        <v>0.03716494556848429</v>
       </c>
       <c r="W81">
-        <v>0.198956003897698</v>
+        <v>0.1990532615572584</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2280932601057724</v>
+        <v>0.2252420943544502</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8365,22 +8365,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2189548567426412</v>
+        <v>0.2205642229092665</v>
       </c>
       <c r="C82">
-        <v>-6339.478783873768</v>
+        <v>-6586.561268250853</v>
       </c>
       <c r="D82">
-        <v>4502.451393080693</v>
+        <v>4460.98928591554</v>
       </c>
       <c r="E82">
-        <v>15110.29245576139</v>
+        <v>15315.91283297332</v>
       </c>
       <c r="F82">
-        <v>16449.63017695446</v>
+        <v>16655.25055416639</v>
       </c>
       <c r="G82">
         <v>5607.7</v>
@@ -8401,37 +8401,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M82">
-        <v>3400.740888133488</v>
+        <v>3443.250149235156</v>
       </c>
       <c r="N82">
-        <v>-2634.750888133488</v>
+        <v>-2677.260149235156</v>
       </c>
       <c r="O82">
-        <v>-434.7338965420255</v>
+        <v>-441.7479246238008</v>
       </c>
       <c r="P82">
-        <v>-2200.016991591463</v>
+        <v>-2235.512224611356</v>
       </c>
       <c r="Q82">
-        <v>-1806.316991591463</v>
+        <v>-1841.812224611356</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2985612374841722</v>
+        <v>0.3118644605096549</v>
       </c>
       <c r="T82">
-        <v>4.926786982810441</v>
+        <v>5.186091560853097</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.03716494556848429</v>
+        <v>0.03670611907998448</v>
       </c>
       <c r="W82">
-        <v>0.1990532615572584</v>
+        <v>0.199148117793126</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2252420943544502</v>
+        <v>0.2224613277574817</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8447,22 +8447,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2205642229092665</v>
+        <v>0.2221735890758919</v>
       </c>
       <c r="C83">
-        <v>-6586.561268250853</v>
+        <v>-6832.887089310963</v>
       </c>
       <c r="D83">
-        <v>4460.98928591554</v>
+        <v>4420.28384206736</v>
       </c>
       <c r="E83">
-        <v>15315.91283297332</v>
+        <v>15521.53321018525</v>
       </c>
       <c r="F83">
-        <v>16655.25055416639</v>
+        <v>16860.87093137832</v>
       </c>
       <c r="G83">
         <v>5607.7</v>
@@ -8483,37 +8483,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M83">
-        <v>3443.250149235156</v>
+        <v>3485.759410336824</v>
       </c>
       <c r="N83">
-        <v>-2677.260149235156</v>
+        <v>-2719.769410336824</v>
       </c>
       <c r="O83">
-        <v>-441.7479246238008</v>
+        <v>-448.761952705576</v>
       </c>
       <c r="P83">
-        <v>-2235.512224611356</v>
+        <v>-2271.007457631248</v>
       </c>
       <c r="Q83">
-        <v>-1841.812224611356</v>
+        <v>-1877.307457631248</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3118644605096549</v>
+        <v>0.326645819426858</v>
       </c>
       <c r="T83">
-        <v>5.186091560853097</v>
+        <v>5.474207758678268</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.03670611907998448</v>
+        <v>0.0362584834814481</v>
       </c>
       <c r="W83">
-        <v>0.199148117793126</v>
+        <v>0.1992406604622651</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2224613277574817</v>
+        <v>0.219748384736049</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8529,22 +8529,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2221735890758919</v>
+        <v>0.2237829552425172</v>
       </c>
       <c r="C84">
-        <v>-6832.887089310963</v>
+        <v>-7078.476772868049</v>
       </c>
       <c r="D84">
-        <v>4420.28384206736</v>
+        <v>4380.314535722206</v>
       </c>
       <c r="E84">
-        <v>15521.53321018525</v>
+        <v>15727.15358739718</v>
       </c>
       <c r="F84">
-        <v>16860.87093137832</v>
+        <v>17066.49130859026</v>
       </c>
       <c r="G84">
         <v>5607.7</v>
@@ -8565,37 +8565,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M84">
-        <v>3485.759410336824</v>
+        <v>3528.268671438494</v>
       </c>
       <c r="N84">
-        <v>-2719.769410336824</v>
+        <v>-2762.278671438494</v>
       </c>
       <c r="O84">
-        <v>-448.761952705576</v>
+        <v>-455.7759807873515</v>
       </c>
       <c r="P84">
-        <v>-2271.007457631248</v>
+        <v>-2306.502690651142</v>
       </c>
       <c r="Q84">
-        <v>-1877.307457631248</v>
+        <v>-1912.802690651142</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.326645819426858</v>
+        <v>0.343166161746085</v>
       </c>
       <c r="T84">
-        <v>5.474207758678268</v>
+        <v>5.796219979776991</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.0362584834814481</v>
+        <v>0.03582163428287642</v>
       </c>
       <c r="W84">
-        <v>0.1992406604622651</v>
+        <v>0.1993309731875696</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.219748384736049</v>
+        <v>0.2171008138356146</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8611,22 +8611,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2237829552425172</v>
+        <v>0.2253923214091425</v>
       </c>
       <c r="C85">
-        <v>-7078.476772868049</v>
+        <v>-7323.35010899078</v>
       </c>
       <c r="D85">
-        <v>4380.314535722206</v>
+        <v>4341.061576811404</v>
       </c>
       <c r="E85">
-        <v>15727.15358739718</v>
+        <v>15932.77396460911</v>
       </c>
       <c r="F85">
-        <v>17066.49130859026</v>
+        <v>17272.11168580219</v>
       </c>
       <c r="G85">
         <v>5607.7</v>
@@ -8647,37 +8647,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M85">
-        <v>3528.268671438494</v>
+        <v>3570.777932540162</v>
       </c>
       <c r="N85">
-        <v>-2762.278671438494</v>
+        <v>-2804.787932540162</v>
       </c>
       <c r="O85">
-        <v>-455.7759807873515</v>
+        <v>-462.7900088691268</v>
       </c>
       <c r="P85">
-        <v>-2306.502690651142</v>
+        <v>-2341.997923671036</v>
       </c>
       <c r="Q85">
-        <v>-1912.802690651142</v>
+        <v>-1948.297923671036</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.343166161746085</v>
+        <v>0.3617515468552153</v>
       </c>
       <c r="T85">
-        <v>5.796219979776991</v>
+        <v>6.158483728513053</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.03582163428287642</v>
+        <v>0.03539518625569932</v>
       </c>
       <c r="W85">
-        <v>0.1993309731875696</v>
+        <v>0.1994191356098906</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2171008138356146</v>
+        <v>0.2145162803375716</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8693,22 +8693,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2253923214091425</v>
+        <v>0.2270016875757679</v>
       </c>
       <c r="C86">
-        <v>-7323.350108990777</v>
+        <v>-7567.52618467564</v>
       </c>
       <c r="D86">
-        <v>4341.061576811406</v>
+        <v>4302.505878338474</v>
       </c>
       <c r="E86">
-        <v>15932.77396460911</v>
+        <v>16138.39434182104</v>
       </c>
       <c r="F86">
-        <v>17272.11168580218</v>
+        <v>17477.73206301411</v>
       </c>
       <c r="G86">
         <v>5607.7</v>
@@ -8729,37 +8729,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M86">
-        <v>3570.777932540161</v>
+        <v>3613.28719364183</v>
       </c>
       <c r="N86">
-        <v>-2804.787932540161</v>
+        <v>-2847.29719364183</v>
       </c>
       <c r="O86">
-        <v>-462.7900088691267</v>
+        <v>-469.804036950902</v>
       </c>
       <c r="P86">
-        <v>-2341.997923671035</v>
+        <v>-2377.493156690928</v>
       </c>
       <c r="Q86">
-        <v>-1948.297923671035</v>
+        <v>-1983.793156690928</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3617515468552151</v>
+        <v>0.3828149833122295</v>
       </c>
       <c r="T86">
-        <v>6.158483728513048</v>
+        <v>6.56904931041392</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.03539518625569933</v>
+        <v>0.03497877229974992</v>
       </c>
       <c r="W86">
-        <v>0.1994191356098906</v>
+        <v>0.1995052236222746</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2145162803375716</v>
+        <v>0.2119925593924238</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8775,22 +8775,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2270016875757679</v>
+        <v>0.2286110537423932</v>
       </c>
       <c r="C87">
-        <v>-7567.52618467564</v>
+        <v>-7811.02341479419</v>
       </c>
       <c r="D87">
-        <v>4302.505878338474</v>
+        <v>4264.629025431855</v>
       </c>
       <c r="E87">
-        <v>16138.39434182104</v>
+        <v>16344.01471903297</v>
       </c>
       <c r="F87">
-        <v>17477.73206301411</v>
+        <v>17683.35244022604</v>
       </c>
       <c r="G87">
         <v>5607.7</v>
@@ -8811,37 +8811,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M87">
-        <v>3613.28719364183</v>
+        <v>3655.796454743499</v>
       </c>
       <c r="N87">
-        <v>-2847.29719364183</v>
+        <v>-2889.806454743499</v>
       </c>
       <c r="O87">
-        <v>-469.804036950902</v>
+        <v>-476.8180650326773</v>
       </c>
       <c r="P87">
-        <v>-2377.493156690928</v>
+        <v>-2412.988389710822</v>
       </c>
       <c r="Q87">
-        <v>-1983.793156690928</v>
+        <v>-2019.288389710822</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3828149833122295</v>
+        <v>0.4068874821202459</v>
       </c>
       <c r="T87">
-        <v>6.56904931041392</v>
+        <v>7.038267118300628</v>
       </c>
       <c r="U87">
         <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.03497877229974992</v>
+        <v>0.03457204238928772</v>
       </c>
       <c r="W87">
-        <v>0.1995052236222746</v>
+        <v>0.1995893095878591</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2119925593924238</v>
+        <v>0.2095275296320467</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8857,22 +8857,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2286110537423932</v>
+        <v>0.2302204199090185</v>
       </c>
       <c r="C88">
-        <v>-7811.02341479419</v>
+        <v>-8053.85957141994</v>
       </c>
       <c r="D88">
-        <v>4264.629025431855</v>
+        <v>4227.413246018034</v>
       </c>
       <c r="E88">
-        <v>16344.01471903297</v>
+        <v>16549.6350962449</v>
       </c>
       <c r="F88">
-        <v>17683.35244022604</v>
+        <v>17888.97281743797</v>
       </c>
       <c r="G88">
         <v>5607.7</v>
@@ -8893,37 +8893,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M88">
-        <v>3655.796454743499</v>
+        <v>3698.305715845167</v>
       </c>
       <c r="N88">
-        <v>-2889.806454743499</v>
+        <v>-2932.315715845167</v>
       </c>
       <c r="O88">
-        <v>-476.8180650326773</v>
+        <v>-483.8320931144526</v>
       </c>
       <c r="P88">
-        <v>-2412.988389710822</v>
+        <v>-2448.483622730715</v>
       </c>
       <c r="Q88">
-        <v>-2019.288389710822</v>
+        <v>-2054.783622730715</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4068874821202459</v>
+        <v>0.4346634422833417</v>
       </c>
       <c r="T88">
-        <v>7.038267118300628</v>
+        <v>7.579672281246831</v>
       </c>
       <c r="U88">
         <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.03457204238928772</v>
+        <v>0.0341746625917097</v>
       </c>
       <c r="W88">
-        <v>0.1995893095878591</v>
+        <v>0.1996714625427404</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2095275296320467</v>
+        <v>0.207119167222483</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8939,22 +8939,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2302204199090185</v>
+        <v>0.2318297860756439</v>
       </c>
       <c r="C89">
-        <v>-8053.85957141994</v>
+        <v>-8296.051811632989</v>
       </c>
       <c r="D89">
-        <v>4227.413246018034</v>
+        <v>4190.841383016918</v>
       </c>
       <c r="E89">
-        <v>16549.6350962449</v>
+        <v>16755.25547345683</v>
       </c>
       <c r="F89">
-        <v>17888.97281743797</v>
+        <v>18094.59319464991</v>
       </c>
       <c r="G89">
         <v>5607.7</v>
@@ -8975,37 +8975,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M89">
-        <v>3698.305715845167</v>
+        <v>3740.814976946836</v>
       </c>
       <c r="N89">
-        <v>-2932.315715845167</v>
+        <v>-2974.824976946836</v>
       </c>
       <c r="O89">
-        <v>-483.8320931144526</v>
+        <v>-490.846121196228</v>
       </c>
       <c r="P89">
-        <v>-2448.483622730715</v>
+        <v>-2483.978855750608</v>
       </c>
       <c r="Q89">
-        <v>-2054.783622730715</v>
+        <v>-2090.278855750608</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4346634422833417</v>
+        <v>0.4670687291402868</v>
       </c>
       <c r="T89">
-        <v>7.579672281246831</v>
+        <v>8.211311638017399</v>
       </c>
       <c r="U89">
         <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.0341746625917097</v>
+        <v>0.03378631415316754</v>
       </c>
       <c r="W89">
-        <v>0.1996714625427404</v>
+        <v>0.1997517483850108</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.207119167222483</v>
+        <v>0.2047655403222275</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9021,22 +9021,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2318297860756439</v>
+        <v>0.2334391522422692</v>
       </c>
       <c r="C90">
-        <v>-8296.051811632989</v>
+        <v>-8537.616703893744</v>
       </c>
       <c r="D90">
-        <v>4190.841383016918</v>
+        <v>4154.896867968094</v>
       </c>
       <c r="E90">
-        <v>16755.25547345683</v>
+        <v>16960.87585066876</v>
       </c>
       <c r="F90">
-        <v>18094.59319464991</v>
+        <v>18300.21357186184</v>
       </c>
       <c r="G90">
         <v>5607.7</v>
@@ -9057,37 +9057,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M90">
-        <v>3740.814976946836</v>
+        <v>3783.324238048504</v>
       </c>
       <c r="N90">
-        <v>-2974.824976946836</v>
+        <v>-3017.334238048505</v>
       </c>
       <c r="O90">
-        <v>-490.846121196228</v>
+        <v>-497.8601492780033</v>
       </c>
       <c r="P90">
-        <v>-2483.978855750608</v>
+        <v>-2519.474088770501</v>
       </c>
       <c r="Q90">
-        <v>-2090.278855750608</v>
+        <v>-2125.774088770501</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4670687291402868</v>
+        <v>0.5053658863348585</v>
       </c>
       <c r="T90">
-        <v>8.211311638017399</v>
+        <v>8.957794514200801</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.03378631415316754</v>
+        <v>0.03340669264582858</v>
       </c>
       <c r="W90">
-        <v>0.1997517483850108</v>
+        <v>0.1998302300510503</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2047655403222275</v>
+        <v>0.2024648039141126</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9103,22 +9103,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2334391522422692</v>
+        <v>0.2350485184088946</v>
       </c>
       <c r="C91">
-        <v>-8537.616703893744</v>
+        <v>-8778.570253071002</v>
       </c>
       <c r="D91">
-        <v>4154.896867968094</v>
+        <v>4119.563696002765</v>
       </c>
       <c r="E91">
-        <v>16960.87585066876</v>
+        <v>17166.49622788069</v>
       </c>
       <c r="F91">
-        <v>18300.21357186184</v>
+        <v>18505.83394907377</v>
       </c>
       <c r="G91">
         <v>5607.7</v>
@@ -9139,37 +9139,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M91">
-        <v>3783.324238048504</v>
+        <v>3825.833499150173</v>
       </c>
       <c r="N91">
-        <v>-3017.334238048505</v>
+        <v>-3059.843499150173</v>
       </c>
       <c r="O91">
-        <v>-497.8601492780033</v>
+        <v>-504.8741773597786</v>
       </c>
       <c r="P91">
-        <v>-2519.474088770501</v>
+        <v>-2554.969321790395</v>
       </c>
       <c r="Q91">
-        <v>-2125.774088770501</v>
+        <v>-2161.269321790395</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5053658863348585</v>
+        <v>0.5513224749683444</v>
       </c>
       <c r="T91">
-        <v>8.957794514200801</v>
+        <v>9.853573965620884</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.03340669264582858</v>
+        <v>0.03303550717198604</v>
       </c>
       <c r="W91">
-        <v>0.1998302300510503</v>
+        <v>0.1999069676800668</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2024648039141126</v>
+        <v>0.2002151949817336</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9185,22 +9185,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2350485184088946</v>
+        <v>0.2687321683383852</v>
       </c>
       <c r="C92">
-        <v>-8778.570253071002</v>
+        <v>-9606.630821093673</v>
       </c>
       <c r="D92">
-        <v>4119.563696002765</v>
+        <v>3497.123505192028</v>
       </c>
       <c r="E92">
-        <v>17166.49622788069</v>
+        <v>17372.11660509263</v>
       </c>
       <c r="F92">
-        <v>18505.83394907377</v>
+        <v>18711.4543262857</v>
       </c>
       <c r="G92">
         <v>5607.7</v>
@@ -9221,45 +9221,45 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M92">
-        <v>3825.833499150173</v>
+        <v>4523.243661671841</v>
       </c>
       <c r="N92">
-        <v>-3059.843499150173</v>
+        <v>-3757.253661671842</v>
       </c>
       <c r="O92">
-        <v>-504.8741773597786</v>
+        <v>-619.9468541758539</v>
       </c>
       <c r="P92">
-        <v>-2554.969321790395</v>
+        <v>-3137.306807495988</v>
       </c>
       <c r="Q92">
-        <v>-2161.269321790395</v>
+        <v>-2743.606807495988</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5513224749683444</v>
+        <v>0.6099836806633305</v>
       </c>
       <c r="T92">
-        <v>9.853573965620884</v>
+        <v>10.99699005066091</v>
       </c>
       <c r="U92">
-        <v>0.2067366166625341</v>
+        <v>0.2417366166625341</v>
       </c>
       <c r="V92">
-        <v>0.03303550717198604</v>
+        <v>0.02794197249884289</v>
       </c>
       <c r="W92">
-        <v>0.1999069676800668</v>
+        <v>0.2349820187677862</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.2002151949817336</v>
+        <v>0.1693452878717751</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9267,22 +9267,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2687321683383852</v>
+        <v>0.2706915345050105</v>
       </c>
       <c r="C93">
-        <v>-9606.630821093673</v>
+        <v>-9842.719866197727</v>
       </c>
       <c r="D93">
-        <v>3497.123505192028</v>
+        <v>3466.654837299902</v>
       </c>
       <c r="E93">
-        <v>17372.11660509263</v>
+        <v>17577.73698230456</v>
       </c>
       <c r="F93">
-        <v>18711.4543262857</v>
+        <v>18917.07470349763</v>
       </c>
       <c r="G93">
         <v>5607.7</v>
@@ -9303,37 +9303,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M93">
-        <v>4523.243661671841</v>
+        <v>4572.949635975928</v>
       </c>
       <c r="N93">
-        <v>-3757.253661671842</v>
+        <v>-3806.959635975928</v>
       </c>
       <c r="O93">
-        <v>-619.9468541758539</v>
+        <v>-628.1483399360282</v>
       </c>
       <c r="P93">
-        <v>-3137.306807495988</v>
+        <v>-3178.8112960399</v>
       </c>
       <c r="Q93">
-        <v>-2743.606807495988</v>
+        <v>-2785.1112960399</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6099836806633305</v>
+        <v>0.680506640746247</v>
       </c>
       <c r="T93">
-        <v>10.99699005066091</v>
+        <v>12.37161380699352</v>
       </c>
       <c r="U93">
         <v>0.2417366166625341</v>
       </c>
       <c r="V93">
-        <v>0.02794197249884289</v>
+        <v>0.02763825540646415</v>
       </c>
       <c r="W93">
-        <v>0.2349820187677862</v>
+        <v>0.2350554383101205</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1693452878717751</v>
+        <v>0.1675045782209948</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9349,22 +9349,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2706915345050105</v>
+        <v>0.2726509006716359</v>
       </c>
       <c r="C94">
-        <v>-9842.719866197727</v>
+        <v>-10078.28258077514</v>
       </c>
       <c r="D94">
-        <v>3466.654837299902</v>
+        <v>3436.712499934421</v>
       </c>
       <c r="E94">
-        <v>17577.73698230456</v>
+        <v>17783.35735951649</v>
       </c>
       <c r="F94">
-        <v>18917.07470349763</v>
+        <v>19122.69508070956</v>
       </c>
       <c r="G94">
         <v>5607.7</v>
@@ -9385,37 +9385,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M94">
-        <v>4572.949635975928</v>
+        <v>4622.655610280013</v>
       </c>
       <c r="N94">
-        <v>-3806.959635975928</v>
+        <v>-3856.665610280013</v>
       </c>
       <c r="O94">
-        <v>-628.1483399360282</v>
+        <v>-636.3498256962023</v>
       </c>
       <c r="P94">
-        <v>-3178.8112960399</v>
+        <v>-3220.315784583811</v>
       </c>
       <c r="Q94">
-        <v>-2785.1112960399</v>
+        <v>-2826.615784583812</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.680506640746247</v>
+        <v>0.7711790179957109</v>
       </c>
       <c r="T94">
-        <v>12.37161380699352</v>
+        <v>14.1389872079926</v>
       </c>
       <c r="U94">
         <v>0.2417366166625341</v>
       </c>
       <c r="V94">
-        <v>0.02763825540646415</v>
+        <v>0.02734106986445917</v>
       </c>
       <c r="W94">
-        <v>0.2350554383101205</v>
+        <v>0.2351272789375658</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1675045782209948</v>
+        <v>0.165703453723995</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9431,22 +9431,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2726509006716359</v>
+        <v>0.2746102668382613</v>
       </c>
       <c r="C95">
-        <v>-10078.28258077514</v>
+        <v>-10313.33248617144</v>
       </c>
       <c r="D95">
-        <v>3436.712499934421</v>
+        <v>3407.28297175005</v>
       </c>
       <c r="E95">
-        <v>17783.35735951649</v>
+        <v>17988.97773672842</v>
       </c>
       <c r="F95">
-        <v>19122.69508070956</v>
+        <v>19328.31545792149</v>
       </c>
       <c r="G95">
         <v>5607.7</v>
@@ -9467,37 +9467,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M95">
-        <v>4622.655610280013</v>
+        <v>4672.3615845841</v>
       </c>
       <c r="N95">
-        <v>-3856.665610280013</v>
+        <v>-3906.371584584101</v>
       </c>
       <c r="O95">
-        <v>-636.3498256962023</v>
+        <v>-644.5513114563767</v>
       </c>
       <c r="P95">
-        <v>-3220.315784583811</v>
+        <v>-3261.820273127724</v>
       </c>
       <c r="Q95">
-        <v>-2826.615784583812</v>
+        <v>-2868.120273127724</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7711790179957109</v>
+        <v>0.8920755209949964</v>
       </c>
       <c r="T95">
-        <v>14.1389872079926</v>
+        <v>16.49548507599137</v>
       </c>
       <c r="U95">
         <v>0.2417366166625341</v>
       </c>
       <c r="V95">
-        <v>0.02734106986445917</v>
+        <v>0.02705020741909258</v>
       </c>
       <c r="W95">
-        <v>0.2351272789375658</v>
+        <v>0.2351975910410229</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.165703453723995</v>
+        <v>0.1639406510248035</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9513,22 +9513,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2746102668382613</v>
+        <v>0.2765696330048866</v>
       </c>
       <c r="C96">
-        <v>-10313.33248617144</v>
+        <v>-10547.88264451634</v>
       </c>
       <c r="D96">
-        <v>3407.28297175005</v>
+        <v>3378.353190617087</v>
       </c>
       <c r="E96">
-        <v>17988.97773672842</v>
+        <v>18194.59811394035</v>
       </c>
       <c r="F96">
-        <v>19328.31545792149</v>
+        <v>19533.93583513342</v>
       </c>
       <c r="G96">
         <v>5607.7</v>
@@ -9549,37 +9549,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M96">
-        <v>4672.3615845841</v>
+        <v>4722.067558888186</v>
       </c>
       <c r="N96">
-        <v>-3906.371584584101</v>
+        <v>-3956.077558888186</v>
       </c>
       <c r="O96">
-        <v>-644.5513114563767</v>
+        <v>-652.7527972165508</v>
       </c>
       <c r="P96">
-        <v>-3261.820273127724</v>
+        <v>-3303.324761671635</v>
       </c>
       <c r="Q96">
-        <v>-2868.120273127724</v>
+        <v>-2909.624761671635</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8920755209949964</v>
+        <v>1.061330625193996</v>
       </c>
       <c r="T96">
-        <v>16.49548507599137</v>
+        <v>19.79458209118965</v>
       </c>
       <c r="U96">
         <v>0.2417366166625341</v>
       </c>
       <c r="V96">
-        <v>0.02705020741909258</v>
+        <v>0.02676546839362845</v>
       </c>
       <c r="W96">
-        <v>0.2351975910410229</v>
+        <v>0.2352664228896704</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1639406510248035</v>
+        <v>0.1622149599613845</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9595,22 +9595,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2765696330048866</v>
+        <v>0.2785289991715119</v>
       </c>
       <c r="C97">
-        <v>-10547.88264451634</v>
+        <v>-10781.9456780546</v>
       </c>
       <c r="D97">
-        <v>3378.353190617087</v>
+        <v>3349.910534290758</v>
       </c>
       <c r="E97">
-        <v>18194.59811394035</v>
+        <v>18400.21849115228</v>
       </c>
       <c r="F97">
-        <v>19533.93583513342</v>
+        <v>19739.55621234535</v>
       </c>
       <c r="G97">
         <v>5607.7</v>
@@ -9631,37 +9631,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M97">
-        <v>4722.067558888186</v>
+        <v>4771.773533192272</v>
       </c>
       <c r="N97">
-        <v>-3956.077558888186</v>
+        <v>-4005.783533192272</v>
       </c>
       <c r="O97">
-        <v>-652.7527972165508</v>
+        <v>-660.954282976725</v>
       </c>
       <c r="P97">
-        <v>-3303.324761671635</v>
+        <v>-3344.829250215547</v>
       </c>
       <c r="Q97">
-        <v>-2909.624761671635</v>
+        <v>-2951.129250215547</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.061330625193996</v>
+        <v>1.315213281492496</v>
       </c>
       <c r="T97">
-        <v>19.79458209118965</v>
+        <v>24.74322761398708</v>
       </c>
       <c r="U97">
         <v>0.2417366166625341</v>
       </c>
       <c r="V97">
-        <v>0.02676546839362845</v>
+        <v>0.02648666143119482</v>
       </c>
       <c r="W97">
-        <v>0.2352664228896704</v>
+        <v>0.235333820741471</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1622149599613845</v>
+        <v>0.1605252207951201</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9677,22 +9677,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2785289991715119</v>
+        <v>0.2804883653381373</v>
       </c>
       <c r="C98">
-        <v>-10781.9456780546</v>
+        <v>-11015.53378750862</v>
       </c>
       <c r="D98">
-        <v>3349.910534290758</v>
+        <v>3321.942802048666</v>
       </c>
       <c r="E98">
-        <v>18400.21849115228</v>
+        <v>18605.83886836421</v>
       </c>
       <c r="F98">
-        <v>19739.55621234535</v>
+        <v>19945.17658955728</v>
       </c>
       <c r="G98">
         <v>5607.7</v>
@@ -9713,37 +9713,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M98">
-        <v>4771.773533192272</v>
+        <v>4821.479507496358</v>
       </c>
       <c r="N98">
-        <v>-4005.783533192272</v>
+        <v>-4055.489507496358</v>
       </c>
       <c r="O98">
-        <v>-660.954282976725</v>
+        <v>-669.1557687368991</v>
       </c>
       <c r="P98">
-        <v>-3344.829250215547</v>
+        <v>-3386.333738759459</v>
       </c>
       <c r="Q98">
-        <v>-2951.129250215547</v>
+        <v>-2992.633738759459</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.315213281492492</v>
+        <v>1.73835104198999</v>
       </c>
       <c r="T98">
-        <v>24.74322761398701</v>
+        <v>32.99097015198269</v>
       </c>
       <c r="U98">
         <v>0.2417366166625341</v>
       </c>
       <c r="V98">
-        <v>0.02648666143119482</v>
+        <v>0.02621360306592477</v>
       </c>
       <c r="W98">
-        <v>0.235333820741471</v>
+        <v>0.2353998289468428</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1605252207951201</v>
+        <v>0.1588703216116653</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9759,22 +9759,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2804883653381373</v>
+        <v>0.2824477315047626</v>
       </c>
       <c r="C99">
-        <v>-11015.53378750862</v>
+        <v>-11248.65876952876</v>
       </c>
       <c r="D99">
-        <v>3321.942802048666</v>
+        <v>3294.438197240454</v>
       </c>
       <c r="E99">
-        <v>18605.83886836421</v>
+        <v>18811.45924557614</v>
       </c>
       <c r="F99">
-        <v>19945.17658955728</v>
+        <v>20150.79696676921</v>
       </c>
       <c r="G99">
         <v>5607.7</v>
@@ -9795,37 +9795,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M99">
-        <v>4821.479507496358</v>
+        <v>4871.185481800444</v>
       </c>
       <c r="N99">
-        <v>-4055.489507496358</v>
+        <v>-4105.195481800444</v>
       </c>
       <c r="O99">
-        <v>-669.1557687368991</v>
+        <v>-677.3572544970733</v>
       </c>
       <c r="P99">
-        <v>-3386.333738759459</v>
+        <v>-3427.838227303371</v>
       </c>
       <c r="Q99">
-        <v>-2992.633738759459</v>
+        <v>-3034.138227303371</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.73835104198999</v>
+        <v>2.584626562984984</v>
       </c>
       <c r="T99">
-        <v>32.99097015198269</v>
+        <v>49.48645522797402</v>
       </c>
       <c r="U99">
         <v>0.2417366166625341</v>
       </c>
       <c r="V99">
-        <v>0.02621360306592477</v>
+        <v>0.02594611732035411</v>
       </c>
       <c r="W99">
-        <v>0.2353998289468428</v>
+        <v>0.2354644900459825</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1588703216116653</v>
+        <v>0.157249195880934</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9841,22 +9841,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2824477315047626</v>
+        <v>0.2844070976713879</v>
       </c>
       <c r="C100">
-        <v>-11248.65876952876</v>
+        <v>-11481.33203328391</v>
       </c>
       <c r="D100">
-        <v>3294.438197240454</v>
+        <v>3267.385310697232</v>
       </c>
       <c r="E100">
-        <v>18811.45924557614</v>
+        <v>19017.07962278807</v>
       </c>
       <c r="F100">
-        <v>20150.79696676921</v>
+        <v>20356.41734398115</v>
       </c>
       <c r="G100">
         <v>5607.7</v>
@@ -9877,37 +9877,37 @@
         <v>765.9899999999999</v>
       </c>
       <c r="M100">
-        <v>4871.185481800444</v>
+        <v>4920.89145610453</v>
       </c>
       <c r="N100">
-        <v>-4105.195481800444</v>
+        <v>-4154.901456104531</v>
       </c>
       <c r="O100">
-        <v>-677.3572544970733</v>
+        <v>-685.5587402572476</v>
       </c>
       <c r="P100">
-        <v>-3427.838227303371</v>
+        <v>-3469.342715847283</v>
       </c>
       <c r="Q100">
-        <v>-3034.138227303371</v>
+        <v>-3075.642715847283</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.584626562984984</v>
+        <v>5.123453125969969</v>
       </c>
       <c r="T100">
-        <v>49.48645522797402</v>
+        <v>98.97291045594804</v>
       </c>
       <c r="U100">
         <v>0.2417366166625341</v>
       </c>
       <c r="V100">
-        <v>0.02594611732035411</v>
+        <v>0.02568403532721922</v>
       </c>
       <c r="W100">
-        <v>0.2354644900459825</v>
+        <v>0.2355278448602911</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9915,91 +9915,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.157249195880934</v>
+        <v>0.155660820164965</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2844070976713879</v>
-      </c>
-      <c r="C101">
-        <v>-11481.33203328391</v>
-      </c>
-      <c r="D101">
-        <v>3267.385310697232</v>
-      </c>
-      <c r="E101">
-        <v>19017.07962278807</v>
-      </c>
-      <c r="F101">
-        <v>20356.41734398115</v>
-      </c>
-      <c r="G101">
-        <v>5607.7</v>
-      </c>
-      <c r="H101">
-        <v>19222.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1159.69</v>
-      </c>
-      <c r="K101">
-        <v>393.6999999999999</v>
-      </c>
-      <c r="L101">
-        <v>765.9899999999999</v>
-      </c>
-      <c r="M101">
-        <v>4920.89145610453</v>
-      </c>
-      <c r="N101">
-        <v>-4154.901456104531</v>
-      </c>
-      <c r="O101">
-        <v>-685.5587402572476</v>
-      </c>
-      <c r="P101">
-        <v>-3469.342715847283</v>
-      </c>
-      <c r="Q101">
-        <v>-3075.642715847283</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.123453125969969</v>
-      </c>
-      <c r="T101">
-        <v>98.97291045594804</v>
-      </c>
-      <c r="U101">
-        <v>0.2417366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.02568403532721922</v>
-      </c>
-      <c r="W101">
-        <v>0.2355278448602911</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.155660820164965</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
